--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team X" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Team X" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Log" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -200,7 +200,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -270,6 +270,7 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-20 18:45 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-20 19:59 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1372,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1427,6 +1428,78 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n"/>
+      <c r="G2" s="27" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n"/>
+      <c r="G3" s="27" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-20 19:59 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-20 21:00 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1373,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1431,7 +1431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F3" s="27" t="n"/>
@@ -1479,7 +1479,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1494,11 +1494,155 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F4" s="27" t="n"/>
       <c r="G4" s="27" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:27:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="27" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:22:11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="27" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:20:27</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="27" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="27" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-20 21:00 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-20 21:25 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1373,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1431,22 +1431,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F2" s="27" t="n"/>
@@ -1455,22 +1455,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F3" s="27" t="n"/>
@@ -1479,22 +1479,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F4" s="27" t="n"/>
@@ -1503,22 +1503,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F5" s="27" t="n"/>
@@ -1527,22 +1527,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F6" s="27" t="n"/>
@@ -1551,7 +1551,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F9" s="27" t="n"/>
@@ -1623,7 +1623,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1638,11 +1638,131 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F10" s="27" t="n"/>
       <c r="G10" s="27" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:22:11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:20:27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="27" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="27" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-20 21:25 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-20 22:14 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1373,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1431,7 +1431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F2" s="27" t="n"/>
@@ -1455,7 +1455,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F3" s="27" t="n"/>
@@ -1479,7 +1479,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F4" s="27" t="n"/>
@@ -1503,7 +1503,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F5" s="27" t="n"/>
@@ -1527,7 +1527,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F6" s="27" t="n"/>
@@ -1551,22 +1551,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F7" s="27" t="n"/>
@@ -1575,7 +1575,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F9" s="27" t="n"/>
@@ -1623,7 +1623,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F10" s="27" t="n"/>
@@ -1647,7 +1647,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F11" s="27" t="n"/>
@@ -1671,7 +1671,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F12" s="27" t="n"/>
@@ -1695,7 +1695,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1719,7 +1719,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F14" s="27" t="n"/>
@@ -1743,7 +1743,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1758,11 +1758,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F15" s="27" t="n"/>
       <c r="G15" s="27" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-20 22:14 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-21 05:15 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -852,7 +852,9 @@
         <f>SUM(E3:AE3)</f>
         <v/>
       </c>
-      <c r="E3" s="22" t="n"/>
+      <c r="E3" s="22" t="n">
+        <v>6310</v>
+      </c>
       <c r="F3" s="22" t="n"/>
       <c r="G3" s="22" t="n"/>
       <c r="H3" s="22" t="n"/>
@@ -1373,7 +1375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1431,46 +1433,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G2" s="27" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F3" s="27" t="n"/>
@@ -1479,7 +1493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1503,7 +1517,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1527,7 +1541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1542,7 +1556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F6" s="27" t="n"/>
@@ -1551,7 +1565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1566,7 +1580,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F7" s="27" t="n"/>
@@ -1575,22 +1589,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F8" s="27" t="n"/>
@@ -1599,22 +1613,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F9" s="27" t="n"/>
@@ -1623,7 +1637,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1638,7 +1652,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F10" s="27" t="n"/>
@@ -1647,7 +1661,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1671,7 +1685,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1695,7 +1709,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1719,7 +1733,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1734,7 +1748,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F14" s="27" t="n"/>
@@ -1743,7 +1757,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1758,7 +1772,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F15" s="27" t="n"/>
@@ -1767,7 +1781,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1782,11 +1796,59 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F16" s="27" t="n"/>
       <c r="G16" s="27" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="27" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n"/>
+      <c r="G18" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-21 05:15 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-21 12:04 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -986,8 +986,12 @@
         <f>SUM(E6:AE6)</f>
         <v/>
       </c>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
+      <c r="E6" s="22" t="n">
+        <v>9060</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="22" t="n"/>
@@ -1375,7 +1379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1433,17 +1437,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1453,11 +1457,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>6310</v>
+        <v>100</v>
       </c>
       <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
@@ -1469,46 +1473,58 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G3" s="27" t="n"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F4" s="27" t="n"/>
@@ -1517,22 +1533,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F5" s="27" t="n"/>
@@ -1541,17 +1557,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1565,46 +1581,58 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G7" s="27" t="n"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F8" s="27" t="n"/>
@@ -1613,7 +1641,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1637,22 +1665,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F10" s="27" t="n"/>
@@ -1661,22 +1689,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F11" s="27" t="n"/>
@@ -1685,22 +1713,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F12" s="27" t="n"/>
@@ -1709,22 +1737,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F13" s="27" t="n"/>
@@ -1733,22 +1761,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F14" s="27" t="n"/>
@@ -1757,7 +1785,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1781,7 +1809,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1805,7 +1833,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1820,7 +1848,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F17" s="27" t="n"/>
@@ -1829,7 +1857,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1844,11 +1872,131 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F18" s="27" t="n"/>
       <c r="G18" s="27" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:22:11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="27" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:20:27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="27" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="27" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-21 12:04 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-21 13:40 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -898,7 +898,9 @@
         <f>SUM(E4:AE4)</f>
         <v/>
       </c>
-      <c r="E4" s="22" t="n"/>
+      <c r="E4" s="22" t="n">
+        <v>10383</v>
+      </c>
       <c r="F4" s="22" t="n"/>
       <c r="G4" s="22" t="n"/>
       <c r="H4" s="22" t="n"/>
@@ -1379,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1437,118 +1439,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n"/>
       <c r="G2" s="27" t="n"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n"/>
       <c r="G3" s="27" t="n"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G4" s="27" t="n"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F5" s="27" t="n"/>
@@ -1557,17 +1547,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1581,17 +1571,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1601,11 +1591,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>6310</v>
+        <v>100</v>
       </c>
       <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
@@ -1617,46 +1607,58 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G8" s="27" t="n"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F9" s="27" t="n"/>
@@ -1665,22 +1667,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F10" s="27" t="n"/>
@@ -1689,17 +1691,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1713,46 +1715,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G12" s="27" t="n"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F13" s="27" t="n"/>
@@ -1761,7 +1775,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1785,22 +1799,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F15" s="27" t="n"/>
@@ -1809,22 +1823,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F16" s="27" t="n"/>
@@ -1833,22 +1847,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F17" s="27" t="n"/>
@@ -1857,22 +1871,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F18" s="27" t="n"/>
@@ -1881,22 +1895,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F19" s="27" t="n"/>
@@ -1905,7 +1919,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1929,7 +1943,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1953,7 +1967,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1968,7 +1982,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F22" s="27" t="n"/>
@@ -1977,7 +1991,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1992,11 +2006,131 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F23" s="27" t="n"/>
       <c r="G23" s="27" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:22:11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="27" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:20:27</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="27" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="27" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n"/>
+      <c r="G27" s="27" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-21 13:40 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-21 15:12 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -992,7 +992,7 @@
         <v>9060</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>100</v>
+        <v>1985</v>
       </c>
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1439,31 +1439,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n"/>
-      <c r="G2" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G2" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1478,7 +1492,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F3" s="27" t="n"/>
@@ -1487,43 +1501,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n"/>
       <c r="G4" s="27" t="n"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1538,16 +1540,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F5" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G5" s="27" t="n"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1562,7 +1576,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F6" s="27" t="n"/>
@@ -1571,43 +1585,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n"/>
       <c r="G7" s="27" t="n"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1627,11 +1629,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
@@ -1643,31 +1645,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G9" s="27" t="n"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1682,7 +1696,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F10" s="27" t="n"/>
@@ -1691,7 +1705,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1706,7 +1720,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F11" s="27" t="n"/>
@@ -1715,43 +1729,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n"/>
       <c r="G12" s="27" t="n"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1766,26 +1768,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G13" s="27" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1799,7 +1813,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1814,7 +1828,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F15" s="27" t="n"/>
@@ -1823,7 +1837,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1838,7 +1852,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F16" s="27" t="n"/>
@@ -1847,7 +1861,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1862,7 +1876,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F17" s="27" t="n"/>
@@ -1871,7 +1885,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1886,7 +1900,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F18" s="27" t="n"/>
@@ -1895,7 +1909,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1910,7 +1924,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F19" s="27" t="n"/>
@@ -1919,22 +1933,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F20" s="27" t="n"/>
@@ -1943,7 +1957,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1967,7 +1981,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1982,7 +1996,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F22" s="27" t="n"/>
@@ -1991,7 +2005,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2006,7 +2020,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F23" s="27" t="n"/>
@@ -2015,7 +2029,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2030,7 +2044,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F24" s="27" t="n"/>
@@ -2039,7 +2053,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2054,7 +2068,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F25" s="27" t="n"/>
@@ -2063,7 +2077,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2087,7 +2101,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2102,7 +2116,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F27" s="27" t="n"/>
@@ -2111,7 +2125,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2126,11 +2140,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
       <c r="G28" s="27" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-21 15:12 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-21 22:25 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-21 22:25 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-22 00:45 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1081,7 +1081,9 @@
         <v/>
       </c>
       <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
+      <c r="F8" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="G8" s="22" t="n"/>
       <c r="H8" s="22" t="n"/>
       <c r="I8" s="22" t="n"/>
@@ -1168,7 +1170,9 @@
         <f>SUM(E10:AE10)</f>
         <v/>
       </c>
-      <c r="E10" s="22" t="n"/>
+      <c r="E10" s="22" t="n">
+        <v>5345</v>
+      </c>
       <c r="F10" s="22" t="n"/>
       <c r="G10" s="22" t="n"/>
       <c r="H10" s="22" t="n"/>
@@ -1212,7 +1216,9 @@
         <f>SUM(E11:AE11)</f>
         <v/>
       </c>
-      <c r="E11" s="22" t="n"/>
+      <c r="E11" s="22" t="n">
+        <v>12641</v>
+      </c>
       <c r="F11" s="22" t="n"/>
       <c r="G11" s="22" t="n"/>
       <c r="H11" s="22" t="n"/>
@@ -1381,7 +1387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1439,17 +1445,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1463,36 +1469,34 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F3" s="27" t="n"/>
@@ -1501,22 +1505,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F4" s="27" t="n"/>
@@ -1525,17 +1529,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1549,7 +1553,7 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>10383</v>
+        <v>12641</v>
       </c>
       <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
@@ -1561,22 +1565,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F6" s="27" t="n"/>
@@ -1585,137 +1589,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G7" s="27" t="n"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n"/>
       <c r="G8" s="27" t="n"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n"/>
       <c r="G9" s="27" t="n"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1729,17 +1735,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1753,17 +1759,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1777,7 +1783,7 @@
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>6310</v>
+        <v>10383</v>
       </c>
       <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
@@ -1789,22 +1795,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F14" s="27" t="n"/>
@@ -1813,17 +1819,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1837,70 +1843,94 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G16" s="27" t="n"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G17" s="27" t="n"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F18" s="27" t="n"/>
@@ -1909,22 +1939,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F19" s="27" t="n"/>
@@ -1933,17 +1963,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1957,46 +1987,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G21" s="27" t="n"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F22" s="27" t="n"/>
@@ -2005,22 +2047,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F23" s="27" t="n"/>
@@ -2029,22 +2071,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F24" s="27" t="n"/>
@@ -2053,22 +2095,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F25" s="27" t="n"/>
@@ -2077,22 +2119,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F26" s="27" t="n"/>
@@ -2101,22 +2143,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F27" s="27" t="n"/>
@@ -2125,22 +2167,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2149,7 +2191,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2164,11 +2206,203 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F29" s="27" t="n"/>
       <c r="G29" s="27" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:41:34</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="27" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:41:28</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n"/>
+      <c r="G31" s="27" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:27:02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="27" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:22:11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="27" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:20:27</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="27" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n"/>
+      <c r="G35" s="27" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-22 00:45 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-22 03:44 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-22 03:44 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-22 05:24 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1173,7 +1173,9 @@
       <c r="E10" s="22" t="n">
         <v>5345</v>
       </c>
-      <c r="F10" s="22" t="n"/>
+      <c r="F10" s="22" t="n">
+        <v>4842</v>
+      </c>
       <c r="G10" s="22" t="n"/>
       <c r="H10" s="22" t="n"/>
       <c r="I10" s="22" t="n"/>
@@ -1387,7 +1389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1445,17 +1447,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1469,34 +1471,34 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>0</v>
+        <v>4842</v>
       </c>
       <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F3" s="27" t="n"/>
@@ -1505,67 +1507,67 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G4" s="27" t="n"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="n"/>
       <c r="G5" s="27" t="n"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1580,7 +1582,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F6" s="27" t="n"/>
@@ -1589,17 +1591,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1613,7 +1615,7 @@
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>5345</v>
+        <v>12641</v>
       </c>
       <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
@@ -1625,22 +1627,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F8" s="27" t="n"/>
@@ -1649,7 +1651,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1664,69 +1666,67 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G9" s="27" t="n"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F11" s="27" t="n"/>
@@ -1735,82 +1735,84 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n"/>
       <c r="G13" s="27" t="n"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F14" s="27" t="n"/>
@@ -1819,7 +1821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1834,136 +1836,148 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G15" s="27" t="n"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n"/>
       <c r="G16" s="27" t="n"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n"/>
       <c r="G17" s="27" t="n"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G18" s="27" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G19" s="27" t="n"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1978,7 +1992,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F20" s="27" t="n"/>
@@ -1987,53 +2001,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n"/>
       <c r="G21" s="27" t="n"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2047,46 +2049,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G23" s="27" t="n"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F24" s="27" t="n"/>
@@ -2095,7 +2109,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2119,7 +2133,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2143,7 +2157,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2158,7 +2172,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F27" s="27" t="n"/>
@@ -2167,7 +2181,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2182,7 +2196,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2191,22 +2205,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F29" s="27" t="n"/>
@@ -2215,22 +2229,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F30" s="27" t="n"/>
@@ -2239,7 +2253,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2254,7 +2268,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F31" s="27" t="n"/>
@@ -2263,7 +2277,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2287,7 +2301,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2311,7 +2325,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2335,7 +2349,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2350,7 +2364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F35" s="27" t="n"/>
@@ -2359,7 +2373,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2374,7 +2388,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F36" s="27" t="n"/>
@@ -2383,7 +2397,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2398,11 +2412,59 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F37" s="27" t="n"/>
       <c r="G37" s="27" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
+      <c r="G38" s="27" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-22 05:24 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-22 10:29 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1447,43 +1447,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n"/>
       <c r="G2" s="27" t="n"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1498,7 +1486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F3" s="27" t="n"/>
@@ -1507,17 +1495,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1531,34 +1519,34 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>0</v>
+        <v>4842</v>
       </c>
       <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F5" s="27" t="n"/>
@@ -1567,67 +1555,67 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" s="27" t="n"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n"/>
       <c r="G7" s="27" t="n"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1642,7 +1630,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F8" s="27" t="n"/>
@@ -1651,17 +1639,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1675,7 +1663,7 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>5345</v>
+        <v>12641</v>
       </c>
       <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
@@ -1687,22 +1675,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F10" s="27" t="n"/>
@@ -1711,7 +1699,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1726,69 +1714,67 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G11" s="27" t="n"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F13" s="27" t="n"/>
@@ -1797,82 +1783,84 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n"/>
       <c r="G15" s="27" t="n"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F16" s="27" t="n"/>
@@ -1881,7 +1869,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1896,136 +1884,148 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G17" s="27" t="n"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n"/>
       <c r="G18" s="27" t="n"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n"/>
       <c r="G19" s="27" t="n"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G20" s="27" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G21" s="27" t="n"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F22" s="27" t="n"/>
@@ -2049,53 +2049,41 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n"/>
       <c r="G23" s="27" t="n"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2109,46 +2097,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G25" s="27" t="n"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F26" s="27" t="n"/>
@@ -2157,7 +2157,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2205,7 +2205,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F29" s="27" t="n"/>
@@ -2229,7 +2229,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F30" s="27" t="n"/>
@@ -2253,22 +2253,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F31" s="27" t="n"/>
@@ -2277,22 +2277,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2301,7 +2301,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F33" s="27" t="n"/>
@@ -2325,7 +2325,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2349,7 +2349,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2373,7 +2373,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F37" s="27" t="n"/>
@@ -2421,7 +2421,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F38" s="27" t="n"/>
@@ -2445,7 +2445,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2460,11 +2460,59 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
       <c r="G39" s="27" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="27" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-22 10:29 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-22 10:52 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -992,9 +992,11 @@
         <v>9060</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G6" s="22" t="n"/>
+        <v>18461</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <v>1100</v>
+      </c>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="22" t="n"/>
@@ -1389,7 +1391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1447,7 +1449,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1462,16 +1464,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G2" s="27" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1486,52 +1500,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n"/>
-      <c r="G3" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n"/>
       <c r="G4" s="27" t="n"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1546,7 +1562,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F5" s="27" t="n"/>
@@ -1555,17 +1571,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1579,34 +1595,34 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>0</v>
+        <v>4842</v>
       </c>
       <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F7" s="27" t="n"/>
@@ -1615,67 +1631,67 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G8" s="27" t="n"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n"/>
       <c r="G9" s="27" t="n"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1690,7 +1706,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F10" s="27" t="n"/>
@@ -1699,17 +1715,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1723,7 +1739,7 @@
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>5345</v>
+        <v>12641</v>
       </c>
       <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
@@ -1735,22 +1751,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F12" s="27" t="n"/>
@@ -1759,7 +1775,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1774,69 +1790,67 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G13" s="27" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F15" s="27" t="n"/>
@@ -1845,82 +1859,84 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n"/>
       <c r="G17" s="27" t="n"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F18" s="27" t="n"/>
@@ -1929,7 +1945,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1944,136 +1960,148 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G19" s="27" t="n"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n"/>
       <c r="G20" s="27" t="n"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n"/>
       <c r="G21" s="27" t="n"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G22" s="27" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G23" s="27" t="n"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2088,7 +2116,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F24" s="27" t="n"/>
@@ -2097,53 +2125,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n"/>
       <c r="G25" s="27" t="n"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2157,46 +2173,58 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G27" s="27" t="n"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2205,7 +2233,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2229,7 +2257,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2253,7 +2281,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2268,7 +2296,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F31" s="27" t="n"/>
@@ -2277,7 +2305,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2292,7 +2320,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2301,22 +2329,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F33" s="27" t="n"/>
@@ -2325,22 +2353,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F34" s="27" t="n"/>
@@ -2349,7 +2377,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2364,7 +2392,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F35" s="27" t="n"/>
@@ -2373,7 +2401,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2397,7 +2425,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2421,7 +2449,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2445,7 +2473,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2460,7 +2488,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2469,7 +2497,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2484,7 +2512,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F40" s="27" t="n"/>
@@ -2493,7 +2521,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2508,11 +2536,59 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F41" s="27" t="n"/>
       <c r="G41" s="27" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n"/>
+      <c r="G42" s="27" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-22 10:52 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-22 15:22 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1449,81 +1449,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n"/>
       <c r="G2" s="27" t="n"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n"/>
+      <c r="G3" s="27" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1547,7 +1521,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1562,26 +1536,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F5" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G5" s="27" t="n"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1595,9 +1581,11 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>4842</v>
-      </c>
-      <c r="G6" s="27" t="n"/>
+        <v>18461</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>1985</v>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>app</t>
@@ -1607,7 +1595,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1631,82 +1619,82 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n"/>
       <c r="G8" s="27" t="n"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G9" s="27" t="n"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F10" s="27" t="n"/>
@@ -1715,17 +1703,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1735,38 +1723,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>12641</v>
+        <v>0</v>
       </c>
       <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F12" s="27" t="n"/>
@@ -1775,77 +1763,77 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n"/>
       <c r="G13" s="27" t="n"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G14" s="27" t="n"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1859,17 +1847,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1879,15 +1867,13 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>100</v>
-      </c>
+        <v>5345</v>
+      </c>
+      <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>app</t>
@@ -1897,17 +1883,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1921,17 +1907,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1945,17 +1931,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1965,13 +1951,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>10383</v>
-      </c>
-      <c r="G19" s="27" t="n"/>
+        <v>1985</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>app</t>
@@ -1981,22 +1969,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F20" s="27" t="n"/>
@@ -2005,17 +1993,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2029,17 +2017,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2049,11 +2037,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>100</v>
+        <v>10383</v>
       </c>
       <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
@@ -2065,58 +2053,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n"/>
       <c r="G23" s="27" t="n"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F24" s="27" t="n"/>
@@ -2125,106 +2101,118 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G25" s="27" t="n"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G26" s="27" t="n"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n"/>
       <c r="G27" s="27" t="n"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2233,17 +2221,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2257,41 +2245,53 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G30" s="27" t="n"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2329,7 +2329,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F33" s="27" t="n"/>
@@ -2353,7 +2353,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2377,22 +2377,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F35" s="27" t="n"/>
@@ -2401,22 +2401,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F36" s="27" t="n"/>
@@ -2425,22 +2425,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F37" s="27" t="n"/>
@@ -2449,7 +2449,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2473,7 +2473,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2497,7 +2497,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F40" s="27" t="n"/>
@@ -2521,7 +2521,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2545,7 +2545,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2569,7 +2569,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2584,11 +2584,83 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F43" s="27" t="n"/>
       <c r="G43" s="27" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="27" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n"/>
+      <c r="G45" s="27" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n"/>
+      <c r="G46" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-22 15:22 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-22 19:17 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1086,7 +1086,9 @@
       <c r="F8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="22" t="n"/>
+      <c r="G8" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="H8" s="22" t="n"/>
       <c r="I8" s="22" t="n"/>
       <c r="J8" s="22" t="n"/>
@@ -1223,7 +1225,9 @@
       <c r="E11" s="22" t="n">
         <v>12641</v>
       </c>
-      <c r="F11" s="22" t="n"/>
+      <c r="F11" s="22" t="n">
+        <v>10808</v>
+      </c>
       <c r="G11" s="22" t="n"/>
       <c r="H11" s="22" t="n"/>
       <c r="I11" s="22" t="n"/>
@@ -1391,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1449,7 +1453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1473,7 +1477,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1497,41 +1501,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G4" s="27" t="n"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1545,72 +1561,58 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="27" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F7" s="27" t="n"/>
@@ -1619,7 +1621,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1634,7 +1636,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F8" s="27" t="n"/>
@@ -1643,17 +1645,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1663,11 +1665,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>4842</v>
+        <v>1100</v>
       </c>
       <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
@@ -1679,7 +1681,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1694,67 +1696,69 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n"/>
       <c r="G11" s="27" t="n"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F12" s="27" t="n"/>
@@ -1763,137 +1767,137 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G13" s="27" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n"/>
       <c r="G14" s="27" t="n"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G15" s="27" t="n"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n"/>
       <c r="G16" s="27" t="n"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1907,108 +1911,118 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G18" s="27" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="27" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G20" s="27" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F21" s="27" t="n"/>
@@ -2017,82 +2031,84 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n"/>
       <c r="G22" s="27" t="n"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G23" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F24" s="27" t="n"/>
@@ -2101,53 +2117,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n"/>
       <c r="G25" s="27" t="n"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2161,7 +2165,7 @@
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>9060</v>
+        <v>10383</v>
       </c>
       <c r="G26" s="27" t="n"/>
       <c r="H26" t="inlineStr">
@@ -2173,17 +2177,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2197,22 +2201,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2221,41 +2225,53 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G29" s="27" t="n"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2269,7 +2285,7 @@
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>6310</v>
+        <v>9060</v>
       </c>
       <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
@@ -2281,22 +2297,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F31" s="27" t="n"/>
@@ -2305,22 +2321,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2329,22 +2345,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F33" s="27" t="n"/>
@@ -2353,46 +2369,58 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G34" s="27" t="n"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F35" s="27" t="n"/>
@@ -2401,7 +2429,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2416,7 +2444,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F36" s="27" t="n"/>
@@ -2425,7 +2453,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2440,7 +2468,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F37" s="27" t="n"/>
@@ -2449,22 +2477,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F38" s="27" t="n"/>
@@ -2473,22 +2501,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2497,22 +2525,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F40" s="27" t="n"/>
@@ -2521,22 +2549,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F41" s="27" t="n"/>
@@ -2545,7 +2573,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2560,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2569,7 +2597,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2593,7 +2621,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2608,7 +2636,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F44" s="27" t="n"/>
@@ -2617,7 +2645,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2632,7 +2660,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F45" s="27" t="n"/>
@@ -2641,7 +2669,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2656,11 +2684,107 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F46" s="27" t="n"/>
       <c r="G46" s="27" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:20:27</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="n"/>
+      <c r="G47" s="27" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n"/>
+      <c r="G48" s="27" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="n"/>
+      <c r="G49" s="27" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="n"/>
+      <c r="G50" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-22 19:17 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-23 05:24 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1180,7 +1180,9 @@
       <c r="F10" s="22" t="n">
         <v>4842</v>
       </c>
-      <c r="G10" s="22" t="n"/>
+      <c r="G10" s="22" t="n">
+        <v>9097</v>
+      </c>
       <c r="H10" s="22" t="n"/>
       <c r="I10" s="22" t="n"/>
       <c r="J10" s="22" t="n"/>
@@ -1395,7 +1397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1453,31 +1455,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G2" s="27" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1492,7 +1506,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F3" s="27" t="n"/>
@@ -1501,53 +1515,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n"/>
       <c r="G4" s="27" t="n"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1557,47 +1559,59 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" s="27" t="n"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1612,7 +1626,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F7" s="27" t="n"/>
@@ -1621,22 +1635,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F8" s="27" t="n"/>
@@ -1645,7 +1659,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1660,28 +1674,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n"/>
       <c r="G9" s="27" t="n"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1701,15 +1703,13 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G10" s="27" t="n"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>app</t>
@@ -1719,7 +1719,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1734,16 +1734,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1758,7 +1772,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F12" s="27" t="n"/>
@@ -1767,103 +1781,91 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n"/>
       <c r="G13" s="27" t="n"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G14" s="27" t="n"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n"/>
       <c r="G15" s="27" t="n"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1878,31 +1880,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G16" s="27" t="n"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F17" s="27" t="n"/>
@@ -1911,7 +1925,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1926,28 +1940,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n"/>
       <c r="G18" s="27" t="n"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1962,52 +1964,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G19" s="27" t="n"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n"/>
       <c r="G20" s="27" t="n"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2022,16 +2024,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G21" s="27" t="n"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2046,7 +2060,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F22" s="27" t="n"/>
@@ -2055,69 +2069,69 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G23" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="27" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2132,7 +2146,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F25" s="27" t="n"/>
@@ -2141,43 +2155,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n"/>
       <c r="G26" s="27" t="n"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2192,16 +2194,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G27" s="27" t="n"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2216,7 +2230,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2225,43 +2239,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n"/>
       <c r="G29" s="27" t="n"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2281,11 +2283,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
@@ -2297,31 +2299,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G31" s="27" t="n"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2336,7 +2350,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2345,7 +2359,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2360,7 +2374,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F33" s="27" t="n"/>
@@ -2369,43 +2383,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
       <c r="G34" s="27" t="n"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2420,26 +2422,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G35" s="27" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2453,7 +2467,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2468,7 +2482,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F37" s="27" t="n"/>
@@ -2477,7 +2491,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2492,7 +2506,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F38" s="27" t="n"/>
@@ -2501,7 +2515,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2516,7 +2530,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2525,7 +2539,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2540,7 +2554,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F40" s="27" t="n"/>
@@ -2549,7 +2563,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2564,7 +2578,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F41" s="27" t="n"/>
@@ -2573,22 +2587,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2597,7 +2611,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2621,7 +2635,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2636,7 +2650,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F44" s="27" t="n"/>
@@ -2645,7 +2659,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2660,7 +2674,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F45" s="27" t="n"/>
@@ -2669,7 +2683,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2684,7 +2698,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F46" s="27" t="n"/>
@@ -2693,7 +2707,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2708,7 +2722,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F47" s="27" t="n"/>
@@ -2717,7 +2731,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2741,7 +2755,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2756,7 +2770,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F49" s="27" t="n"/>
@@ -2765,7 +2779,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2780,11 +2794,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F50" s="27" t="n"/>
       <c r="G50" s="27" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n"/>
+      <c r="G51" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-23 05:24 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-23 10:15 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -995,9 +995,11 @@
         <v>18461</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H6" s="22" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>387</v>
+      </c>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="22" t="n"/>
       <c r="K6" s="23" t="n"/>
@@ -1397,7 +1399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1455,101 +1457,115 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n">
-        <v>9097</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n"/>
       <c r="G2" s="27" t="n"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>387</v>
+      </c>
       <c r="G3" s="27" t="n"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>9720</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1559,11 +1575,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>10808</v>
+        <v>9097</v>
       </c>
       <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
@@ -1575,43 +1591,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n"/>
       <c r="G6" s="27" t="n"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1626,7 +1630,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F7" s="27" t="n"/>
@@ -1635,129 +1639,127 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G8" s="27" t="n"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G9" s="27" t="n"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n"/>
       <c r="G10" s="27" t="n"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1781,7 +1783,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1796,26 +1798,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G13" s="27" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1829,9 +1843,11 @@
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>4842</v>
-      </c>
-      <c r="G14" s="27" t="n"/>
+        <v>18461</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>1985</v>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>app</t>
@@ -1841,7 +1857,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1865,82 +1881,82 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n"/>
       <c r="G16" s="27" t="n"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G17" s="27" t="n"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F18" s="27" t="n"/>
@@ -1949,17 +1965,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1969,38 +1985,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>12641</v>
+        <v>0</v>
       </c>
       <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F20" s="27" t="n"/>
@@ -2009,77 +2025,77 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n"/>
       <c r="G21" s="27" t="n"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G22" s="27" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2093,17 +2109,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2113,15 +2129,13 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G24" s="27" t="n">
-        <v>100</v>
-      </c>
+        <v>5345</v>
+      </c>
+      <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>app</t>
@@ -2131,17 +2145,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2155,17 +2169,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2179,17 +2193,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2199,13 +2213,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>10383</v>
-      </c>
-      <c r="G27" s="27" t="n"/>
+        <v>1985</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>app</t>
@@ -2215,22 +2231,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2239,17 +2255,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2263,17 +2279,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2283,11 +2299,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>100</v>
+        <v>10383</v>
       </c>
       <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
@@ -2299,58 +2315,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n"/>
       <c r="G31" s="27" t="n"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2359,106 +2363,118 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G33" s="27" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G34" s="27" t="n"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n"/>
       <c r="G35" s="27" t="n"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F36" s="27" t="n"/>
@@ -2467,17 +2483,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2491,41 +2507,53 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G38" s="27" t="n"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2539,7 +2567,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2554,7 +2582,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F40" s="27" t="n"/>
@@ -2563,7 +2591,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2578,7 +2606,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F41" s="27" t="n"/>
@@ -2587,7 +2615,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2611,22 +2639,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F43" s="27" t="n"/>
@@ -2635,22 +2663,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F44" s="27" t="n"/>
@@ -2659,22 +2687,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F45" s="27" t="n"/>
@@ -2683,7 +2711,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2707,7 +2735,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2722,7 +2750,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F47" s="27" t="n"/>
@@ -2731,7 +2759,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2746,7 +2774,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F48" s="27" t="n"/>
@@ -2755,7 +2783,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2779,7 +2807,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2794,7 +2822,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F50" s="27" t="n"/>
@@ -2803,7 +2831,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2818,11 +2846,83 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n"/>
+      <c r="G52" s="27" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="n"/>
+      <c r="G53" s="27" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n"/>
+      <c r="G54" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-23 10:15 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-23 15:06 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -998,7 +998,7 @@
         <v>9720</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>387</v>
+        <v>831</v>
       </c>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="22" t="n"/>
@@ -1399,7 +1399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1457,7 +1457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1472,16 +1472,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n"/>
-      <c r="G2" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G2" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1496,28 +1510,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n"/>
       <c r="G3" s="27" t="n"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1537,15 +1539,13 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>app</t>
@@ -1555,17 +1555,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1579,9 +1579,11 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G5" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>app</t>
@@ -1591,31 +1593,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G6" s="27" t="n"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1630,7 +1644,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F7" s="27" t="n"/>
@@ -1639,53 +1653,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n"/>
       <c r="G8" s="27" t="n"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1695,47 +1697,59 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G10" s="27" t="n"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1750,7 +1764,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F11" s="27" t="n"/>
@@ -1759,22 +1773,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F12" s="27" t="n"/>
@@ -1783,7 +1797,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1798,28 +1812,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n"/>
       <c r="G13" s="27" t="n"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1839,15 +1841,13 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>app</t>
@@ -1857,7 +1857,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1872,16 +1872,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1896,7 +1910,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F16" s="27" t="n"/>
@@ -1905,103 +1919,91 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n"/>
       <c r="G17" s="27" t="n"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G18" s="27" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n"/>
       <c r="G19" s="27" t="n"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2016,31 +2018,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G20" s="27" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F21" s="27" t="n"/>
@@ -2049,7 +2063,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2064,28 +2078,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n"/>
       <c r="G22" s="27" t="n"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2100,52 +2102,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G23" s="27" t="n"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n"/>
       <c r="G24" s="27" t="n"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2160,16 +2162,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G25" s="27" t="n"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2184,7 +2198,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F26" s="27" t="n"/>
@@ -2193,69 +2207,69 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G27" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n"/>
+      <c r="G27" s="27" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G28" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2270,7 +2284,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F29" s="27" t="n"/>
@@ -2279,43 +2293,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n"/>
       <c r="G30" s="27" t="n"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2330,16 +2332,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G31" s="27" t="n"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,7 +2368,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2363,43 +2377,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n"/>
       <c r="G33" s="27" t="n"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2419,11 +2421,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F34" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G34" s="27" t="n"/>
       <c r="H34" t="inlineStr">
@@ -2435,31 +2437,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G35" s="27" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2474,7 +2488,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F36" s="27" t="n"/>
@@ -2483,7 +2497,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2498,7 +2512,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F37" s="27" t="n"/>
@@ -2507,43 +2521,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
       <c r="G38" s="27" t="n"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2558,26 +2560,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G39" s="27" t="n"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2591,7 +2605,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2606,7 +2620,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F41" s="27" t="n"/>
@@ -2615,7 +2629,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2630,7 +2644,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2639,7 +2653,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2654,7 +2668,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F43" s="27" t="n"/>
@@ -2663,7 +2677,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2678,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F44" s="27" t="n"/>
@@ -2687,7 +2701,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2702,7 +2716,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F45" s="27" t="n"/>
@@ -2711,22 +2725,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F46" s="27" t="n"/>
@@ -2735,7 +2749,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2759,7 +2773,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2774,7 +2788,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F48" s="27" t="n"/>
@@ -2783,7 +2797,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2798,7 +2812,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F49" s="27" t="n"/>
@@ -2807,7 +2821,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2822,7 +2836,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F50" s="27" t="n"/>
@@ -2831,7 +2845,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2846,7 +2860,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F51" s="27" t="n"/>
@@ -2855,7 +2869,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2879,7 +2893,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2894,7 +2908,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -2903,7 +2917,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2918,11 +2932,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F54" s="27" t="n"/>
       <c r="G54" s="27" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n"/>
+      <c r="G55" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-23 15:06 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-23 19:06 UTC by the Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -998,7 +998,7 @@
         <v>9720</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>831</v>
+        <v>2650</v>
       </c>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="22" t="n"/>
@@ -1091,7 +1091,9 @@
       <c r="G8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="22" t="n"/>
+      <c r="H8" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="I8" s="22" t="n"/>
       <c r="J8" s="22" t="n"/>
       <c r="K8" s="23" t="n"/>
@@ -1399,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1457,7 +1459,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1481,10 +1483,10 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G2" s="27" t="n">
         <v>831</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>387</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1495,31 +1497,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" s="27" t="n"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1543,9 +1557,11 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G4" s="27" t="n">
         <v>387</v>
       </c>
-      <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>app</t>
@@ -1555,7 +1571,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1570,40 +1586,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1613,11 +1615,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>9097</v>
+        <v>387</v>
       </c>
       <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
@@ -1629,190 +1631,216 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>9720</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G8" s="27" t="n"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n"/>
       <c r="G9" s="27" t="n"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n"/>
       <c r="G10" s="27" t="n"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G11" s="27" t="n"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G12" s="27" t="n"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F13" s="27" t="n"/>
@@ -1821,43 +1849,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n"/>
       <c r="G14" s="27" t="n"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1872,30 +1888,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1910,16 +1912,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G16" s="27" t="n"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1934,52 +1948,54 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n"/>
       <c r="G18" s="27" t="n"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1994,7 +2010,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F19" s="27" t="n"/>
@@ -2003,17 +2019,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2027,34 +2043,34 @@
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>0</v>
+        <v>4842</v>
       </c>
       <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F21" s="27" t="n"/>
@@ -2063,67 +2079,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G22" s="27" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n"/>
       <c r="G23" s="27" t="n"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2138,7 +2154,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F24" s="27" t="n"/>
@@ -2147,17 +2163,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2171,7 +2187,7 @@
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>5345</v>
+        <v>12641</v>
       </c>
       <c r="G25" s="27" t="n"/>
       <c r="H25" t="inlineStr">
@@ -2183,22 +2199,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F26" s="27" t="n"/>
@@ -2207,7 +2223,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2222,69 +2238,67 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G27" s="27" t="n"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="27" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F29" s="27" t="n"/>
@@ -2293,82 +2307,84 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n"/>
-      <c r="G30" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G30" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n"/>
       <c r="G31" s="27" t="n"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2377,7 +2393,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2392,136 +2408,148 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G33" s="27" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
       <c r="G34" s="27" t="n"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n"/>
       <c r="G35" s="27" t="n"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G36" s="27" t="n"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G37" s="27" t="n"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2536,7 +2564,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F38" s="27" t="n"/>
@@ -2545,53 +2573,41 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n"/>
       <c r="G39" s="27" t="n"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2605,46 +2621,58 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G41" s="27" t="n"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2653,7 +2681,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2677,7 +2705,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2701,7 +2729,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2716,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F45" s="27" t="n"/>
@@ -2725,7 +2753,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2740,7 +2768,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F46" s="27" t="n"/>
@@ -2749,22 +2777,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F47" s="27" t="n"/>
@@ -2773,22 +2801,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F48" s="27" t="n"/>
@@ -2797,7 +2825,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2812,7 +2840,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F49" s="27" t="n"/>
@@ -2821,7 +2849,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2845,7 +2873,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2869,7 +2897,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2893,7 +2921,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2908,7 +2936,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -2917,7 +2945,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2932,7 +2960,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F54" s="27" t="n"/>
@@ -2941,7 +2969,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2956,11 +2984,59 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
       <c r="G55" s="27" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n"/>
+      <c r="G56" s="27" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-23 19:06 UTC by the Team 8 app</t>
+          <t>Updated 2026-10-23 19:56 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1084,15 +1084,17 @@
         <f>SUM(E8:AE8)</f>
         <v/>
       </c>
-      <c r="E8" s="22" t="n"/>
+      <c r="E8" s="22" t="n">
+        <v>4933</v>
+      </c>
       <c r="F8" s="22" t="n">
-        <v>0</v>
+        <v>7567</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>0</v>
+        <v>4189</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>0</v>
+        <v>3685</v>
       </c>
       <c r="I8" s="22" t="n"/>
       <c r="J8" s="22" t="n"/>
@@ -1401,7 +1403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1459,17 +1461,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1479,15 +1481,13 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>831</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>app</t>
@@ -1497,7 +1497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1517,33 +1517,35 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F3" s="27" t="n">
+        <v>7567</v>
+      </c>
+      <c r="G3" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="27" t="n"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1553,14 +1555,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>831</v>
+        <v>4189</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1571,31 +1573,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1619,9 +1635,11 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>387</v>
-      </c>
-      <c r="G6" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>app</t>
@@ -1631,17 +1649,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1651,35 +1669,33 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1689,13 +1705,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G8" s="27" t="n"/>
+        <v>831</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>387</v>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>app</t>
@@ -1705,22 +1723,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F9" s="27" t="n"/>
@@ -1729,41 +1747,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>387</v>
+      </c>
       <c r="G10" s="27" t="n"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1773,13 +1803,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>10808</v>
-      </c>
-      <c r="G11" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>app</t>
@@ -1789,17 +1821,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1813,19 +1845,19 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>0</v>
+        <v>9097</v>
       </c>
       <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1849,7 +1881,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1873,41 +1905,53 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G15" s="27" t="n"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1921,72 +1965,58 @@
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="27" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F18" s="27" t="n"/>
@@ -1995,7 +2025,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2010,7 +2040,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F19" s="27" t="n"/>
@@ -2019,17 +2049,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2039,11 +2069,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>4842</v>
+        <v>1100</v>
       </c>
       <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
@@ -2055,7 +2085,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2070,67 +2100,69 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n"/>
       <c r="G22" s="27" t="n"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F23" s="27" t="n"/>
@@ -2139,137 +2171,137 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G24" s="27" t="n"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n"/>
       <c r="G25" s="27" t="n"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G26" s="27" t="n"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n"/>
       <c r="G27" s="27" t="n"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2283,108 +2315,118 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G29" s="27" t="n"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G30" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="27" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G31" s="27" t="n"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2393,82 +2435,84 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n"/>
       <c r="G33" s="27" t="n"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F35" s="27" t="n"/>
@@ -2477,53 +2521,41 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
       <c r="G36" s="27" t="n"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2537,7 +2569,7 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>9060</v>
+        <v>10383</v>
       </c>
       <c r="G37" s="27" t="n"/>
       <c r="H37" t="inlineStr">
@@ -2549,17 +2581,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2573,22 +2605,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2597,41 +2629,53 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G40" s="27" t="n"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2645,7 +2689,7 @@
         </is>
       </c>
       <c r="F41" s="27" t="n">
-        <v>6310</v>
+        <v>9060</v>
       </c>
       <c r="G41" s="27" t="n"/>
       <c r="H41" t="inlineStr">
@@ -2657,22 +2701,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2681,22 +2725,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F43" s="27" t="n"/>
@@ -2705,22 +2749,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F44" s="27" t="n"/>
@@ -2729,46 +2773,58 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G45" s="27" t="n"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F46" s="27" t="n"/>
@@ -2777,7 +2833,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2792,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F47" s="27" t="n"/>
@@ -2801,7 +2857,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2816,7 +2872,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F48" s="27" t="n"/>
@@ -2825,22 +2881,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F49" s="27" t="n"/>
@@ -2849,22 +2905,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F50" s="27" t="n"/>
@@ -2873,22 +2929,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F51" s="27" t="n"/>
@@ -2897,22 +2953,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F52" s="27" t="n"/>
@@ -2921,7 +2977,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2936,7 +2992,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -2945,7 +3001,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2969,7 +3025,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2984,7 +3040,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
@@ -2993,7 +3049,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3008,7 +3064,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F56" s="27" t="n"/>
@@ -3017,7 +3073,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3032,11 +3088,107 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
       <c r="G57" s="27" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:20:27</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="n"/>
+      <c r="G58" s="27" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n"/>
+      <c r="G59" s="27" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n"/>
+      <c r="G60" s="27" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="n"/>
+      <c r="G61" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-23 19:56 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-23 22:03 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -998,7 +998,7 @@
         <v>9720</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>2650</v>
+        <v>2680</v>
       </c>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="22" t="n"/>
@@ -1403,7 +1403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1461,17 +1461,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1481,13 +1481,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G2" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G2" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>app</t>
@@ -1497,7 +1499,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1517,15 +1519,13 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G3" s="27" t="n"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>app</t>
@@ -1535,7 +1535,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1555,11 +1555,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0</v>
@@ -1573,7 +1573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1593,35 +1593,35 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G5" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1635,31 +1635,31 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1673,29 +1673,31 @@
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1709,21 +1711,19 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1738,16 +1738,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1762,28 +1776,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n"/>
       <c r="G10" s="27" t="n"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1803,15 +1805,13 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>app</t>
@@ -1821,17 +1821,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1845,9 +1845,11 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G12" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1857,31 +1859,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G13" s="27" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1896,7 +1910,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F14" s="27" t="n"/>
@@ -1905,53 +1919,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n"/>
       <c r="G15" s="27" t="n"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1961,47 +1963,59 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G17" s="27" t="n"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2016,7 +2030,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F18" s="27" t="n"/>
@@ -2025,22 +2039,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F19" s="27" t="n"/>
@@ -2049,7 +2063,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,28 +2078,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n"/>
       <c r="G20" s="27" t="n"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2105,15 +2107,13 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G21" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>app</t>
@@ -2123,7 +2123,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2138,16 +2138,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2162,7 +2176,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F23" s="27" t="n"/>
@@ -2171,103 +2185,91 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n"/>
       <c r="G24" s="27" t="n"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G25" s="27" t="n"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n"/>
       <c r="G26" s="27" t="n"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2282,31 +2284,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G27" s="27" t="n"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2315,7 +2329,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2330,28 +2344,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n"/>
       <c r="G29" s="27" t="n"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2366,52 +2368,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G30" s="27" t="n"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n"/>
       <c r="G31" s="27" t="n"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2426,16 +2428,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G32" s="27" t="n"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2450,7 +2464,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F33" s="27" t="n"/>
@@ -2459,69 +2473,69 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G34" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="27" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n"/>
-      <c r="G35" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2536,7 +2550,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F36" s="27" t="n"/>
@@ -2545,43 +2559,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n"/>
       <c r="G37" s="27" t="n"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2596,16 +2598,28 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G38" s="27" t="n"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2620,7 +2634,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2629,43 +2643,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n"/>
       <c r="G40" s="27" t="n"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2685,11 +2687,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F41" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G41" s="27" t="n"/>
       <c r="H41" t="inlineStr">
@@ -2701,31 +2703,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G42" s="27" t="n"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2740,7 +2754,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F43" s="27" t="n"/>
@@ -2749,7 +2763,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2764,7 +2778,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F44" s="27" t="n"/>
@@ -2773,43 +2787,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n"/>
       <c r="G45" s="27" t="n"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2824,26 +2826,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G46" s="27" t="n"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2857,7 +2871,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2872,7 +2886,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F48" s="27" t="n"/>
@@ -2881,7 +2895,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2896,7 +2910,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F49" s="27" t="n"/>
@@ -2905,7 +2919,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2920,7 +2934,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F50" s="27" t="n"/>
@@ -2929,7 +2943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2944,7 +2958,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F51" s="27" t="n"/>
@@ -2953,7 +2967,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2968,7 +2982,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F52" s="27" t="n"/>
@@ -2977,22 +2991,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3001,7 +3015,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3025,7 +3039,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3040,7 +3054,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
@@ -3049,7 +3063,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3064,7 +3078,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F56" s="27" t="n"/>
@@ -3073,7 +3087,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3088,7 +3102,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3097,7 +3111,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3112,7 +3126,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3121,7 +3135,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3145,7 +3159,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3160,7 +3174,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F60" s="27" t="n"/>
@@ -3169,7 +3183,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3184,11 +3198,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
       <c r="G61" s="27" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="n"/>
+      <c r="G62" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-23 22:03 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-24 04:52 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -998,7 +998,7 @@
         <v>9720</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>2680</v>
+        <v>8981</v>
       </c>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="22" t="n"/>
@@ -1403,7 +1403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1461,7 +1461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G2" s="27" t="n">
         <v>2680</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>2650</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1499,53 +1499,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n">
-        <v>4933</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n"/>
       <c r="G3" s="27" t="n"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1555,14 +1543,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>7567</v>
+        <v>2680</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>0</v>
+        <v>2650</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1573,7 +1561,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1593,15 +1581,13 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>4189</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>app</t>
@@ -1611,7 +1597,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1631,35 +1617,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>3685</v>
+        <v>7567</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1669,14 +1655,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>2650</v>
+        <v>4189</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1687,7 +1673,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1711,9 +1697,11 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G8" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>shortcut</t>
@@ -1723,7 +1711,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1747,10 +1735,10 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G9" s="27" t="n">
         <v>831</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>387</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1761,31 +1749,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G10" s="27" t="n"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1809,9 +1809,11 @@
         </is>
       </c>
       <c r="F11" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G11" s="27" t="n">
         <v>387</v>
       </c>
-      <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>app</t>
@@ -1821,7 +1823,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1836,40 +1838,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1879,11 +1867,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>9097</v>
+        <v>387</v>
       </c>
       <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
@@ -1895,190 +1883,216 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>9720</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G15" s="27" t="n"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n"/>
       <c r="G16" s="27" t="n"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n"/>
       <c r="G17" s="27" t="n"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G18" s="27" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G19" s="27" t="n"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F20" s="27" t="n"/>
@@ -2087,43 +2101,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n"/>
       <c r="G21" s="27" t="n"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2138,30 +2140,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G22" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="27" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2176,16 +2164,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G23" s="27" t="n"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2200,52 +2200,54 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n"/>
       <c r="G25" s="27" t="n"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2260,7 +2262,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F26" s="27" t="n"/>
@@ -2269,17 +2271,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2293,34 +2295,34 @@
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>0</v>
+        <v>4842</v>
       </c>
       <c r="G27" s="27" t="n"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2329,67 +2331,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G29" s="27" t="n"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n"/>
       <c r="G30" s="27" t="n"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2404,7 +2406,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F31" s="27" t="n"/>
@@ -2413,17 +2415,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2437,7 +2439,7 @@
         </is>
       </c>
       <c r="F32" s="27" t="n">
-        <v>5345</v>
+        <v>12641</v>
       </c>
       <c r="G32" s="27" t="n"/>
       <c r="H32" t="inlineStr">
@@ -2449,22 +2451,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F33" s="27" t="n"/>
@@ -2473,7 +2475,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2488,69 +2490,67 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G34" s="27" t="n"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G35" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n"/>
+      <c r="G35" s="27" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F36" s="27" t="n"/>
@@ -2559,82 +2559,84 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
       <c r="G38" s="27" t="n"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2643,7 +2645,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2658,136 +2660,148 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G40" s="27" t="n"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n"/>
       <c r="G41" s="27" t="n"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n"/>
       <c r="G42" s="27" t="n"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G43" s="27" t="n"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G44" s="27" t="n"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2802,7 +2816,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F45" s="27" t="n"/>
@@ -2811,53 +2825,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n"/>
       <c r="G46" s="27" t="n"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2871,46 +2873,58 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G48" s="27" t="n"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F49" s="27" t="n"/>
@@ -2919,7 +2933,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2943,7 +2957,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2967,7 +2981,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2982,7 +2996,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F52" s="27" t="n"/>
@@ -2991,7 +3005,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3006,7 +3020,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3015,22 +3029,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F54" s="27" t="n"/>
@@ -3039,22 +3053,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
@@ -3063,7 +3077,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3078,7 +3092,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F56" s="27" t="n"/>
@@ -3087,7 +3101,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3111,7 +3125,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3135,7 +3149,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3159,7 +3173,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3174,7 +3188,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F60" s="27" t="n"/>
@@ -3183,7 +3197,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3198,7 +3212,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3207,7 +3221,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3222,11 +3236,59 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F62" s="27" t="n"/>
       <c r="G62" s="27" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="n"/>
+      <c r="G63" s="27" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="n"/>
+      <c r="G64" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-24 04:52 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-24 09:10 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1000,7 +1000,9 @@
       <c r="H6" s="22" t="n">
         <v>8981</v>
       </c>
-      <c r="I6" s="22" t="n"/>
+      <c r="I6" s="22" t="n">
+        <v>120</v>
+      </c>
       <c r="J6" s="22" t="n"/>
       <c r="K6" s="23" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -1403,7 +1405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1461,7 +1463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1481,15 +1483,13 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>app</t>
@@ -1499,7 +1499,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1514,16 +1514,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n"/>
-      <c r="G3" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1538,40 +1552,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1581,13 +1581,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G5" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>app</t>
@@ -1597,7 +1599,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1617,15 +1619,13 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>app</t>
@@ -1635,7 +1635,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1655,11 +1655,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G7" s="27" t="n">
         <v>0</v>
@@ -1673,7 +1673,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1693,35 +1693,35 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1735,31 +1735,31 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1773,29 +1773,31 @@
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1809,21 +1811,19 @@
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1838,16 +1838,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1862,28 +1876,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n"/>
       <c r="G13" s="27" t="n"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1903,15 +1905,13 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>app</t>
@@ -1921,17 +1921,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1945,9 +1945,11 @@
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G15" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>app</t>
@@ -1957,31 +1959,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G16" s="27" t="n"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1996,7 +2010,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F17" s="27" t="n"/>
@@ -2005,53 +2019,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n"/>
       <c r="G18" s="27" t="n"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2061,47 +2063,59 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G20" s="27" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2116,7 +2130,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F21" s="27" t="n"/>
@@ -2125,22 +2139,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F22" s="27" t="n"/>
@@ -2149,7 +2163,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2164,28 +2178,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n"/>
       <c r="G23" s="27" t="n"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2205,15 +2207,13 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G24" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>app</t>
@@ -2223,7 +2223,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2238,16 +2238,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2262,7 +2276,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F26" s="27" t="n"/>
@@ -2271,103 +2285,91 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n"/>
       <c r="G27" s="27" t="n"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G28" s="27" t="n"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n"/>
       <c r="G29" s="27" t="n"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2382,31 +2384,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G30" s="27" t="n"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F31" s="27" t="n"/>
@@ -2415,7 +2429,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2430,28 +2444,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n"/>
       <c r="G32" s="27" t="n"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2466,52 +2468,52 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G33" s="27" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
       <c r="G34" s="27" t="n"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2526,16 +2528,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G35" s="27" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2550,7 +2564,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F36" s="27" t="n"/>
@@ -2559,69 +2573,69 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G38" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2636,7 +2650,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2645,43 +2659,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n"/>
       <c r="G40" s="27" t="n"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2696,16 +2698,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G41" s="27" t="n"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2720,7 +2734,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2729,43 +2743,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n"/>
       <c r="G43" s="27" t="n"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2785,11 +2787,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F44" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G44" s="27" t="n"/>
       <c r="H44" t="inlineStr">
@@ -2801,31 +2803,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G45" s="27" t="n"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2840,7 +2854,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F46" s="27" t="n"/>
@@ -2849,7 +2863,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2864,7 +2878,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F47" s="27" t="n"/>
@@ -2873,43 +2887,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n"/>
       <c r="G48" s="27" t="n"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2924,26 +2926,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F49" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G49" s="27" t="n"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2957,7 +2971,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2972,7 +2986,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F51" s="27" t="n"/>
@@ -2981,7 +2995,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2996,7 +3010,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F52" s="27" t="n"/>
@@ -3005,7 +3019,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3020,7 +3034,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3029,7 +3043,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3044,7 +3058,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F54" s="27" t="n"/>
@@ -3053,7 +3067,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3068,7 +3082,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
@@ -3077,22 +3091,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F56" s="27" t="n"/>
@@ -3101,7 +3115,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3125,7 +3139,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3140,7 +3154,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3149,7 +3163,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3164,7 +3178,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F59" s="27" t="n"/>
@@ -3173,7 +3187,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3188,7 +3202,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F60" s="27" t="n"/>
@@ -3197,7 +3211,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3212,7 +3226,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3221,7 +3235,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3245,7 +3259,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3260,7 +3274,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3269,7 +3283,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3284,11 +3298,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F64" s="27" t="n"/>
       <c r="G64" s="27" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="n"/>
+      <c r="G65" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-24 09:10 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-24 18:58 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>8981</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J6" s="22" t="n"/>
       <c r="K6" s="23" t="n"/>
@@ -1405,7 +1405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1463,7 +1463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1487,9 +1487,11 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>120</v>
-      </c>
-      <c r="G2" s="27" t="n"/>
+        <v>122</v>
+      </c>
+      <c r="G2" s="27" t="n">
+        <v>121</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>app</t>
@@ -1499,7 +1501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1519,14 +1521,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>8981</v>
+        <v>121</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>2680</v>
+        <v>120</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1537,7 +1539,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1552,16 +1554,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>120</v>
+      </c>
       <c r="G4" s="27" t="n"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1585,10 +1599,10 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G5" s="27" t="n">
         <v>2680</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>2650</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1599,53 +1613,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>4933</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n"/>
       <c r="G6" s="27" t="n"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1655,14 +1657,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>7567</v>
+        <v>2680</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>0</v>
+        <v>2650</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1673,7 +1675,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1693,15 +1695,13 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>4189</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>app</t>
@@ -1711,7 +1711,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1731,35 +1731,35 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>3685</v>
+        <v>7567</v>
       </c>
       <c r="G9" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1769,14 +1769,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>2650</v>
+        <v>4189</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1811,9 +1811,11 @@
         </is>
       </c>
       <c r="F11" s="27" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G11" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>shortcut</t>
@@ -1823,7 +1825,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1847,10 +1849,10 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G12" s="27" t="n">
         <v>831</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>387</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1861,31 +1863,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G13" s="27" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1909,9 +1923,11 @@
         </is>
       </c>
       <c r="F14" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G14" s="27" t="n">
         <v>387</v>
       </c>
-      <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>app</t>
@@ -1921,7 +1937,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1936,40 +1952,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1979,11 +1981,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>9097</v>
+        <v>387</v>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
@@ -1995,190 +1997,216 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>9720</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G18" s="27" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n"/>
       <c r="G19" s="27" t="n"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n"/>
       <c r="G20" s="27" t="n"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G21" s="27" t="n"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G22" s="27" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F23" s="27" t="n"/>
@@ -2187,43 +2215,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n"/>
       <c r="G24" s="27" t="n"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2238,30 +2254,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G25" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="27" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2276,16 +2278,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G26" s="27" t="n"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2300,52 +2314,54 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n"/>
       <c r="G28" s="27" t="n"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2360,7 +2376,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F29" s="27" t="n"/>
@@ -2369,17 +2385,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2393,34 +2409,34 @@
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>0</v>
+        <v>4842</v>
       </c>
       <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F31" s="27" t="n"/>
@@ -2429,67 +2445,67 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G32" s="27" t="n"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n"/>
       <c r="G33" s="27" t="n"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2504,7 +2520,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F34" s="27" t="n"/>
@@ -2513,17 +2529,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2537,7 +2553,7 @@
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>5345</v>
+        <v>12641</v>
       </c>
       <c r="G35" s="27" t="n"/>
       <c r="H35" t="inlineStr">
@@ -2549,22 +2565,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F36" s="27" t="n"/>
@@ -2573,7 +2589,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2588,69 +2604,67 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G37" s="27" t="n"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G38" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
+      <c r="G38" s="27" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2659,82 +2673,84 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G40" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n"/>
       <c r="G41" s="27" t="n"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2743,7 +2759,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2758,136 +2774,148 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G43" s="27" t="n"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n"/>
       <c r="G44" s="27" t="n"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n"/>
       <c r="G45" s="27" t="n"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G46" s="27" t="n"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F47" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G47" s="27" t="n"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2902,7 +2930,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F48" s="27" t="n"/>
@@ -2911,53 +2939,41 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F49" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="n"/>
       <c r="G49" s="27" t="n"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2971,46 +2987,58 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G51" s="27" t="n"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F52" s="27" t="n"/>
@@ -3019,7 +3047,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3043,7 +3071,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3067,7 +3095,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3082,7 +3110,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
@@ -3091,7 +3119,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3106,7 +3134,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F56" s="27" t="n"/>
@@ -3115,22 +3143,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3139,22 +3167,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3163,7 +3191,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,7 +3206,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F59" s="27" t="n"/>
@@ -3187,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3211,7 +3239,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3235,7 +3263,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3259,7 +3287,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3274,7 +3302,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3283,7 +3311,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3298,7 +3326,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F64" s="27" t="n"/>
@@ -3307,7 +3335,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3322,11 +3350,59 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F65" s="27" t="n"/>
       <c r="G65" s="27" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="n"/>
+      <c r="G66" s="27" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="n"/>
+      <c r="G67" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-24 18:58 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-25 01:22 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1098,7 +1098,9 @@
       <c r="H8" s="22" t="n">
         <v>3685</v>
       </c>
-      <c r="I8" s="22" t="n"/>
+      <c r="I8" s="22" t="n">
+        <v>7493</v>
+      </c>
       <c r="J8" s="22" t="n"/>
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="23" t="n"/>
@@ -1405,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1463,17 +1465,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1487,21 +1489,19 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G3" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1563,9 +1563,11 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G4" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>app</t>
@@ -1575,7 +1577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1595,15 +1597,13 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>app</t>
@@ -1613,7 +1613,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1628,16 +1628,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1652,40 +1666,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1695,13 +1695,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G8" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>app</t>
@@ -1711,7 +1713,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1731,15 +1733,13 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>app</t>
@@ -1749,7 +1749,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1769,11 +1769,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1807,35 +1807,35 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G11" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1849,31 +1849,31 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1887,29 +1887,31 @@
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1923,21 +1925,19 @@
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1952,16 +1952,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1976,28 +1990,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n"/>
       <c r="G16" s="27" t="n"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2017,15 +2019,13 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>app</t>
@@ -2035,17 +2035,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2059,9 +2059,11 @@
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G18" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>app</t>
@@ -2071,31 +2073,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G19" s="27" t="n"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2110,7 +2124,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F20" s="27" t="n"/>
@@ -2119,53 +2133,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n"/>
       <c r="G21" s="27" t="n"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2175,47 +2177,59 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G23" s="27" t="n"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2230,7 +2244,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F24" s="27" t="n"/>
@@ -2239,22 +2253,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F25" s="27" t="n"/>
@@ -2263,7 +2277,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2278,28 +2292,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n"/>
       <c r="G26" s="27" t="n"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2319,15 +2321,13 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G27" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G27" s="27" t="n"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>app</t>
@@ -2337,7 +2337,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2352,16 +2352,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G28" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2376,7 +2390,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F29" s="27" t="n"/>
@@ -2385,103 +2399,91 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n"/>
       <c r="G30" s="27" t="n"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G31" s="27" t="n"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n"/>
       <c r="G32" s="27" t="n"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2496,31 +2498,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G33" s="27" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F34" s="27" t="n"/>
@@ -2529,7 +2543,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2544,28 +2558,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n"/>
       <c r="G35" s="27" t="n"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2580,52 +2582,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G36" s="27" t="n"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n"/>
       <c r="G37" s="27" t="n"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2640,16 +2642,28 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G38" s="27" t="n"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2664,7 +2678,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2673,69 +2687,69 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G40" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="27" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2750,7 +2764,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2759,43 +2773,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n"/>
       <c r="G43" s="27" t="n"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2810,16 +2812,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G44" s="27" t="n"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2834,7 +2848,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F45" s="27" t="n"/>
@@ -2843,43 +2857,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n"/>
       <c r="G46" s="27" t="n"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2899,11 +2901,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F47" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G47" s="27" t="n"/>
       <c r="H47" t="inlineStr">
@@ -2915,31 +2917,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G48" s="27" t="n"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2954,7 +2968,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F49" s="27" t="n"/>
@@ -2963,7 +2977,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2978,7 +2992,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F50" s="27" t="n"/>
@@ -2987,43 +3001,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3038,26 +3040,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G52" s="27" t="n"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3071,7 +3085,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3086,7 +3100,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F54" s="27" t="n"/>
@@ -3095,7 +3109,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3110,7 +3124,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
@@ -3119,7 +3133,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3134,7 +3148,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F56" s="27" t="n"/>
@@ -3143,7 +3157,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3158,7 +3172,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3167,7 +3181,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3182,7 +3196,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3191,22 +3205,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F59" s="27" t="n"/>
@@ -3215,7 +3229,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3239,7 +3253,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3254,7 +3268,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3263,7 +3277,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3278,7 +3292,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F62" s="27" t="n"/>
@@ -3287,7 +3301,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3302,7 +3316,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3311,7 +3325,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3326,7 +3340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F64" s="27" t="n"/>
@@ -3335,7 +3349,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3359,7 +3373,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3374,7 +3388,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F66" s="27" t="n"/>
@@ -3383,7 +3397,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3398,11 +3412,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F67" s="27" t="n"/>
       <c r="G67" s="27" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F68" s="27" t="n"/>
+      <c r="G68" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-25 01:22 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-25 06:17 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>8981</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>122</v>
+        <v>8060</v>
       </c>
       <c r="J6" s="22" t="n"/>
       <c r="K6" s="23" t="n"/>
@@ -1407,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1465,17 +1465,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1489,29 +1489,31 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G2" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G2" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1525,21 +1527,19 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G3" s="27" t="n"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G4" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1601,9 +1601,11 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G5" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>app</t>
@@ -1613,7 +1615,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1633,15 +1635,13 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>app</t>
@@ -1651,7 +1651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1666,16 +1666,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1690,40 +1704,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="27" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1733,13 +1733,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G9" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>app</t>
@@ -1749,7 +1751,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1769,15 +1771,13 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G10" s="27" t="n"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>app</t>
@@ -1787,7 +1787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1807,11 +1807,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G11" s="27" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1845,35 +1845,35 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1887,31 +1887,31 @@
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1925,29 +1925,31 @@
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1961,21 +1963,19 @@
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1990,16 +1990,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2014,28 +2028,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n"/>
       <c r="G17" s="27" t="n"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2055,15 +2057,13 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>app</t>
@@ -2073,17 +2073,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2097,9 +2097,11 @@
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G19" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>app</t>
@@ -2109,31 +2111,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G20" s="27" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2148,7 +2162,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F21" s="27" t="n"/>
@@ -2157,53 +2171,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n"/>
       <c r="G22" s="27" t="n"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2213,47 +2215,59 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G23" s="27" t="n"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G24" s="27" t="n"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2268,7 +2282,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F25" s="27" t="n"/>
@@ -2277,22 +2291,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F26" s="27" t="n"/>
@@ -2301,7 +2315,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2316,28 +2330,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n"/>
       <c r="G27" s="27" t="n"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2357,15 +2359,13 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F28" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G28" s="27" t="n"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>app</t>
@@ -2375,7 +2375,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2390,16 +2390,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2414,7 +2428,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F30" s="27" t="n"/>
@@ -2423,103 +2437,91 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n"/>
       <c r="G31" s="27" t="n"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G32" s="27" t="n"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n"/>
       <c r="G33" s="27" t="n"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2534,31 +2536,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G34" s="27" t="n"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F35" s="27" t="n"/>
@@ -2567,7 +2581,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2582,28 +2596,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
       <c r="G36" s="27" t="n"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2618,52 +2620,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G37" s="27" t="n"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
       <c r="G38" s="27" t="n"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2678,16 +2680,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G39" s="27" t="n"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2702,7 +2716,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F40" s="27" t="n"/>
@@ -2711,69 +2725,69 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G41" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="27" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="n"/>
-      <c r="G42" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G42" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2788,7 +2802,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F43" s="27" t="n"/>
@@ -2797,43 +2811,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n"/>
       <c r="G44" s="27" t="n"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2848,16 +2850,28 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G45" s="27" t="n"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2872,7 +2886,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F46" s="27" t="n"/>
@@ -2881,43 +2895,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F47" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="n"/>
       <c r="G47" s="27" t="n"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2937,11 +2939,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F48" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G48" s="27" t="n"/>
       <c r="H48" t="inlineStr">
@@ -2953,31 +2955,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F49" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G49" s="27" t="n"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2992,7 +3006,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F50" s="27" t="n"/>
@@ -3001,7 +3015,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3016,7 +3030,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F51" s="27" t="n"/>
@@ -3025,43 +3039,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n"/>
       <c r="G52" s="27" t="n"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3076,26 +3078,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F53" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G53" s="27" t="n"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3109,7 +3123,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3124,7 +3138,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
@@ -3133,7 +3147,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3148,7 +3162,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F56" s="27" t="n"/>
@@ -3157,7 +3171,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3172,7 +3186,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3181,7 +3195,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3196,7 +3210,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3205,7 +3219,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3220,7 +3234,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F59" s="27" t="n"/>
@@ -3229,22 +3243,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F60" s="27" t="n"/>
@@ -3253,7 +3267,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3277,7 +3291,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3292,7 +3306,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F62" s="27" t="n"/>
@@ -3301,7 +3315,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3316,7 +3330,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3325,7 +3339,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3340,7 +3354,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F64" s="27" t="n"/>
@@ -3349,7 +3363,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3364,7 +3378,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F65" s="27" t="n"/>
@@ -3373,7 +3387,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3397,7 +3411,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3412,7 +3426,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F67" s="27" t="n"/>
@@ -3421,7 +3435,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3436,11 +3450,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F68" s="27" t="n"/>
       <c r="G68" s="27" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n"/>
+      <c r="G69" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-25 06:17 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-25 15:02 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1407,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1465,7 +1465,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1480,40 +1480,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n"/>
+      <c r="G2" s="27" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1527,29 +1513,31 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G3" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1563,21 +1551,19 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1601,10 +1587,10 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G5" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1615,7 +1601,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1639,9 +1625,11 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G6" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>app</t>
@@ -1651,7 +1639,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1671,15 +1659,13 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>app</t>
@@ -1689,7 +1675,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1704,16 +1690,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1728,40 +1728,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="27" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1771,13 +1757,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G10" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>app</t>
@@ -1787,7 +1775,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1807,15 +1795,13 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>app</t>
@@ -1825,7 +1811,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1845,11 +1831,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0</v>
@@ -1863,7 +1849,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1883,35 +1869,35 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G13" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1925,31 +1911,31 @@
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1963,29 +1949,31 @@
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1999,21 +1987,19 @@
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2028,16 +2014,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2052,28 +2052,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n"/>
       <c r="G18" s="27" t="n"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2093,15 +2081,13 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>app</t>
@@ -2111,17 +2097,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2135,9 +2121,11 @@
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G20" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>app</t>
@@ -2147,31 +2135,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G21" s="27" t="n"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F22" s="27" t="n"/>
@@ -2195,53 +2195,41 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n"/>
       <c r="G23" s="27" t="n"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2251,47 +2239,59 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G25" s="27" t="n"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F26" s="27" t="n"/>
@@ -2315,22 +2315,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F27" s="27" t="n"/>
@@ -2339,7 +2339,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2354,28 +2354,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n"/>
       <c r="G28" s="27" t="n"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2395,15 +2383,13 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F29" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G29" s="27" t="n"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>app</t>
@@ -2413,7 +2399,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2428,16 +2414,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n"/>
-      <c r="G30" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G30" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F31" s="27" t="n"/>
@@ -2461,103 +2461,91 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n"/>
       <c r="G32" s="27" t="n"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G33" s="27" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
       <c r="G34" s="27" t="n"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2572,31 +2560,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G35" s="27" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F36" s="27" t="n"/>
@@ -2605,7 +2605,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2620,28 +2620,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n"/>
       <c r="G37" s="27" t="n"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2656,52 +2644,52 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G38" s="27" t="n"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n"/>
       <c r="G39" s="27" t="n"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2716,16 +2704,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G40" s="27" t="n"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F41" s="27" t="n"/>
@@ -2749,69 +2749,69 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G42" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n"/>
+      <c r="G42" s="27" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G43" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F44" s="27" t="n"/>
@@ -2835,43 +2835,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n"/>
       <c r="G45" s="27" t="n"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2886,16 +2874,28 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G46" s="27" t="n"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F47" s="27" t="n"/>
@@ -2919,43 +2919,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n"/>
       <c r="G48" s="27" t="n"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2975,11 +2963,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G49" s="27" t="n"/>
       <c r="H49" t="inlineStr">
@@ -2991,31 +2979,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F50" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G50" s="27" t="n"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F51" s="27" t="n"/>
@@ -3039,7 +3039,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F52" s="27" t="n"/>
@@ -3063,43 +3063,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F53" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="n"/>
       <c r="G53" s="27" t="n"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3114,26 +3102,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G54" s="27" t="n"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3147,7 +3147,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F56" s="27" t="n"/>
@@ -3171,7 +3171,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3195,7 +3195,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3219,7 +3219,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F59" s="27" t="n"/>
@@ -3243,7 +3243,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F60" s="27" t="n"/>
@@ -3267,22 +3267,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3291,7 +3291,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3315,7 +3315,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3339,7 +3339,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F64" s="27" t="n"/>
@@ -3363,7 +3363,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F65" s="27" t="n"/>
@@ -3387,7 +3387,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F66" s="27" t="n"/>
@@ -3411,7 +3411,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F68" s="27" t="n"/>
@@ -3459,7 +3459,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3474,11 +3474,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F69" s="27" t="n"/>
       <c r="G69" s="27" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n"/>
+      <c r="G70" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-25 15:02 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-25 18:20 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1003,7 +1003,9 @@
       <c r="I6" s="22" t="n">
         <v>8060</v>
       </c>
-      <c r="J6" s="22" t="n"/>
+      <c r="J6" s="22" t="n">
+        <v>351</v>
+      </c>
       <c r="K6" s="23" t="n"/>
       <c r="L6" s="23" t="n"/>
       <c r="M6" s="23" t="n"/>
@@ -1407,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1465,7 +1467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1480,16 +1482,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G2" s="27" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1504,40 +1518,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n"/>
+      <c r="G3" s="27" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1551,29 +1551,31 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G4" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1587,21 +1589,19 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G6" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1663,9 +1663,11 @@
         </is>
       </c>
       <c r="F7" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G7" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>app</t>
@@ -1675,7 +1677,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1695,15 +1697,13 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>app</t>
@@ -1713,7 +1713,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1728,16 +1728,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1752,40 +1766,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1795,13 +1795,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G11" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>app</t>
@@ -1811,7 +1813,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1831,15 +1833,13 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1849,7 +1849,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G13" s="27" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,35 +1907,35 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1949,31 +1949,31 @@
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1987,29 +1987,31 @@
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2023,21 +2025,19 @@
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2052,16 +2052,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2076,28 +2090,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n"/>
       <c r="G19" s="27" t="n"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2117,15 +2119,13 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>app</t>
@@ -2135,17 +2135,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2159,9 +2159,11 @@
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G21" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>app</t>
@@ -2171,31 +2173,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G22" s="27" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2210,7 +2224,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F23" s="27" t="n"/>
@@ -2219,53 +2233,41 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n"/>
       <c r="G24" s="27" t="n"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2275,47 +2277,59 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G25" s="27" t="n"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G26" s="27" t="n"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2330,7 +2344,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F27" s="27" t="n"/>
@@ -2339,22 +2353,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2363,7 +2377,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2378,28 +2392,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n"/>
       <c r="G29" s="27" t="n"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2419,15 +2421,13 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G30" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>app</t>
@@ -2437,7 +2437,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2452,16 +2452,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n"/>
-      <c r="G31" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2476,7 +2490,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2485,103 +2499,91 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n"/>
       <c r="G33" s="27" t="n"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G34" s="27" t="n"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n"/>
       <c r="G35" s="27" t="n"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2596,31 +2598,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G36" s="27" t="n"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F37" s="27" t="n"/>
@@ -2629,7 +2643,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2644,28 +2658,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
       <c r="G38" s="27" t="n"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2680,52 +2682,52 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G39" s="27" t="n"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n"/>
       <c r="G40" s="27" t="n"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2740,16 +2742,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G41" s="27" t="n"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2764,7 +2778,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2773,69 +2787,69 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G43" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="27" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G44" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2850,7 +2864,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F45" s="27" t="n"/>
@@ -2859,43 +2873,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n"/>
       <c r="G46" s="27" t="n"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2910,16 +2912,28 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F47" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G47" s="27" t="n"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2934,7 +2948,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F48" s="27" t="n"/>
@@ -2943,43 +2957,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F49" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="n"/>
       <c r="G49" s="27" t="n"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2999,11 +3001,11 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F50" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G50" s="27" t="n"/>
       <c r="H50" t="inlineStr">
@@ -3015,31 +3017,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G51" s="27" t="n"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3054,7 +3068,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F52" s="27" t="n"/>
@@ -3063,7 +3077,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3078,7 +3092,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3087,43 +3101,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n"/>
       <c r="G54" s="27" t="n"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3138,26 +3140,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G55" s="27" t="n"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3171,7 +3185,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3186,7 +3200,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3195,7 +3209,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3210,7 +3224,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3219,7 +3233,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3234,7 +3248,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F59" s="27" t="n"/>
@@ -3243,7 +3257,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3258,7 +3272,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F60" s="27" t="n"/>
@@ -3267,7 +3281,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3282,7 +3296,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3291,22 +3305,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F62" s="27" t="n"/>
@@ -3315,7 +3329,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3339,7 +3353,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3354,7 +3368,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F64" s="27" t="n"/>
@@ -3363,7 +3377,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3378,7 +3392,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F65" s="27" t="n"/>
@@ -3387,7 +3401,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3402,7 +3416,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F66" s="27" t="n"/>
@@ -3411,7 +3425,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3426,7 +3440,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F67" s="27" t="n"/>
@@ -3435,7 +3449,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3459,7 +3473,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3474,7 +3488,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F69" s="27" t="n"/>
@@ -3483,7 +3497,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3498,11 +3512,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F70" s="27" t="n"/>
       <c r="G70" s="27" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F71" s="27" t="n"/>
+      <c r="G71" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-25 18:20 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-26 01:02 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1103,7 +1103,9 @@
       <c r="I8" s="22" t="n">
         <v>7493</v>
       </c>
-      <c r="J8" s="22" t="n"/>
+      <c r="J8" s="22" t="n">
+        <v>13001</v>
+      </c>
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="23" t="n"/>
       <c r="M8" s="23" t="n"/>
@@ -1409,7 +1411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1467,17 +1469,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1491,19 +1493,19 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>351</v>
+        <v>13001</v>
       </c>
       <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1518,16 +1520,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G3" s="27" t="n"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1542,40 +1556,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1589,29 +1589,31 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G5" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1625,21 +1627,19 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="F7" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G7" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1701,9 +1701,11 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G8" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>app</t>
@@ -1713,7 +1715,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1733,15 +1735,13 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>app</t>
@@ -1751,7 +1751,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1766,16 +1766,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1790,40 +1804,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1833,13 +1833,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G12" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1849,7 +1851,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1869,15 +1871,13 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>app</t>
@@ -1887,7 +1887,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,11 +1907,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1945,35 +1945,35 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G15" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1987,31 +1987,31 @@
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2025,29 +2025,31 @@
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2061,21 +2063,19 @@
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2090,16 +2090,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2114,28 +2128,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n"/>
       <c r="G20" s="27" t="n"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2155,15 +2157,13 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G21" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>app</t>
@@ -2173,17 +2173,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2197,9 +2197,11 @@
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G22" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>app</t>
@@ -2209,31 +2211,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G23" s="27" t="n"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2248,7 +2262,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F24" s="27" t="n"/>
@@ -2257,53 +2271,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n"/>
       <c r="G25" s="27" t="n"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2313,47 +2315,59 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G26" s="27" t="n"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G27" s="27" t="n"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2368,7 +2382,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2377,22 +2391,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F29" s="27" t="n"/>
@@ -2401,7 +2415,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2416,28 +2430,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n"/>
       <c r="G30" s="27" t="n"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2457,15 +2459,13 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F31" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G31" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G31" s="27" t="n"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>app</t>
@@ -2475,7 +2475,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2490,16 +2490,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2514,7 +2528,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F33" s="27" t="n"/>
@@ -2523,103 +2537,91 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
       <c r="G34" s="27" t="n"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G35" s="27" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
       <c r="G36" s="27" t="n"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2634,31 +2636,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G37" s="27" t="n"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F38" s="27" t="n"/>
@@ -2667,7 +2681,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2682,28 +2696,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n"/>
       <c r="G39" s="27" t="n"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2718,52 +2720,52 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G40" s="27" t="n"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n"/>
       <c r="G41" s="27" t="n"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2778,16 +2780,28 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G42" s="27" t="n"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2802,7 +2816,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F43" s="27" t="n"/>
@@ -2811,69 +2825,69 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G44" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="27" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G45" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2888,7 +2902,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F46" s="27" t="n"/>
@@ -2897,43 +2911,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F47" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="n"/>
       <c r="G47" s="27" t="n"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2948,16 +2950,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G48" s="27" t="n"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2972,7 +2986,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F49" s="27" t="n"/>
@@ -2981,43 +2995,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F50" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="n"/>
       <c r="G50" s="27" t="n"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3037,11 +3039,11 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F51" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G51" s="27" t="n"/>
       <c r="H51" t="inlineStr">
@@ -3053,31 +3055,43 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G52" s="27" t="n"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3092,7 +3106,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3101,7 +3115,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3116,7 +3130,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F54" s="27" t="n"/>
@@ -3125,43 +3139,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n"/>
       <c r="G55" s="27" t="n"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3176,26 +3178,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G56" s="27" t="n"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3209,7 +3223,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3224,7 +3238,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3233,7 +3247,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3248,7 +3262,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F59" s="27" t="n"/>
@@ -3257,7 +3271,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3272,7 +3286,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F60" s="27" t="n"/>
@@ -3281,7 +3295,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3296,7 +3310,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3305,7 +3319,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3320,7 +3334,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F62" s="27" t="n"/>
@@ -3329,22 +3343,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3353,7 +3367,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3377,7 +3391,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3392,7 +3406,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F65" s="27" t="n"/>
@@ -3401,7 +3415,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3416,7 +3430,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F66" s="27" t="n"/>
@@ -3425,7 +3439,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3440,7 +3454,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F67" s="27" t="n"/>
@@ -3449,7 +3463,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3464,7 +3478,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F68" s="27" t="n"/>
@@ -3473,7 +3487,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3497,7 +3511,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3512,7 +3526,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F70" s="27" t="n"/>
@@ -3521,7 +3535,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3536,11 +3550,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
       <c r="G71" s="27" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="n"/>
+      <c r="G72" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-26 01:02 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-26 05:57 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1004,9 +1004,11 @@
         <v>8060</v>
       </c>
       <c r="J6" s="22" t="n">
+        <v>20274</v>
+      </c>
+      <c r="K6" s="23" t="n">
         <v>351</v>
       </c>
-      <c r="K6" s="23" t="n"/>
       <c r="L6" s="23" t="n"/>
       <c r="M6" s="23" t="n"/>
       <c r="N6" s="23" t="n"/>
@@ -1411,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1469,17 +1471,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1489,23 +1491,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>13001</v>
+        <v>351</v>
       </c>
       <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1529,9 +1531,11 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>351</v>
-      </c>
-      <c r="G3" s="27" t="n"/>
+        <v>20274</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>3510</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>app</t>
@@ -1541,7 +1545,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1556,26 +1560,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>351</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1585,35 +1603,33 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>122</v>
-      </c>
+        <v>13001</v>
+      </c>
+      <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1623,23 +1639,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>7493</v>
+        <v>351</v>
       </c>
       <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1654,30 +1670,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>121</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1701,10 +1703,10 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>121</v>
+        <v>8060</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1715,17 +1717,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1739,19 +1741,19 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>120</v>
+        <v>7493</v>
       </c>
       <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1771,14 +1773,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>8981</v>
+        <v>122</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>2680</v>
+        <v>121</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1789,7 +1791,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1804,16 +1806,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>120</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1833,15 +1849,13 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>2650</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1851,17 +1865,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1871,13 +1885,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G13" s="27" t="n"/>
+        <v>8981</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>2680</v>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>app</t>
@@ -1887,55 +1903,41 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1945,14 +1947,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>4189</v>
+        <v>2680</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>0</v>
+        <v>2650</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1963,7 +1965,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1983,35 +1985,33 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>3685</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2021,14 +2021,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>2650</v>
+        <v>7567</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2059,33 +2059,35 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
+        <v>4189</v>
+      </c>
+      <c r="G18" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2099,21 +2101,21 @@
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>831</v>
+        <v>3685</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2128,26 +2130,40 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2161,19 +2177,19 @@
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2193,14 +2209,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>9720</v>
+        <v>831</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>1100</v>
+        <v>387</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2211,101 +2227,115 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n">
-        <v>9097</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n"/>
       <c r="G23" s="27" t="n"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>387</v>
+      </c>
       <c r="G24" s="27" t="n"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>9720</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2315,11 +2345,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>10808</v>
+        <v>9097</v>
       </c>
       <c r="G26" s="27" t="n"/>
       <c r="H26" t="inlineStr">
@@ -2331,43 +2361,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n"/>
       <c r="G27" s="27" t="n"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2382,7 +2400,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2391,129 +2409,127 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G29" s="27" t="n"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G30" s="27" t="n"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n"/>
       <c r="G31" s="27" t="n"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G32" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="27" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2537,7 +2553,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2552,26 +2568,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G34" s="27" t="n"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2585,9 +2613,11 @@
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>4842</v>
-      </c>
-      <c r="G35" s="27" t="n"/>
+        <v>18461</v>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>1985</v>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>app</t>
@@ -2597,7 +2627,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2621,82 +2651,82 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n"/>
       <c r="G37" s="27" t="n"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G38" s="27" t="n"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2705,17 +2735,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2725,38 +2755,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F40" s="27" t="n">
-        <v>12641</v>
+        <v>0</v>
       </c>
       <c r="G40" s="27" t="n"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F41" s="27" t="n"/>
@@ -2765,77 +2795,77 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n"/>
       <c r="G42" s="27" t="n"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G43" s="27" t="n"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2849,17 +2879,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2869,15 +2899,13 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F45" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G45" s="27" t="n">
-        <v>100</v>
-      </c>
+        <v>5345</v>
+      </c>
+      <c r="G45" s="27" t="n"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>app</t>
@@ -2887,17 +2915,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2911,17 +2939,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2935,17 +2963,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2955,13 +2983,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F48" s="27" t="n">
-        <v>10383</v>
-      </c>
-      <c r="G48" s="27" t="n"/>
+        <v>1985</v>
+      </c>
+      <c r="G48" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>app</t>
@@ -2971,22 +3001,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F49" s="27" t="n"/>
@@ -2995,17 +3025,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3019,17 +3049,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3039,11 +3069,11 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F51" s="27" t="n">
-        <v>100</v>
+        <v>10383</v>
       </c>
       <c r="G51" s="27" t="n"/>
       <c r="H51" t="inlineStr">
@@ -3055,58 +3085,46 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n"/>
       <c r="G52" s="27" t="n"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3115,106 +3133,118 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G54" s="27" t="n"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G55" s="27" t="n"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n"/>
       <c r="G56" s="27" t="n"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3223,17 +3253,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3247,41 +3277,53 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G59" s="27" t="n"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3295,7 +3337,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3310,7 +3352,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3319,7 +3361,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3334,7 +3376,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F62" s="27" t="n"/>
@@ -3343,7 +3385,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3367,22 +3409,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F64" s="27" t="n"/>
@@ -3391,22 +3433,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F65" s="27" t="n"/>
@@ -3415,22 +3457,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F66" s="27" t="n"/>
@@ -3439,7 +3481,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3463,7 +3505,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3478,7 +3520,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F68" s="27" t="n"/>
@@ -3487,7 +3529,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3502,7 +3544,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F69" s="27" t="n"/>
@@ -3511,7 +3553,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3535,7 +3577,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3550,7 +3592,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
@@ -3559,7 +3601,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3574,11 +3616,83 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F72" s="27" t="n"/>
       <c r="G72" s="27" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="n"/>
+      <c r="G73" s="27" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="n"/>
+      <c r="G74" s="27" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="n"/>
+      <c r="G75" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-26 05:57 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-26 18:39 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1007,7 +1007,7 @@
         <v>20274</v>
       </c>
       <c r="K6" s="23" t="n">
-        <v>351</v>
+        <v>911</v>
       </c>
       <c r="L6" s="23" t="n"/>
       <c r="M6" s="23" t="n"/>
@@ -1413,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1471,7 +1471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1495,9 +1495,11 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="G2" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>app</t>
@@ -1507,7 +1509,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1527,15 +1529,13 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G3" s="27" t="n"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>app</t>
@@ -1545,7 +1545,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
+        <v>20274</v>
+      </c>
+      <c r="G4" s="27" t="n">
         <v>3510</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1583,17 +1583,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1607,29 +1607,31 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G5" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1643,19 +1645,19 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>351</v>
+        <v>13001</v>
       </c>
       <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1670,16 +1672,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G7" s="27" t="n"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1694,40 +1708,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="27" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1741,29 +1741,31 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G9" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1777,21 +1779,19 @@
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G10" s="27" t="n"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="F11" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G11" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1853,9 +1853,11 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G12" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1865,7 +1867,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1885,15 +1887,13 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>app</t>
@@ -1903,7 +1903,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,16 +1918,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1942,40 +1956,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1985,13 +1985,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G16" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>app</t>
@@ -2001,7 +2003,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2021,15 +2023,13 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>app</t>
@@ -2039,7 +2039,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2059,11 +2059,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>0</v>
@@ -2077,7 +2077,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2097,35 +2097,35 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2139,31 +2139,31 @@
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2177,29 +2177,31 @@
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2213,21 +2215,19 @@
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G22" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2242,16 +2242,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G23" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2266,28 +2280,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n"/>
       <c r="G24" s="27" t="n"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2307,15 +2309,13 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G25" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G25" s="27" t="n"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>app</t>
@@ -2325,17 +2325,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2349,9 +2349,11 @@
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G26" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G26" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>app</t>
@@ -2361,31 +2363,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G27" s="27" t="n"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2400,7 +2414,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F28" s="27" t="n"/>
@@ -2409,53 +2423,41 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n"/>
       <c r="G29" s="27" t="n"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2465,47 +2467,59 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G31" s="27" t="n"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2520,7 +2534,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2529,22 +2543,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F33" s="27" t="n"/>
@@ -2553,7 +2567,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2568,28 +2582,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
       <c r="G34" s="27" t="n"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2609,15 +2611,13 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G35" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G35" s="27" t="n"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>app</t>
@@ -2627,7 +2627,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2642,16 +2642,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n"/>
-      <c r="G36" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2666,7 +2680,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F37" s="27" t="n"/>
@@ -2675,103 +2689,91 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
       <c r="G38" s="27" t="n"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G39" s="27" t="n"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n"/>
       <c r="G40" s="27" t="n"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2786,31 +2788,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G41" s="27" t="n"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2819,7 +2833,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2834,28 +2848,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n"/>
       <c r="G43" s="27" t="n"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2870,52 +2872,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G44" s="27" t="n"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n"/>
       <c r="G45" s="27" t="n"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2930,16 +2932,28 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G46" s="27" t="n"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2954,7 +2968,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F47" s="27" t="n"/>
@@ -2963,69 +2977,69 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G48" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n"/>
+      <c r="G48" s="27" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G49" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3040,7 +3054,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F50" s="27" t="n"/>
@@ -3049,43 +3063,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3100,16 +3102,28 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G52" s="27" t="n"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3124,7 +3138,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3133,43 +3147,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n"/>
       <c r="G54" s="27" t="n"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3189,11 +3191,11 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F55" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G55" s="27" t="n"/>
       <c r="H55" t="inlineStr">
@@ -3205,31 +3207,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G56" s="27" t="n"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3244,7 +3258,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3253,7 +3267,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3268,7 +3282,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3277,43 +3291,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n"/>
       <c r="G59" s="27" t="n"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3328,26 +3330,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G60" s="27" t="n"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3361,7 +3375,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3376,7 +3390,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F62" s="27" t="n"/>
@@ -3385,7 +3399,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3400,7 +3414,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3409,7 +3423,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3424,7 +3438,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F64" s="27" t="n"/>
@@ -3433,7 +3447,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3448,7 +3462,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F65" s="27" t="n"/>
@@ -3457,7 +3471,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3472,7 +3486,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F66" s="27" t="n"/>
@@ -3481,22 +3495,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F67" s="27" t="n"/>
@@ -3505,7 +3519,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3529,7 +3543,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3544,7 +3558,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F69" s="27" t="n"/>
@@ -3553,7 +3567,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3568,7 +3582,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F70" s="27" t="n"/>
@@ -3577,7 +3591,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3592,7 +3606,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
@@ -3601,7 +3615,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3616,7 +3630,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F72" s="27" t="n"/>
@@ -3625,7 +3639,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3649,7 +3663,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3664,7 +3678,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F74" s="27" t="n"/>
@@ -3673,7 +3687,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3688,11 +3702,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F75" s="27" t="n"/>
       <c r="G75" s="27" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="n"/>
+      <c r="G76" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-26 18:39 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-27 01:38 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1007,7 +1007,7 @@
         <v>20274</v>
       </c>
       <c r="K6" s="23" t="n">
-        <v>911</v>
+        <v>1157</v>
       </c>
       <c r="L6" s="23" t="n"/>
       <c r="M6" s="23" t="n"/>
@@ -1108,7 +1108,9 @@
       <c r="J8" s="22" t="n">
         <v>13001</v>
       </c>
-      <c r="K8" s="23" t="n"/>
+      <c r="K8" s="23" t="n">
+        <v>8300</v>
+      </c>
       <c r="L8" s="23" t="n"/>
       <c r="M8" s="23" t="n"/>
       <c r="N8" s="23" t="n"/>
@@ -1413,7 +1415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1471,7 +1473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1486,30 +1488,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>351</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n"/>
+      <c r="G2" s="27" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1533,9 +1521,11 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>351</v>
-      </c>
-      <c r="G3" s="27" t="n"/>
+        <v>1157</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>911</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>app</t>
@@ -1545,17 +1535,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1565,25 +1555,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>8300</v>
+      </c>
+      <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1603,11 +1591,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>3510</v>
+        <v>911</v>
       </c>
       <c r="G5" s="27" t="n">
         <v>351</v>
@@ -1621,17 +1609,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1641,23 +1629,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>13001</v>
+        <v>351</v>
       </c>
       <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1681,9 +1669,11 @@
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>351</v>
-      </c>
-      <c r="G7" s="27" t="n"/>
+        <v>20274</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>3510</v>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>app</t>
@@ -1693,7 +1683,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1708,26 +1698,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>351</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1737,35 +1741,33 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>122</v>
-      </c>
+        <v>13001</v>
+      </c>
+      <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1775,23 +1777,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>7493</v>
+        <v>351</v>
       </c>
       <c r="G10" s="27" t="n"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1806,30 +1808,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>121</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1853,10 +1841,10 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>121</v>
+        <v>8060</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1867,17 +1855,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1891,19 +1879,19 @@
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>120</v>
+        <v>7493</v>
       </c>
       <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1923,14 +1911,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>8981</v>
+        <v>122</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>2680</v>
+        <v>121</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1941,7 +1929,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1956,16 +1944,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>120</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1985,15 +1987,13 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>2650</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>app</t>
@@ -2003,17 +2003,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2023,13 +2023,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G17" s="27" t="n"/>
+        <v>8981</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>2680</v>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>app</t>
@@ -2039,55 +2041,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n"/>
+      <c r="G18" s="27" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2097,14 +2085,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>4189</v>
+        <v>2680</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>0</v>
+        <v>2650</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2115,7 +2103,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2135,35 +2123,33 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>3685</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2173,14 +2159,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>2650</v>
+        <v>7567</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2191,7 +2177,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2211,33 +2197,35 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
+        <v>4189</v>
+      </c>
+      <c r="G22" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2251,21 +2239,21 @@
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>831</v>
+        <v>3685</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2280,26 +2268,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2313,19 +2315,19 @@
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="G25" s="27" t="n"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2345,14 +2347,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>9720</v>
+        <v>831</v>
       </c>
       <c r="G26" s="27" t="n">
-        <v>1100</v>
+        <v>387</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2363,101 +2365,115 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>9097</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n"/>
       <c r="G27" s="27" t="n"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>387</v>
+      </c>
       <c r="G28" s="27" t="n"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>9720</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2467,11 +2483,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>10808</v>
+        <v>9097</v>
       </c>
       <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
@@ -2483,43 +2499,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n"/>
       <c r="G31" s="27" t="n"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2534,7 +2538,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F32" s="27" t="n"/>
@@ -2543,129 +2547,127 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G33" s="27" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G34" s="27" t="n"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n"/>
       <c r="G35" s="27" t="n"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G36" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2689,7 +2691,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2704,26 +2706,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G38" s="27" t="n"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2737,9 +2751,11 @@
         </is>
       </c>
       <c r="F39" s="27" t="n">
-        <v>4842</v>
-      </c>
-      <c r="G39" s="27" t="n"/>
+        <v>18461</v>
+      </c>
+      <c r="G39" s="27" t="n">
+        <v>1985</v>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>app</t>
@@ -2749,7 +2765,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2773,82 +2789,82 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n"/>
       <c r="G41" s="27" t="n"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G42" s="27" t="n"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F43" s="27" t="n"/>
@@ -2857,17 +2873,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2877,38 +2893,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F44" s="27" t="n">
-        <v>12641</v>
+        <v>0</v>
       </c>
       <c r="G44" s="27" t="n"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F45" s="27" t="n"/>
@@ -2917,77 +2933,77 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n"/>
       <c r="G46" s="27" t="n"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F47" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G47" s="27" t="n"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3001,17 +3017,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3021,15 +3037,13 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G49" s="27" t="n">
-        <v>100</v>
-      </c>
+        <v>5345</v>
+      </c>
+      <c r="G49" s="27" t="n"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>app</t>
@@ -3039,17 +3053,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3063,17 +3077,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3087,17 +3101,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3107,13 +3121,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F52" s="27" t="n">
-        <v>10383</v>
-      </c>
-      <c r="G52" s="27" t="n"/>
+        <v>1985</v>
+      </c>
+      <c r="G52" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>app</t>
@@ -3123,22 +3139,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3147,17 +3163,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3171,17 +3187,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3191,11 +3207,11 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F55" s="27" t="n">
-        <v>100</v>
+        <v>10383</v>
       </c>
       <c r="G55" s="27" t="n"/>
       <c r="H55" t="inlineStr">
@@ -3207,58 +3223,46 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n"/>
       <c r="G56" s="27" t="n"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3267,106 +3271,118 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F58" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G58" s="27" t="n"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G59" s="27" t="n"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n"/>
       <c r="G60" s="27" t="n"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3375,17 +3391,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3399,41 +3415,53 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="F63" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G63" s="27" t="n"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3447,7 +3475,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3462,7 +3490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F65" s="27" t="n"/>
@@ -3471,7 +3499,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3486,7 +3514,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F66" s="27" t="n"/>
@@ -3495,7 +3523,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3519,22 +3547,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F68" s="27" t="n"/>
@@ -3543,22 +3571,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F69" s="27" t="n"/>
@@ -3567,22 +3595,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F70" s="27" t="n"/>
@@ -3591,7 +3619,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3615,7 +3643,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3630,7 +3658,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F72" s="27" t="n"/>
@@ -3639,7 +3667,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3654,7 +3682,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F73" s="27" t="n"/>
@@ -3663,7 +3691,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3687,7 +3715,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3702,7 +3730,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F75" s="27" t="n"/>
@@ -3711,7 +3739,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3726,11 +3754,83 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F76" s="27" t="n"/>
       <c r="G76" s="27" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F77" s="27" t="n"/>
+      <c r="G77" s="27" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="n"/>
+      <c r="G78" s="27" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F79" s="27" t="n"/>
+      <c r="G79" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-27 01:38 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-27 12:43 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1007,9 +1007,11 @@
         <v>20274</v>
       </c>
       <c r="K6" s="23" t="n">
-        <v>1157</v>
-      </c>
-      <c r="L6" s="23" t="n"/>
+        <v>15809</v>
+      </c>
+      <c r="L6" s="23" t="n">
+        <v>311</v>
+      </c>
       <c r="M6" s="23" t="n"/>
       <c r="N6" s="23" t="n"/>
       <c r="O6" s="23" t="n"/>
@@ -1415,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1473,7 +1475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1488,16 +1490,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="G2" s="27" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1521,10 +1535,10 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G3" s="27" t="n">
         <v>1157</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>911</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1535,43 +1549,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>8300</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n"/>
       <c r="G4" s="27" t="n"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1595,10 +1597,10 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="G5" s="27" t="n">
         <v>911</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1609,17 +1611,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1633,19 +1635,19 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>351</v>
+        <v>8300</v>
       </c>
       <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1665,14 +1667,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>20274</v>
+        <v>911</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>3510</v>
+        <v>351</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1683,7 +1685,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1703,15 +1705,13 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>3510</v>
-      </c>
-      <c r="G8" s="27" t="n">
         <v>351</v>
       </c>
+      <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>app</t>
@@ -1721,17 +1721,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1745,19 +1745,21 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G9" s="27" t="n"/>
+        <v>20274</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>3510</v>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1781,9 +1783,11 @@
         </is>
       </c>
       <c r="F10" s="27" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G10" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G10" s="27" t="n"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>app</t>
@@ -1793,31 +1797,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>13001</v>
+      </c>
       <c r="G11" s="27" t="n"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1837,15 +1853,13 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>122</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1855,43 +1869,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>7493</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n"/>
       <c r="G13" s="27" t="n"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1915,10 +1917,10 @@
         </is>
       </c>
       <c r="F14" s="27" t="n">
+        <v>8060</v>
+      </c>
+      <c r="G14" s="27" t="n">
         <v>122</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>121</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1929,17 +1931,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1953,21 +1955,19 @@
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>121</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>120</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,9 +1991,11 @@
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>120</v>
-      </c>
-      <c r="G16" s="27" t="n"/>
+        <v>122</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>121</v>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>app</t>
@@ -2003,7 +2005,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2023,14 +2025,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>8981</v>
+        <v>121</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>2680</v>
+        <v>120</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2041,7 +2043,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2056,16 +2058,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>120</v>
+      </c>
       <c r="G18" s="27" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2089,10 +2103,10 @@
         </is>
       </c>
       <c r="F19" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G19" s="27" t="n">
         <v>2680</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>2650</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2103,53 +2117,41 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>4933</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n"/>
       <c r="G20" s="27" t="n"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2159,14 +2161,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>7567</v>
+        <v>2680</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>0</v>
+        <v>2650</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2177,7 +2179,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2197,15 +2199,13 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>4189</v>
-      </c>
-      <c r="G22" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>app</t>
@@ -2215,7 +2215,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2235,35 +2235,35 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>3685</v>
+        <v>7567</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2273,14 +2273,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>2650</v>
+        <v>4189</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2315,9 +2315,11 @@
         </is>
       </c>
       <c r="F25" s="27" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G25" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="27" t="n"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>shortcut</t>
@@ -2327,7 +2329,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2351,10 +2353,10 @@
         </is>
       </c>
       <c r="F26" s="27" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G26" s="27" t="n">
         <v>831</v>
-      </c>
-      <c r="G26" s="27" t="n">
-        <v>387</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2365,31 +2367,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G27" s="27" t="n"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2413,9 +2427,11 @@
         </is>
       </c>
       <c r="F28" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G28" s="27" t="n">
         <v>387</v>
       </c>
-      <c r="G28" s="27" t="n"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>app</t>
@@ -2425,7 +2441,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2440,40 +2456,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="27" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2483,11 +2485,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>9097</v>
+        <v>387</v>
       </c>
       <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
@@ -2499,190 +2501,216 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n"/>
-      <c r="G31" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>9720</v>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G32" s="27" t="n"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n"/>
       <c r="G33" s="27" t="n"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
       <c r="G34" s="27" t="n"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G35" s="27" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G36" s="27" t="n"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F37" s="27" t="n"/>
@@ -2691,43 +2719,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
       <c r="G38" s="27" t="n"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2742,30 +2758,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G39" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2780,16 +2782,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G40" s="27" t="n"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2804,52 +2818,54 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n"/>
       <c r="G42" s="27" t="n"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2864,7 +2880,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F43" s="27" t="n"/>
@@ -2873,17 +2889,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2897,34 +2913,34 @@
         </is>
       </c>
       <c r="F44" s="27" t="n">
-        <v>0</v>
+        <v>4842</v>
       </c>
       <c r="G44" s="27" t="n"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F45" s="27" t="n"/>
@@ -2933,67 +2949,67 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G46" s="27" t="n"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F47" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="n"/>
       <c r="G47" s="27" t="n"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3008,7 +3024,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F48" s="27" t="n"/>
@@ -3017,17 +3033,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3041,7 +3057,7 @@
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>5345</v>
+        <v>12641</v>
       </c>
       <c r="G49" s="27" t="n"/>
       <c r="H49" t="inlineStr">
@@ -3053,22 +3069,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F50" s="27" t="n"/>
@@ -3077,7 +3093,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3092,69 +3108,67 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G51" s="27" t="n"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G52" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n"/>
+      <c r="G52" s="27" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3163,82 +3177,84 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="n"/>
-      <c r="G54" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G54" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n"/>
       <c r="G55" s="27" t="n"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F56" s="27" t="n"/>
@@ -3247,7 +3263,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3262,136 +3278,148 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G57" s="27" t="n"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F58" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="n"/>
       <c r="G58" s="27" t="n"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n"/>
       <c r="G59" s="27" t="n"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G60" s="27" t="n"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F61" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G61" s="27" t="n"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3406,7 +3434,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F62" s="27" t="n"/>
@@ -3415,53 +3443,41 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F63" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="n"/>
       <c r="G63" s="27" t="n"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3475,46 +3491,58 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G65" s="27" t="n"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F66" s="27" t="n"/>
@@ -3523,7 +3551,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3547,7 +3575,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3571,7 +3599,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3586,7 +3614,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F69" s="27" t="n"/>
@@ -3595,7 +3623,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3610,7 +3638,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F70" s="27" t="n"/>
@@ -3619,22 +3647,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
@@ -3643,22 +3671,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F72" s="27" t="n"/>
@@ -3667,7 +3695,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3682,7 +3710,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F73" s="27" t="n"/>
@@ -3691,7 +3719,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3715,7 +3743,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3739,7 +3767,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3763,7 +3791,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3778,7 +3806,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F77" s="27" t="n"/>
@@ -3787,7 +3815,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3802,7 +3830,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F78" s="27" t="n"/>
@@ -3811,7 +3839,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3826,11 +3854,59 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F79" s="27" t="n"/>
       <c r="G79" s="27" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F80" s="27" t="n"/>
+      <c r="G80" s="27" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F81" s="27" t="n"/>
+      <c r="G81" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-27 12:43 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-27 18:18 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1010,7 +1010,7 @@
         <v>15809</v>
       </c>
       <c r="L6" s="23" t="n">
-        <v>311</v>
+        <v>1401</v>
       </c>
       <c r="M6" s="23" t="n"/>
       <c r="N6" s="23" t="n"/>
@@ -1203,10 +1203,18 @@
       <c r="G10" s="22" t="n">
         <v>9097</v>
       </c>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="23" t="n"/>
+      <c r="H10" s="22" t="n">
+        <v>4947</v>
+      </c>
+      <c r="I10" s="22" t="n">
+        <v>3787</v>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>307</v>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>4640</v>
+      </c>
       <c r="L10" s="23" t="n"/>
       <c r="M10" s="23" t="n"/>
       <c r="N10" s="23" t="n"/>
@@ -1417,7 +1425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1475,7 +1483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1499,9 +1507,11 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
+        <v>1401</v>
+      </c>
+      <c r="G2" s="27" t="n">
         <v>311</v>
       </c>
-      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>app</t>
@@ -1511,17 +1521,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1535,11 +1545,9 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>4640</v>
+      </c>
+      <c r="G3" s="27" t="n"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>app</t>
@@ -1549,41 +1557,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>307</v>
+      </c>
       <c r="G4" s="27" t="n"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1593,15 +1613,13 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>911</v>
-      </c>
+        <v>3787</v>
+      </c>
+      <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>app</t>
@@ -1611,17 +1629,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1631,23 +1649,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>8300</v>
+        <v>4947</v>
       </c>
       <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1667,15 +1685,13 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>app</t>
@@ -1685,7 +1701,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1709,9 +1725,11 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>351</v>
-      </c>
-      <c r="G8" s="27" t="n"/>
+        <v>15809</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>1157</v>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>app</t>
@@ -1721,7 +1739,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1736,30 +1754,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>3510</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="27" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1779,14 +1783,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>3510</v>
+        <v>1157</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>351</v>
+        <v>911</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1797,7 +1801,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1817,11 +1821,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>13001</v>
+        <v>8300</v>
       </c>
       <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
@@ -1833,7 +1837,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1853,13 +1857,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="G12" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1869,7 +1875,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1884,16 +1890,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G13" s="27" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1913,14 +1931,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>8060</v>
+        <v>20274</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>122</v>
+        <v>3510</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1931,17 +1949,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1951,33 +1969,35 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G15" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1987,25 +2007,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>13001</v>
+      </c>
+      <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2025,15 +2043,13 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>121</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>120</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>app</t>
@@ -2043,7 +2059,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2058,28 +2074,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>120</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n"/>
       <c r="G18" s="27" t="n"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2099,14 +2103,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>8981</v>
+        <v>8060</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>2680</v>
+        <v>122</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2117,31 +2121,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>7493</v>
+      </c>
       <c r="G20" s="27" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2161,14 +2177,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>2680</v>
+        <v>122</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>2650</v>
+        <v>121</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2179,17 +2195,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2199,13 +2215,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G22" s="27" t="n"/>
+        <v>121</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>120</v>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>app</t>
@@ -2215,17 +2233,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2235,15 +2253,13 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G23" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G23" s="27" t="n"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>app</t>
@@ -2253,17 +2269,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2273,14 +2289,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>4189</v>
+        <v>8981</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>0</v>
+        <v>2680</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2291,45 +2307,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>3685</v>
-      </c>
-      <c r="G25" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="27" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2353,10 +2355,10 @@
         </is>
       </c>
       <c r="F26" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="G26" s="27" t="n">
         <v>2650</v>
-      </c>
-      <c r="G26" s="27" t="n">
-        <v>831</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2367,7 +2369,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2387,33 +2389,33 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>0</v>
+        <v>4933</v>
       </c>
       <c r="G27" s="27" t="n"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2423,14 +2425,14 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F28" s="27" t="n">
-        <v>831</v>
+        <v>7567</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2441,41 +2443,55 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>4189</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2489,19 +2505,21 @@
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>387</v>
-      </c>
-      <c r="G30" s="27" t="n"/>
+        <v>3685</v>
+      </c>
+      <c r="G30" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2521,14 +2539,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F31" s="27" t="n">
-        <v>9720</v>
+        <v>2650</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>1100</v>
+        <v>831</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2539,17 +2557,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2559,62 +2577,76 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F32" s="27" t="n">
-        <v>9097</v>
+        <v>0</v>
       </c>
       <c r="G32" s="27" t="n"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F34" s="27" t="n"/>
@@ -2623,17 +2655,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2643,11 +2675,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>10808</v>
+        <v>387</v>
       </c>
       <c r="G35" s="27" t="n"/>
       <c r="H35" t="inlineStr">
@@ -2659,17 +2691,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2683,43 +2715,57 @@
         </is>
       </c>
       <c r="F36" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G37" s="27" t="n"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2734,7 +2780,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F38" s="27" t="n"/>
@@ -2743,22 +2789,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F39" s="27" t="n"/>
@@ -2767,17 +2813,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2787,11 +2833,11 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F40" s="27" t="n">
-        <v>1100</v>
+        <v>10808</v>
       </c>
       <c r="G40" s="27" t="n"/>
       <c r="H40" t="inlineStr">
@@ -2803,17 +2849,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2823,40 +2869,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F41" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G41" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G41" s="27" t="n"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2865,22 +2909,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F43" s="27" t="n"/>
@@ -2889,43 +2933,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n"/>
       <c r="G44" s="27" t="n"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2940,26 +2972,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G45" s="27" t="n"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2973,34 +3017,36 @@
         </is>
       </c>
       <c r="F46" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="27" t="n"/>
+        <v>18461</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>1985</v>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F47" s="27" t="n"/>
@@ -3009,22 +3055,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F48" s="27" t="n"/>
@@ -3033,17 +3079,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3053,11 +3099,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>12641</v>
+        <v>4842</v>
       </c>
       <c r="G49" s="27" t="n"/>
       <c r="H49" t="inlineStr">
@@ -3069,22 +3115,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F50" s="27" t="n"/>
@@ -3093,17 +3139,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3113,38 +3159,38 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F51" s="27" t="n">
-        <v>5345</v>
+        <v>0</v>
       </c>
       <c r="G51" s="27" t="n"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F52" s="27" t="n"/>
@@ -3153,22 +3199,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3177,17 +3223,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3197,15 +3243,13 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F54" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G54" s="27" t="n">
-        <v>100</v>
-      </c>
+        <v>12641</v>
+      </c>
+      <c r="G54" s="27" t="n"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>app</t>
@@ -3215,22 +3259,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
@@ -3239,82 +3283,82 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G56" s="27" t="n"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="n"/>
       <c r="G57" s="27" t="n"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3323,142 +3367,144 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G59" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n"/>
       <c r="G60" s="27" t="n"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F61" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="n"/>
       <c r="G61" s="27" t="n"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F62" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G62" s="27" t="n"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3467,17 +3513,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3491,17 +3537,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3511,11 +3557,11 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F65" s="27" t="n">
-        <v>6310</v>
+        <v>100</v>
       </c>
       <c r="G65" s="27" t="n"/>
       <c r="H65" t="inlineStr">
@@ -3527,46 +3573,58 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F66" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G66" s="27" t="n"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F67" s="27" t="n"/>
@@ -3575,22 +3633,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F68" s="27" t="n"/>
@@ -3599,17 +3657,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3623,46 +3681,58 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G70" s="27" t="n"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
@@ -3671,7 +3741,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3695,22 +3765,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F73" s="27" t="n"/>
@@ -3719,22 +3789,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F74" s="27" t="n"/>
@@ -3743,22 +3813,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F75" s="27" t="n"/>
@@ -3767,22 +3837,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F76" s="27" t="n"/>
@@ -3791,22 +3861,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F77" s="27" t="n"/>
@@ -3815,7 +3885,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3839,7 +3909,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3863,7 +3933,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3878,7 +3948,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F80" s="27" t="n"/>
@@ -3887,7 +3957,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3902,11 +3972,131 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F81" s="27" t="n"/>
       <c r="G81" s="27" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:22:11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="F82" s="27" t="n"/>
+      <c r="G82" s="27" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:20:27</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F83" s="27" t="n"/>
+      <c r="G83" s="27" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F84" s="27" t="n"/>
+      <c r="G84" s="27" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F85" s="27" t="n"/>
+      <c r="G85" s="27" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F86" s="27" t="n"/>
+      <c r="G86" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-27 18:18 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-28 07:03 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1010,9 +1010,11 @@
         <v>15809</v>
       </c>
       <c r="L6" s="23" t="n">
-        <v>1401</v>
-      </c>
-      <c r="M6" s="23" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="M6" s="23" t="n">
+        <v>271</v>
+      </c>
       <c r="N6" s="23" t="n"/>
       <c r="O6" s="23" t="n"/>
       <c r="P6" s="23" t="n"/>
@@ -1258,12 +1260,24 @@
       <c r="F11" s="22" t="n">
         <v>10808</v>
       </c>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="22" t="n"/>
-      <c r="I11" s="22" t="n"/>
-      <c r="J11" s="22" t="n"/>
-      <c r="K11" s="23" t="n"/>
-      <c r="L11" s="23" t="n"/>
+      <c r="G11" s="22" t="n">
+        <v>13681</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>11109</v>
+      </c>
+      <c r="I11" s="22" t="n">
+        <v>10595</v>
+      </c>
+      <c r="J11" s="22" t="n">
+        <v>10320</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>10300</v>
+      </c>
+      <c r="L11" s="23" t="n">
+        <v>12221</v>
+      </c>
       <c r="M11" s="23" t="n"/>
       <c r="N11" s="23" t="n"/>
       <c r="O11" s="23" t="n"/>
@@ -1425,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1483,7 +1497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1503,15 +1517,13 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>app</t>
@@ -1521,17 +1533,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1541,13 +1553,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G3" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>app</t>
@@ -1557,17 +1571,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1581,7 +1595,7 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>307</v>
+        <v>10320</v>
       </c>
       <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
@@ -1593,17 +1607,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1613,11 +1627,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>3787</v>
+        <v>12221</v>
       </c>
       <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
@@ -1629,17 +1643,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1649,11 +1663,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>4947</v>
+        <v>10300</v>
       </c>
       <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
@@ -1665,17 +1679,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1685,11 +1699,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>311</v>
+        <v>10595</v>
       </c>
       <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
@@ -1701,17 +1715,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1721,15 +1735,13 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>11109</v>
+      </c>
+      <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>app</t>
@@ -1739,31 +1751,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>13681</v>
+      </c>
       <c r="G9" s="27" t="n"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1783,14 +1807,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>1157</v>
+        <v>1401</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>911</v>
+        <v>311</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1801,17 +1825,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1825,29 +1849,29 @@
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>8300</v>
+        <v>4640</v>
       </c>
       <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1857,15 +1881,13 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1875,17 +1897,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1895,11 +1917,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>351</v>
+        <v>3787</v>
       </c>
       <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
@@ -1911,17 +1933,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1931,15 +1953,13 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>4947</v>
+      </c>
+      <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>app</t>
@@ -1949,7 +1969,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1969,15 +1989,13 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>3510</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>app</t>
@@ -1987,17 +2005,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2007,23 +2025,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G16" s="27" t="n"/>
+        <v>15809</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>1157</v>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2038,28 +2058,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>351</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n"/>
       <c r="G17" s="27" t="n"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2074,26 +2082,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2103,35 +2125,33 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>122</v>
-      </c>
+        <v>8300</v>
+      </c>
+      <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2141,23 +2161,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G20" s="27" t="n"/>
+        <v>911</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2177,15 +2199,13 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G21" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>app</t>
@@ -2195,7 +2215,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,14 +2235,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>121</v>
+        <v>20274</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>120</v>
+        <v>3510</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2233,7 +2253,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2253,13 +2273,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>120</v>
-      </c>
-      <c r="G23" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G23" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>app</t>
@@ -2269,17 +2291,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2289,25 +2311,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G24" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>13001</v>
+      </c>
+      <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2322,16 +2342,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G25" s="27" t="n"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2346,40 +2378,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G26" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="27" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2389,13 +2407,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G27" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>app</t>
@@ -2405,7 +2425,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2425,35 +2445,33 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F28" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G28" s="27" t="n"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2463,14 +2481,14 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F29" s="27" t="n">
-        <v>4189</v>
+        <v>122</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2481,17 +2499,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2501,25 +2519,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>3685</v>
+        <v>121</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2539,15 +2557,13 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F31" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="G31" s="27" t="n">
-        <v>831</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G31" s="27" t="n"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>app</t>
@@ -2557,17 +2573,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2581,19 +2597,21 @@
         </is>
       </c>
       <c r="F32" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="27" t="n"/>
+        <v>8981</v>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>2680</v>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2608,30 +2626,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G33" s="27" t="n">
-        <v>387</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="27" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2646,26 +2650,40 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>2650</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2675,11 +2693,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>387</v>
+        <v>4933</v>
       </c>
       <c r="G35" s="27" t="n"/>
       <c r="H35" t="inlineStr">
@@ -2691,17 +2709,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2711,14 +2729,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F36" s="27" t="n">
-        <v>9720</v>
+        <v>7567</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2729,17 +2747,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2753,9 +2771,11 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G37" s="27" t="n"/>
+        <v>4189</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>app</t>
@@ -2765,65 +2785,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G38" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G39" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2833,33 +2881,33 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F40" s="27" t="n">
-        <v>10808</v>
+        <v>0</v>
       </c>
       <c r="G40" s="27" t="n"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2869,38 +2917,40 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F41" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="27" t="n"/>
+        <v>831</v>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>387</v>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F42" s="27" t="n"/>
@@ -2909,31 +2959,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n">
+        <v>387</v>
+      </c>
       <c r="G43" s="27" t="n"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2948,26 +3010,40 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>9720</v>
+      </c>
+      <c r="G44" s="27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2981,7 +3057,7 @@
         </is>
       </c>
       <c r="F45" s="27" t="n">
-        <v>1100</v>
+        <v>9097</v>
       </c>
       <c r="G45" s="27" t="n"/>
       <c r="H45" t="inlineStr">
@@ -2993,60 +3069,46 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G46" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n"/>
+      <c r="G46" s="27" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F47" s="27" t="n"/>
@@ -3055,41 +3117,53 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G48" s="27" t="n"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3099,38 +3173,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>4842</v>
+        <v>0</v>
       </c>
       <c r="G49" s="27" t="n"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F50" s="27" t="n"/>
@@ -3139,58 +3213,46 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F52" s="27" t="n"/>
@@ -3199,41 +3261,53 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F53" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G53" s="27" t="n"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3243,13 +3317,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F54" s="27" t="n">
-        <v>12641</v>
-      </c>
-      <c r="G54" s="27" t="n"/>
+        <v>18461</v>
+      </c>
+      <c r="G54" s="27" t="n">
+        <v>1985</v>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>app</t>
@@ -3259,22 +3335,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
@@ -3283,43 +3359,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n"/>
       <c r="G56" s="27" t="n"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3334,31 +3398,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G57" s="27" t="n"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3367,17 +3443,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3391,36 +3467,34 @@
         </is>
       </c>
       <c r="F59" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G59" s="27" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G59" s="27" t="n"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F60" s="27" t="n"/>
@@ -3429,22 +3503,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3453,17 +3527,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3477,7 +3551,7 @@
         </is>
       </c>
       <c r="F62" s="27" t="n">
-        <v>10383</v>
+        <v>12641</v>
       </c>
       <c r="G62" s="27" t="n"/>
       <c r="H62" t="inlineStr">
@@ -3489,22 +3563,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3513,137 +3587,139 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F64" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G64" s="27" t="n"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="n"/>
       <c r="G65" s="27" t="n"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F66" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="n"/>
       <c r="G66" s="27" t="n"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="n"/>
-      <c r="G67" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G67" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3657,17 +3733,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3681,17 +3757,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3705,7 +3781,7 @@
         </is>
       </c>
       <c r="F70" s="27" t="n">
-        <v>6310</v>
+        <v>10383</v>
       </c>
       <c r="G70" s="27" t="n"/>
       <c r="H70" t="inlineStr">
@@ -3717,22 +3793,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
@@ -3741,17 +3817,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3765,70 +3841,94 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G73" s="27" t="n"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G74" s="27" t="n"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F75" s="27" t="n"/>
@@ -3837,22 +3937,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F76" s="27" t="n"/>
@@ -3861,17 +3961,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3885,46 +3985,58 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F78" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G78" s="27" t="n"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F79" s="27" t="n"/>
@@ -3933,22 +4045,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F80" s="27" t="n"/>
@@ -3957,22 +4069,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F81" s="27" t="n"/>
@@ -3981,22 +4093,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F82" s="27" t="n"/>
@@ -4005,22 +4117,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F83" s="27" t="n"/>
@@ -4029,22 +4141,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F84" s="27" t="n"/>
@@ -4053,22 +4165,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F85" s="27" t="n"/>
@@ -4077,7 +4189,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4092,11 +4204,203 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F86" s="27" t="n"/>
       <c r="G86" s="27" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:41:34</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F87" s="27" t="n"/>
+      <c r="G87" s="27" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:41:28</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="F88" s="27" t="n"/>
+      <c r="G88" s="27" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:27:02</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F89" s="27" t="n"/>
+      <c r="G89" s="27" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:22:11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="F90" s="27" t="n"/>
+      <c r="G90" s="27" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:20:27</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F91" s="27" t="n"/>
+      <c r="G91" s="27" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:58:34</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F92" s="27" t="n"/>
+      <c r="G92" s="27" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F93" s="27" t="n"/>
+      <c r="G93" s="27" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F94" s="27" t="n"/>
+      <c r="G94" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-28 07:03 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-28 19:15 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1013,7 +1013,7 @@
         <v>9670</v>
       </c>
       <c r="M6" s="23" t="n">
-        <v>271</v>
+        <v>371</v>
       </c>
       <c r="N6" s="23" t="n"/>
       <c r="O6" s="23" t="n"/>
@@ -1439,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1497,7 +1497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1521,9 +1521,11 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G2" s="27" t="n">
         <v>271</v>
       </c>
-      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>app</t>
@@ -1533,7 +1535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1548,40 +1550,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n"/>
+      <c r="G3" s="27" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1591,11 +1579,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>10320</v>
+        <v>271</v>
       </c>
       <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
@@ -1607,17 +1595,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1631,9 +1619,11 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>12221</v>
-      </c>
-      <c r="G5" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>app</t>
@@ -1643,7 +1633,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1663,11 +1653,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>10300</v>
+        <v>10320</v>
       </c>
       <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
@@ -1679,7 +1669,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1699,11 +1689,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>10595</v>
+        <v>12221</v>
       </c>
       <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
@@ -1715,7 +1705,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1735,11 +1725,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>11109</v>
+        <v>10300</v>
       </c>
       <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
@@ -1751,7 +1741,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1771,11 +1761,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>13681</v>
+        <v>10595</v>
       </c>
       <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
@@ -1787,17 +1777,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1807,15 +1797,13 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>11109</v>
+      </c>
+      <c r="G10" s="27" t="n"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>app</t>
@@ -1825,17 +1813,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1845,11 +1833,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>4640</v>
+        <v>13681</v>
       </c>
       <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
@@ -1861,17 +1849,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1881,13 +1869,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>307</v>
-      </c>
-      <c r="G12" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1897,7 +1887,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1917,11 +1907,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>3787</v>
+        <v>4640</v>
       </c>
       <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
@@ -1933,7 +1923,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1953,11 +1943,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>4947</v>
+        <v>307</v>
       </c>
       <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
@@ -1969,17 +1959,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1989,11 +1979,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>311</v>
+        <v>3787</v>
       </c>
       <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
@@ -2005,17 +1995,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2025,15 +2015,13 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>4947</v>
+      </c>
+      <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>app</t>
@@ -2043,7 +2031,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2058,16 +2046,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="G17" s="27" t="n"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="F18" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G18" s="27" t="n">
         <v>1157</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>911</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2105,43 +2105,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>8300</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n"/>
       <c r="G19" s="27" t="n"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2165,10 +2153,10 @@
         </is>
       </c>
       <c r="F20" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="G20" s="27" t="n">
         <v>911</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2179,17 +2167,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2203,19 +2191,19 @@
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>351</v>
+        <v>8300</v>
       </c>
       <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2235,14 +2223,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>20274</v>
+        <v>911</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>3510</v>
+        <v>351</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2253,7 +2241,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2273,15 +2261,13 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>3510</v>
-      </c>
-      <c r="G23" s="27" t="n">
         <v>351</v>
       </c>
+      <c r="G23" s="27" t="n"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>app</t>
@@ -2291,17 +2277,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2315,19 +2301,21 @@
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G24" s="27" t="n"/>
+        <v>20274</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>3510</v>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2351,9 +2339,11 @@
         </is>
       </c>
       <c r="F25" s="27" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G25" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G25" s="27" t="n"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>app</t>
@@ -2363,31 +2353,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>13001</v>
+      </c>
       <c r="G26" s="27" t="n"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2407,15 +2409,13 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G27" s="27" t="n">
-        <v>122</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G27" s="27" t="n"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>app</t>
@@ -2425,43 +2425,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="n">
-        <v>7493</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n"/>
       <c r="G28" s="27" t="n"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2485,10 +2473,10 @@
         </is>
       </c>
       <c r="F29" s="27" t="n">
+        <v>8060</v>
+      </c>
+      <c r="G29" s="27" t="n">
         <v>122</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>121</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2499,17 +2487,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2523,21 +2511,19 @@
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>121</v>
-      </c>
-      <c r="G30" s="27" t="n">
-        <v>120</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2561,9 +2547,11 @@
         </is>
       </c>
       <c r="F31" s="27" t="n">
-        <v>120</v>
-      </c>
-      <c r="G31" s="27" t="n"/>
+        <v>122</v>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>121</v>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>app</t>
@@ -2573,7 +2561,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2593,14 +2581,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F32" s="27" t="n">
-        <v>8981</v>
+        <v>121</v>
       </c>
       <c r="G32" s="27" t="n">
-        <v>2680</v>
+        <v>120</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2611,7 +2599,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2626,16 +2614,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>120</v>
+      </c>
       <c r="G33" s="27" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="F34" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G34" s="27" t="n">
         <v>2680</v>
-      </c>
-      <c r="G34" s="27" t="n">
-        <v>2650</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2673,53 +2673,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n">
-        <v>4933</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n"/>
       <c r="G35" s="27" t="n"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2729,14 +2717,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F36" s="27" t="n">
-        <v>7567</v>
+        <v>2680</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>0</v>
+        <v>2650</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2747,7 +2735,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2767,15 +2755,13 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>4189</v>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G37" s="27" t="n"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>app</t>
@@ -2785,7 +2771,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2805,35 +2791,35 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F38" s="27" t="n">
-        <v>3685</v>
+        <v>7567</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2843,14 +2829,14 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F39" s="27" t="n">
-        <v>2650</v>
+        <v>4189</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2861,7 +2847,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2885,9 +2871,11 @@
         </is>
       </c>
       <c r="F40" s="27" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G40" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="27" t="n"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>shortcut</t>
@@ -2897,7 +2885,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2921,10 +2909,10 @@
         </is>
       </c>
       <c r="F41" s="27" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G41" s="27" t="n">
         <v>831</v>
-      </c>
-      <c r="G41" s="27" t="n">
-        <v>387</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2935,31 +2923,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G42" s="27" t="n"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2983,9 +2983,11 @@
         </is>
       </c>
       <c r="F43" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G43" s="27" t="n">
         <v>387</v>
       </c>
-      <c r="G43" s="27" t="n"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>app</t>
@@ -2995,7 +2997,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3010,40 +3012,26 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G44" s="27" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="27" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3053,11 +3041,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F45" s="27" t="n">
-        <v>9097</v>
+        <v>387</v>
       </c>
       <c r="G45" s="27" t="n"/>
       <c r="H45" t="inlineStr">
@@ -3069,190 +3057,216 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n"/>
-      <c r="G46" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>9720</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F47" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G47" s="27" t="n"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n"/>
       <c r="G48" s="27" t="n"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F49" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="n"/>
       <c r="G49" s="27" t="n"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F50" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G50" s="27" t="n"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G51" s="27" t="n"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F52" s="27" t="n"/>
@@ -3261,43 +3275,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F53" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="n"/>
       <c r="G53" s="27" t="n"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3312,30 +3314,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G54" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n"/>
+      <c r="G54" s="27" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3350,16 +3338,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G55" s="27" t="n"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3374,52 +3374,54 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="n"/>
-      <c r="G56" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G56" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="n"/>
       <c r="G57" s="27" t="n"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3434,7 +3436,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3443,17 +3445,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3467,34 +3469,34 @@
         </is>
       </c>
       <c r="F59" s="27" t="n">
-        <v>0</v>
+        <v>4842</v>
       </c>
       <c r="G59" s="27" t="n"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F60" s="27" t="n"/>
@@ -3503,67 +3505,67 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F61" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G61" s="27" t="n"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F62" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="n"/>
       <c r="G62" s="27" t="n"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3578,7 +3580,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3587,17 +3589,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3611,7 +3613,7 @@
         </is>
       </c>
       <c r="F64" s="27" t="n">
-        <v>5345</v>
+        <v>12641</v>
       </c>
       <c r="G64" s="27" t="n"/>
       <c r="H64" t="inlineStr">
@@ -3623,22 +3625,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F65" s="27" t="n"/>
@@ -3647,7 +3649,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3662,69 +3664,67 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F66" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G66" s="27" t="n"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G67" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="n"/>
+      <c r="G67" s="27" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F68" s="27" t="n"/>
@@ -3733,82 +3733,84 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n"/>
-      <c r="G69" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G69" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n"/>
       <c r="G70" s="27" t="n"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
@@ -3817,7 +3819,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3832,136 +3834,148 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F72" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G72" s="27" t="n"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="n"/>
       <c r="G73" s="27" t="n"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="n"/>
       <c r="G74" s="27" t="n"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G75" s="27" t="n"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F76" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G76" s="27" t="n"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3976,7 +3990,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F77" s="27" t="n"/>
@@ -3985,53 +3999,41 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F78" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="n"/>
       <c r="G78" s="27" t="n"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4045,46 +4047,58 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F80" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F80" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G80" s="27" t="n"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F81" s="27" t="n"/>
@@ -4093,7 +4107,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4117,7 +4131,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4141,7 +4155,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4156,7 +4170,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F84" s="27" t="n"/>
@@ -4165,7 +4179,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4180,7 +4194,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F85" s="27" t="n"/>
@@ -4189,22 +4203,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F86" s="27" t="n"/>
@@ -4213,22 +4227,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F87" s="27" t="n"/>
@@ -4237,7 +4251,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4252,7 +4266,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F88" s="27" t="n"/>
@@ -4261,7 +4275,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4285,7 +4299,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4309,7 +4323,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4333,7 +4347,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4348,7 +4362,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F92" s="27" t="n"/>
@@ -4357,7 +4371,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4372,7 +4386,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F93" s="27" t="n"/>
@@ -4381,7 +4395,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4396,11 +4410,59 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F94" s="27" t="n"/>
       <c r="G94" s="27" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F95" s="27" t="n"/>
+      <c r="G95" s="27" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F96" s="27" t="n"/>
+      <c r="G96" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-28 19:15 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-28 21:28 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1497,7 +1497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:45:48</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1512,30 +1512,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>271</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n"/>
+      <c r="G2" s="27" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28 10:22:51</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1550,16 +1536,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n"/>
-      <c r="G3" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>271</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1574,28 +1574,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>271</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n"/>
       <c r="G4" s="27" t="n"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1615,15 +1603,13 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>1401</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>app</t>
@@ -1633,17 +1619,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1653,13 +1639,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>10320</v>
-      </c>
-      <c r="G6" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>app</t>
@@ -1669,7 +1657,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1689,11 +1677,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>12221</v>
+        <v>10320</v>
       </c>
       <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
@@ -1705,7 +1693,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1725,11 +1713,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>10300</v>
+        <v>12221</v>
       </c>
       <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
@@ -1741,7 +1729,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1761,11 +1749,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>10595</v>
+        <v>10300</v>
       </c>
       <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
@@ -1777,7 +1765,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1797,11 +1785,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>11109</v>
+        <v>10595</v>
       </c>
       <c r="G10" s="27" t="n"/>
       <c r="H10" t="inlineStr">
@@ -1813,7 +1801,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1833,11 +1821,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>13681</v>
+        <v>11109</v>
       </c>
       <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
@@ -1849,17 +1837,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1869,15 +1857,13 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>13681</v>
+      </c>
+      <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1887,17 +1873,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1907,13 +1893,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G13" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>app</t>
@@ -1923,7 +1911,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1943,11 +1931,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>307</v>
+        <v>4640</v>
       </c>
       <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
@@ -1959,7 +1947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1979,11 +1967,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>3787</v>
+        <v>307</v>
       </c>
       <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
@@ -1995,7 +1983,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2015,11 +2003,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>4947</v>
+        <v>3787</v>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
@@ -2031,17 +2019,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2051,11 +2039,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>311</v>
+        <v>4947</v>
       </c>
       <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
@@ -2067,7 +2055,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2087,15 +2075,13 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>app</t>
@@ -2105,7 +2091,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2120,16 +2106,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2144,40 +2144,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2191,29 +2177,31 @@
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>8300</v>
-      </c>
-      <c r="G21" s="27" t="n"/>
+        <v>1157</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>911</v>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2227,21 +2215,19 @@
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G22" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>8300</v>
+      </c>
+      <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2265,9 +2251,11 @@
         </is>
       </c>
       <c r="F23" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="G23" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G23" s="27" t="n"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>app</t>
@@ -2277,7 +2265,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2297,15 +2285,13 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G24" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>app</t>
@@ -2315,7 +2301,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2339,10 +2325,10 @@
         </is>
       </c>
       <c r="F25" s="27" t="n">
+        <v>20274</v>
+      </c>
+      <c r="G25" s="27" t="n">
         <v>3510</v>
-      </c>
-      <c r="G25" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2353,17 +2339,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2377,29 +2363,31 @@
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G26" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G26" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2413,19 +2401,19 @@
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>351</v>
+        <v>13001</v>
       </c>
       <c r="G27" s="27" t="n"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2440,16 +2428,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G28" s="27" t="n"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2464,40 +2464,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="27" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2511,29 +2497,31 @@
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G30" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G30" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2547,21 +2535,19 @@
         </is>
       </c>
       <c r="F31" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G31" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G31" s="27" t="n"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2585,10 +2571,10 @@
         </is>
       </c>
       <c r="F32" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G32" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G32" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2599,7 +2585,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2623,9 +2609,11 @@
         </is>
       </c>
       <c r="F33" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G33" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G33" s="27" t="n"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>app</t>
@@ -2635,7 +2623,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2655,15 +2643,13 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F34" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G34" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G34" s="27" t="n"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>app</t>
@@ -2673,7 +2659,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2688,16 +2674,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n"/>
-      <c r="G35" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2712,40 +2712,26 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G36" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2755,13 +2741,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G37" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>app</t>
@@ -2771,7 +2759,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2791,15 +2779,13 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F38" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G38" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G38" s="27" t="n"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>app</t>
@@ -2809,7 +2795,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2829,11 +2815,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F39" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>0</v>
@@ -2847,7 +2833,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2867,35 +2853,35 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F40" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2909,31 +2895,31 @@
         </is>
       </c>
       <c r="F41" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2947,29 +2933,31 @@
         </is>
       </c>
       <c r="F42" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G42" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2983,21 +2971,19 @@
         </is>
       </c>
       <c r="F43" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G43" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G43" s="27" t="n"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3012,16 +2998,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G44" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3036,28 +3036,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n"/>
       <c r="G45" s="27" t="n"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3077,15 +3065,13 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F46" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G46" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G46" s="27" t="n"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>app</t>
@@ -3095,17 +3081,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3119,9 +3105,11 @@
         </is>
       </c>
       <c r="F47" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G47" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G47" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>app</t>
@@ -3131,31 +3119,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G48" s="27" t="n"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F49" s="27" t="n"/>
@@ -3179,53 +3179,41 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F50" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="n"/>
       <c r="G50" s="27" t="n"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3235,47 +3223,59 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F51" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G51" s="27" t="n"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G52" s="27" t="n"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3299,22 +3299,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F54" s="27" t="n"/>
@@ -3323,7 +3323,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3338,28 +3338,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n"/>
       <c r="G55" s="27" t="n"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3379,15 +3367,13 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F56" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G56" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G56" s="27" t="n"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>app</t>
@@ -3397,7 +3383,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3412,16 +3398,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="n"/>
-      <c r="G57" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G57" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3445,103 +3445,91 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n"/>
       <c r="G59" s="27" t="n"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G60" s="27" t="n"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F61" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="n"/>
       <c r="G61" s="27" t="n"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3556,31 +3544,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F62" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G62" s="27" t="n"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3589,7 +3589,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3604,28 +3604,16 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F64" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="n"/>
       <c r="G64" s="27" t="n"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3640,52 +3628,52 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G65" s="27" t="n"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F66" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="n"/>
       <c r="G66" s="27" t="n"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3700,16 +3688,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G67" s="27" t="n"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F68" s="27" t="n"/>
@@ -3733,69 +3733,69 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G69" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n"/>
+      <c r="G69" s="27" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n"/>
-      <c r="G70" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G70" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
@@ -3819,43 +3819,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F72" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="n"/>
       <c r="G72" s="27" t="n"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3870,16 +3858,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G73" s="27" t="n"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F74" s="27" t="n"/>
@@ -3903,43 +3903,31 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="n"/>
       <c r="G75" s="27" t="n"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3959,11 +3947,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F76" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G76" s="27" t="n"/>
       <c r="H76" t="inlineStr">
@@ -3975,31 +3963,43 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F77" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F77" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G77" s="27" t="n"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F78" s="27" t="n"/>
@@ -4023,7 +4023,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F79" s="27" t="n"/>
@@ -4047,43 +4047,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F80" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F80" s="27" t="n"/>
       <c r="G80" s="27" t="n"/>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4098,26 +4086,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F81" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F81" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G81" s="27" t="n"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4131,7 +4131,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F83" s="27" t="n"/>
@@ -4155,7 +4155,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F84" s="27" t="n"/>
@@ -4179,7 +4179,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F85" s="27" t="n"/>
@@ -4203,7 +4203,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F86" s="27" t="n"/>
@@ -4227,7 +4227,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F87" s="27" t="n"/>
@@ -4251,22 +4251,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F88" s="27" t="n"/>
@@ -4275,7 +4275,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4299,7 +4299,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F90" s="27" t="n"/>
@@ -4323,7 +4323,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F91" s="27" t="n"/>
@@ -4347,7 +4347,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F92" s="27" t="n"/>
@@ -4371,7 +4371,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F93" s="27" t="n"/>
@@ -4395,7 +4395,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4419,7 +4419,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F95" s="27" t="n"/>
@@ -4443,7 +4443,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4458,11 +4458,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F96" s="27" t="n"/>
       <c r="G96" s="27" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F97" s="27" t="n"/>
+      <c r="G97" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-28 21:28 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-28 23:50 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1013,7 +1013,7 @@
         <v>9670</v>
       </c>
       <c r="M6" s="23" t="n">
-        <v>371</v>
+        <v>2371</v>
       </c>
       <c r="N6" s="23" t="n"/>
       <c r="O6" s="23" t="n"/>
@@ -1439,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1497,7 +1497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:32</t>
+          <t>2026-10-28 23:47:44</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1512,16 +1512,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F2" s="27" t="n"/>
-      <c r="G2" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n">
+        <v>2371</v>
+      </c>
+      <c r="G2" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28 17:45:48</t>
+          <t>2026-10-28 23:46:44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1536,30 +1550,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>271</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n"/>
+      <c r="G3" s="27" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28 10:22:51</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F4" s="27" t="n"/>
@@ -1583,7 +1583,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1607,9 +1607,11 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G5" s="27" t="n">
         <v>271</v>
       </c>
-      <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>app</t>
@@ -1619,7 +1621,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1634,40 +1636,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="27" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1677,11 +1665,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>10320</v>
+        <v>271</v>
       </c>
       <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
@@ -1693,17 +1681,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1717,9 +1705,11 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>12221</v>
-      </c>
-      <c r="G8" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>app</t>
@@ -1729,7 +1719,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1749,11 +1739,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>10300</v>
+        <v>10320</v>
       </c>
       <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
@@ -1765,7 +1755,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1785,11 +1775,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>10595</v>
+        <v>12221</v>
       </c>
       <c r="G10" s="27" t="n"/>
       <c r="H10" t="inlineStr">
@@ -1801,7 +1791,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1821,11 +1811,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>11109</v>
+        <v>10300</v>
       </c>
       <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
@@ -1837,7 +1827,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1857,11 +1847,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>13681</v>
+        <v>10595</v>
       </c>
       <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
@@ -1873,17 +1863,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1893,15 +1883,13 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>11109</v>
+      </c>
+      <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>app</t>
@@ -1911,17 +1899,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1931,11 +1919,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>4640</v>
+        <v>13681</v>
       </c>
       <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
@@ -1947,17 +1935,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1967,13 +1955,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>307</v>
-      </c>
-      <c r="G15" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>app</t>
@@ -1983,7 +1973,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2003,11 +1993,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>3787</v>
+        <v>4640</v>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
@@ -2019,7 +2009,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2039,11 +2029,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>4947</v>
+        <v>307</v>
       </c>
       <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
@@ -2055,17 +2045,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2075,11 +2065,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>311</v>
+        <v>3787</v>
       </c>
       <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
@@ -2091,17 +2081,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2111,15 +2101,13 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>4947</v>
+      </c>
+      <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>app</t>
@@ -2129,7 +2117,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2144,16 +2132,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="G20" s="27" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="F21" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G21" s="27" t="n">
         <v>1157</v>
-      </c>
-      <c r="G21" s="27" t="n">
-        <v>911</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2191,43 +2191,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>8300</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n"/>
       <c r="G22" s="27" t="n"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2251,10 +2239,10 @@
         </is>
       </c>
       <c r="F23" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="G23" s="27" t="n">
         <v>911</v>
-      </c>
-      <c r="G23" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2265,17 +2253,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2289,19 +2277,19 @@
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>351</v>
+        <v>8300</v>
       </c>
       <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2321,14 +2309,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>20274</v>
+        <v>911</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>3510</v>
+        <v>351</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2339,7 +2327,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2359,15 +2347,13 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>3510</v>
-      </c>
-      <c r="G26" s="27" t="n">
         <v>351</v>
       </c>
+      <c r="G26" s="27" t="n"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>app</t>
@@ -2377,17 +2363,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2401,19 +2387,21 @@
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G27" s="27" t="n"/>
+        <v>20274</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>3510</v>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2437,9 +2425,11 @@
         </is>
       </c>
       <c r="F28" s="27" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G28" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G28" s="27" t="n"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>app</t>
@@ -2449,31 +2439,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>13001</v>
+      </c>
       <c r="G29" s="27" t="n"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2493,15 +2495,13 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G30" s="27" t="n">
-        <v>122</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>app</t>
@@ -2511,43 +2511,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n">
-        <v>7493</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n"/>
       <c r="G31" s="27" t="n"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2571,10 +2559,10 @@
         </is>
       </c>
       <c r="F32" s="27" t="n">
+        <v>8060</v>
+      </c>
+      <c r="G32" s="27" t="n">
         <v>122</v>
-      </c>
-      <c r="G32" s="27" t="n">
-        <v>121</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2585,17 +2573,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2609,21 +2597,19 @@
         </is>
       </c>
       <c r="F33" s="27" t="n">
-        <v>121</v>
-      </c>
-      <c r="G33" s="27" t="n">
-        <v>120</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G33" s="27" t="n"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2647,9 +2633,11 @@
         </is>
       </c>
       <c r="F34" s="27" t="n">
-        <v>120</v>
-      </c>
-      <c r="G34" s="27" t="n"/>
+        <v>122</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>121</v>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>app</t>
@@ -2659,7 +2647,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2679,14 +2667,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>8981</v>
+        <v>121</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>2680</v>
+        <v>120</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2697,7 +2685,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2712,16 +2700,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>120</v>
+      </c>
       <c r="G36" s="27" t="n"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G37" s="27" t="n">
         <v>2680</v>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>2650</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2759,53 +2759,41 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>4933</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
       <c r="G38" s="27" t="n"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,14 +2803,14 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F39" s="27" t="n">
-        <v>7567</v>
+        <v>2680</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>0</v>
+        <v>2650</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2833,7 +2821,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2853,15 +2841,13 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F40" s="27" t="n">
-        <v>4189</v>
-      </c>
-      <c r="G40" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G40" s="27" t="n"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>app</t>
@@ -2871,7 +2857,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2891,35 +2877,35 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F41" s="27" t="n">
-        <v>3685</v>
+        <v>7567</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2929,14 +2915,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F42" s="27" t="n">
-        <v>2650</v>
+        <v>4189</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2947,7 +2933,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2971,9 +2957,11 @@
         </is>
       </c>
       <c r="F43" s="27" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G43" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="27" t="n"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>shortcut</t>
@@ -2983,7 +2971,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3007,10 +2995,10 @@
         </is>
       </c>
       <c r="F44" s="27" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G44" s="27" t="n">
         <v>831</v>
-      </c>
-      <c r="G44" s="27" t="n">
-        <v>387</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3021,31 +3009,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G45" s="27" t="n"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3069,9 +3069,11 @@
         </is>
       </c>
       <c r="F46" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G46" s="27" t="n">
         <v>387</v>
       </c>
-      <c r="G46" s="27" t="n"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>app</t>
@@ -3081,7 +3083,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3096,40 +3098,26 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F47" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G47" s="27" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="n"/>
+      <c r="G47" s="27" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3139,11 +3127,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F48" s="27" t="n">
-        <v>9097</v>
+        <v>387</v>
       </c>
       <c r="G48" s="27" t="n"/>
       <c r="H48" t="inlineStr">
@@ -3155,190 +3143,216 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>9720</v>
+      </c>
+      <c r="G49" s="27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F50" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G50" s="27" t="n"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n"/>
       <c r="G52" s="27" t="n"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F53" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G53" s="27" t="n"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G54" s="27" t="n"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
@@ -3347,43 +3361,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n"/>
       <c r="G56" s="27" t="n"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3398,30 +3400,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G57" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="27" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3436,16 +3424,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F58" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G58" s="27" t="n"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3460,52 +3460,54 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G59" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n"/>
       <c r="G60" s="27" t="n"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3520,7 +3522,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3529,17 +3531,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3553,34 +3555,34 @@
         </is>
       </c>
       <c r="F62" s="27" t="n">
-        <v>0</v>
+        <v>4842</v>
       </c>
       <c r="G62" s="27" t="n"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3589,67 +3591,67 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F64" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G64" s="27" t="n"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="n"/>
       <c r="G65" s="27" t="n"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3664,7 +3666,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F66" s="27" t="n"/>
@@ -3673,17 +3675,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3697,7 +3699,7 @@
         </is>
       </c>
       <c r="F67" s="27" t="n">
-        <v>5345</v>
+        <v>12641</v>
       </c>
       <c r="G67" s="27" t="n"/>
       <c r="H67" t="inlineStr">
@@ -3709,22 +3711,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F68" s="27" t="n"/>
@@ -3733,7 +3735,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3748,69 +3750,67 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G69" s="27" t="n"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G70" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n"/>
+      <c r="G70" s="27" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
@@ -3819,82 +3819,84 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F72" s="27" t="n"/>
-      <c r="G72" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G72" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="n"/>
       <c r="G73" s="27" t="n"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F74" s="27" t="n"/>
@@ -3903,7 +3905,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3918,136 +3920,148 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G75" s="27" t="n"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F76" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="n"/>
       <c r="G76" s="27" t="n"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F77" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F77" s="27" t="n"/>
       <c r="G77" s="27" t="n"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F78" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G78" s="27" t="n"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F79" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F79" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G79" s="27" t="n"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4062,7 +4076,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F80" s="27" t="n"/>
@@ -4071,53 +4085,41 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F81" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F81" s="27" t="n"/>
       <c r="G81" s="27" t="n"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4131,46 +4133,58 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F83" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F83" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G83" s="27" t="n"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F84" s="27" t="n"/>
@@ -4179,7 +4193,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4203,7 +4217,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4227,7 +4241,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4242,7 +4256,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F87" s="27" t="n"/>
@@ -4251,7 +4265,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4266,7 +4280,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F88" s="27" t="n"/>
@@ -4275,22 +4289,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F89" s="27" t="n"/>
@@ -4299,22 +4313,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F90" s="27" t="n"/>
@@ -4323,7 +4337,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4338,7 +4352,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F91" s="27" t="n"/>
@@ -4347,7 +4361,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4371,7 +4385,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4395,7 +4409,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4419,7 +4433,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4434,7 +4448,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F95" s="27" t="n"/>
@@ -4443,7 +4457,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4458,7 +4472,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F96" s="27" t="n"/>
@@ -4467,7 +4481,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4482,11 +4496,59 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F97" s="27" t="n"/>
       <c r="G97" s="27" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:19</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F98" s="27" t="n"/>
+      <c r="G98" s="27" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F99" s="27" t="n"/>
+      <c r="G99" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-28 23:50 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-29 00:19 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1116,7 +1116,9 @@
         <v>8300</v>
       </c>
       <c r="L8" s="23" t="n"/>
-      <c r="M8" s="23" t="n"/>
+      <c r="M8" s="23" t="n">
+        <v>4018</v>
+      </c>
       <c r="N8" s="23" t="n"/>
       <c r="O8" s="23" t="n"/>
       <c r="P8" s="23" t="n"/>
@@ -1439,7 +1441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1497,17 +1499,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28 23:47:44</t>
+          <t>2026-10-29 00:00:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1521,21 +1523,19 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>2371</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>371</v>
-      </c>
+        <v>4018</v>
+      </c>
+      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28 23:46:44</t>
+          <t>2026-10-28 23:47:44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1550,16 +1550,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="n"/>
-      <c r="G3" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>2371</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:32</t>
+          <t>2026-10-28 23:46:44</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1574,7 +1588,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F4" s="27" t="n"/>
@@ -1583,7 +1597,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28 17:45:48</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1598,30 +1612,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>271</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28 10:22:51</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1636,16 +1636,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>271</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1660,28 +1674,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>271</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n"/>
       <c r="G7" s="27" t="n"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1701,15 +1703,13 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>1401</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>app</t>
@@ -1719,17 +1719,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1739,13 +1739,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>10320</v>
-      </c>
-      <c r="G9" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>app</t>
@@ -1755,7 +1757,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1775,11 +1777,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>12221</v>
+        <v>10320</v>
       </c>
       <c r="G10" s="27" t="n"/>
       <c r="H10" t="inlineStr">
@@ -1791,7 +1793,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1811,11 +1813,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>10300</v>
+        <v>12221</v>
       </c>
       <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
@@ -1827,7 +1829,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1847,11 +1849,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>10595</v>
+        <v>10300</v>
       </c>
       <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
@@ -1863,7 +1865,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1883,11 +1885,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>11109</v>
+        <v>10595</v>
       </c>
       <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
@@ -1899,7 +1901,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1919,11 +1921,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>13681</v>
+        <v>11109</v>
       </c>
       <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
@@ -1935,17 +1937,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1955,15 +1957,13 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>13681</v>
+      </c>
+      <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>app</t>
@@ -1973,17 +1973,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1993,13 +1993,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G16" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>app</t>
@@ -2009,7 +2011,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2029,11 +2031,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>307</v>
+        <v>4640</v>
       </c>
       <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
@@ -2045,7 +2047,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2065,11 +2067,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>3787</v>
+        <v>307</v>
       </c>
       <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
@@ -2081,7 +2083,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2101,11 +2103,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>4947</v>
+        <v>3787</v>
       </c>
       <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
@@ -2117,17 +2119,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2137,11 +2139,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>311</v>
+        <v>4947</v>
       </c>
       <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
@@ -2153,7 +2155,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2173,15 +2175,13 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G21" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>app</t>
@@ -2191,7 +2191,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2206,16 +2206,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2230,40 +2244,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G23" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="27" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2277,29 +2277,31 @@
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>8300</v>
-      </c>
-      <c r="G24" s="27" t="n"/>
+        <v>1157</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>911</v>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2313,21 +2315,19 @@
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G25" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>8300</v>
+      </c>
+      <c r="G25" s="27" t="n"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2351,9 +2351,11 @@
         </is>
       </c>
       <c r="F26" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="G26" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G26" s="27" t="n"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>app</t>
@@ -2363,7 +2365,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2383,15 +2385,13 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G27" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G27" s="27" t="n"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>app</t>
@@ -2401,7 +2401,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="F28" s="27" t="n">
+        <v>20274</v>
+      </c>
+      <c r="G28" s="27" t="n">
         <v>3510</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2439,17 +2439,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2463,29 +2463,31 @@
         </is>
       </c>
       <c r="F29" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G29" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2499,19 +2501,19 @@
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>351</v>
+        <v>13001</v>
       </c>
       <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2526,16 +2528,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G31" s="27" t="n"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2550,40 +2564,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G32" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="27" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2597,29 +2597,31 @@
         </is>
       </c>
       <c r="F33" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G33" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2633,21 +2635,19 @@
         </is>
       </c>
       <c r="F34" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G34" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G34" s="27" t="n"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="F35" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G35" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G35" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2709,9 +2709,11 @@
         </is>
       </c>
       <c r="F36" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G36" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G36" s="27" t="n"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>app</t>
@@ -2721,7 +2723,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2741,15 +2743,13 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G37" s="27" t="n"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>app</t>
@@ -2759,7 +2759,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2774,16 +2774,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G38" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2798,40 +2812,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G39" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2841,13 +2841,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F40" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G40" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G40" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>app</t>
@@ -2857,7 +2859,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2877,15 +2879,13 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F41" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G41" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G41" s="27" t="n"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>app</t>
@@ -2895,7 +2895,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2915,11 +2915,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F42" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>0</v>
@@ -2933,7 +2933,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2953,35 +2953,35 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F43" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2995,31 +2995,31 @@
         </is>
       </c>
       <c r="F44" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3033,29 +3033,31 @@
         </is>
       </c>
       <c r="F45" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G45" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3069,21 +3071,19 @@
         </is>
       </c>
       <c r="F46" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G46" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G46" s="27" t="n"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3098,16 +3098,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G47" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3122,28 +3136,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n"/>
       <c r="G48" s="27" t="n"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3163,15 +3165,13 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G49" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G49" s="27" t="n"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>app</t>
@@ -3181,17 +3181,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3205,9 +3205,11 @@
         </is>
       </c>
       <c r="F50" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G50" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G50" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>app</t>
@@ -3217,31 +3219,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G51" s="27" t="n"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3256,7 +3270,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F52" s="27" t="n"/>
@@ -3265,53 +3279,41 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F53" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="n"/>
       <c r="G53" s="27" t="n"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3321,47 +3323,59 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F54" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G54" s="27" t="n"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G55" s="27" t="n"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3376,7 +3390,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F56" s="27" t="n"/>
@@ -3385,22 +3399,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3409,7 +3423,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3424,28 +3438,16 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F58" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="n"/>
       <c r="G58" s="27" t="n"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3465,15 +3467,13 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F59" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G59" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G59" s="27" t="n"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>app</t>
@@ -3483,7 +3483,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3498,16 +3498,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="n"/>
-      <c r="G60" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G60" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3522,7 +3536,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3531,103 +3545,91 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F62" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="n"/>
       <c r="G62" s="27" t="n"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F63" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G63" s="27" t="n"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F64" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="n"/>
       <c r="G64" s="27" t="n"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3642,31 +3644,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G65" s="27" t="n"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F66" s="27" t="n"/>
@@ -3675,7 +3689,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3690,28 +3704,16 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="n"/>
       <c r="G67" s="27" t="n"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3726,52 +3728,52 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F68" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F68" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G68" s="27" t="n"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n"/>
       <c r="G69" s="27" t="n"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3786,16 +3788,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G70" s="27" t="n"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3810,7 +3824,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
@@ -3819,69 +3833,69 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F72" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G72" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="n"/>
+      <c r="G72" s="27" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="n"/>
-      <c r="G73" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G73" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3896,7 +3910,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F74" s="27" t="n"/>
@@ -3905,43 +3919,31 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="n"/>
       <c r="G75" s="27" t="n"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3956,16 +3958,28 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F76" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G76" s="27" t="n"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3980,7 +3994,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F77" s="27" t="n"/>
@@ -3989,43 +4003,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F78" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="n"/>
       <c r="G78" s="27" t="n"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4045,11 +4047,11 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F79" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G79" s="27" t="n"/>
       <c r="H79" t="inlineStr">
@@ -4061,31 +4063,43 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F80" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F80" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G80" s="27" t="n"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4100,7 +4114,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F81" s="27" t="n"/>
@@ -4109,7 +4123,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4124,7 +4138,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F82" s="27" t="n"/>
@@ -4133,43 +4147,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F83" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F83" s="27" t="n"/>
       <c r="G83" s="27" t="n"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4184,26 +4186,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F84" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F84" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G84" s="27" t="n"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4217,7 +4231,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4232,7 +4246,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F86" s="27" t="n"/>
@@ -4241,7 +4255,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4256,7 +4270,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F87" s="27" t="n"/>
@@ -4265,7 +4279,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4280,7 +4294,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F88" s="27" t="n"/>
@@ -4289,7 +4303,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4304,7 +4318,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F89" s="27" t="n"/>
@@ -4313,7 +4327,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4328,7 +4342,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F90" s="27" t="n"/>
@@ -4337,22 +4351,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F91" s="27" t="n"/>
@@ -4361,7 +4375,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4385,7 +4399,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4400,7 +4414,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F93" s="27" t="n"/>
@@ -4409,7 +4423,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4424,7 +4438,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F94" s="27" t="n"/>
@@ -4433,7 +4447,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4448,7 +4462,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F95" s="27" t="n"/>
@@ -4457,7 +4471,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4472,7 +4486,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F96" s="27" t="n"/>
@@ -4481,7 +4495,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4505,7 +4519,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4520,7 +4534,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F98" s="27" t="n"/>
@@ -4529,7 +4543,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4544,11 +4558,35 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F99" s="27" t="n"/>
       <c r="G99" s="27" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F100" s="27" t="n"/>
+      <c r="G100" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-29 00:19 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-29 02:40 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1013,7 +1013,7 @@
         <v>9670</v>
       </c>
       <c r="M6" s="23" t="n">
-        <v>2371</v>
+        <v>21456</v>
       </c>
       <c r="N6" s="23" t="n"/>
       <c r="O6" s="23" t="n"/>
@@ -1441,7 +1441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1499,17 +1499,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:12</t>
+          <t>2026-10-29 02:35:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1523,29 +1523,31 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>4018</v>
-      </c>
-      <c r="G2" s="27" t="n"/>
+        <v>21456</v>
+      </c>
+      <c r="G2" s="27" t="n">
+        <v>2371</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28 23:47:44</t>
+          <t>2026-10-29 00:00:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1559,21 +1561,19 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>2371</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>371</v>
-      </c>
+        <v>4018</v>
+      </c>
+      <c r="G3" s="27" t="n"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28 23:46:44</t>
+          <t>2026-10-28 23:47:44</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1588,16 +1588,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>2371</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:32</t>
+          <t>2026-10-28 23:46:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1612,7 +1626,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F5" s="27" t="n"/>
@@ -1621,7 +1635,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28 17:45:48</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1636,30 +1650,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>271</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="27" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28 10:22:51</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1674,16 +1674,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>271</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1698,28 +1712,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>271</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n"/>
       <c r="G8" s="27" t="n"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1739,15 +1741,13 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>1401</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>app</t>
@@ -1757,17 +1757,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1777,13 +1777,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>10320</v>
-      </c>
-      <c r="G10" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>app</t>
@@ -1793,7 +1795,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1813,11 +1815,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>12221</v>
+        <v>10320</v>
       </c>
       <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
@@ -1829,7 +1831,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1849,11 +1851,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>10300</v>
+        <v>12221</v>
       </c>
       <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
@@ -1865,7 +1867,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1885,11 +1887,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>10595</v>
+        <v>10300</v>
       </c>
       <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
@@ -1901,7 +1903,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,11 +1923,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>11109</v>
+        <v>10595</v>
       </c>
       <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
@@ -1937,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1957,11 +1959,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>13681</v>
+        <v>11109</v>
       </c>
       <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
@@ -1973,17 +1975,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1993,15 +1995,13 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>13681</v>
+      </c>
+      <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>app</t>
@@ -2011,17 +2011,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2031,13 +2031,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G17" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>app</t>
@@ -2047,7 +2049,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2067,11 +2069,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>307</v>
+        <v>4640</v>
       </c>
       <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
@@ -2083,7 +2085,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2103,11 +2105,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>3787</v>
+        <v>307</v>
       </c>
       <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
@@ -2119,7 +2121,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2139,11 +2141,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>4947</v>
+        <v>3787</v>
       </c>
       <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
@@ -2155,17 +2157,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2175,11 +2177,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>311</v>
+        <v>4947</v>
       </c>
       <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
@@ -2191,7 +2193,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2211,15 +2213,13 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G22" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>app</t>
@@ -2229,7 +2229,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2244,16 +2244,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G23" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2268,40 +2282,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G24" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="27" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2315,29 +2315,31 @@
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>8300</v>
-      </c>
-      <c r="G25" s="27" t="n"/>
+        <v>1157</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>911</v>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2351,21 +2353,19 @@
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G26" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>8300</v>
+      </c>
+      <c r="G26" s="27" t="n"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2389,9 +2389,11 @@
         </is>
       </c>
       <c r="F27" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="G27" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G27" s="27" t="n"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>app</t>
@@ -2401,7 +2403,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2421,15 +2423,13 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F28" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G28" s="27" t="n"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>app</t>
@@ -2439,7 +2439,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="F29" s="27" t="n">
+        <v>20274</v>
+      </c>
+      <c r="G29" s="27" t="n">
         <v>3510</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2477,17 +2477,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2501,29 +2501,31 @@
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G30" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G30" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2537,19 +2539,19 @@
         </is>
       </c>
       <c r="F31" s="27" t="n">
-        <v>351</v>
+        <v>13001</v>
       </c>
       <c r="G31" s="27" t="n"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2564,16 +2566,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G32" s="27" t="n"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2588,40 +2602,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G33" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="27" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2635,29 +2635,31 @@
         </is>
       </c>
       <c r="F34" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G34" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2671,21 +2673,19 @@
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G35" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G35" s="27" t="n"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F36" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G36" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G36" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2747,9 +2747,11 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G37" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G37" s="27" t="n"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>app</t>
@@ -2759,7 +2761,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2779,15 +2781,13 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F38" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G38" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G38" s="27" t="n"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>app</t>
@@ -2797,7 +2797,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2812,16 +2812,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G39" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2836,40 +2850,26 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G40" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="27" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2879,13 +2879,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F41" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G41" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>app</t>
@@ -2895,7 +2897,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2915,15 +2917,13 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F42" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G42" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G42" s="27" t="n"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>app</t>
@@ -2933,7 +2933,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2953,11 +2953,11 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F43" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2991,35 +2991,35 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F44" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3033,31 +3033,31 @@
         </is>
       </c>
       <c r="F45" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3071,29 +3071,31 @@
         </is>
       </c>
       <c r="F46" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3107,21 +3109,19 @@
         </is>
       </c>
       <c r="F47" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G47" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G47" s="27" t="n"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3136,16 +3136,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n"/>
-      <c r="G48" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G48" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3160,28 +3174,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F49" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="n"/>
       <c r="G49" s="27" t="n"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3201,15 +3203,13 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F50" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G50" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G50" s="27" t="n"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>app</t>
@@ -3219,17 +3219,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3243,9 +3243,11 @@
         </is>
       </c>
       <c r="F51" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G51" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G51" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>app</t>
@@ -3255,31 +3257,43 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G52" s="27" t="n"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3294,7 +3308,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F53" s="27" t="n"/>
@@ -3303,53 +3317,41 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n"/>
       <c r="G54" s="27" t="n"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3359,47 +3361,59 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F55" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G55" s="27" t="n"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G56" s="27" t="n"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3414,7 +3428,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3423,22 +3437,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3447,7 +3461,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3462,28 +3476,16 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n"/>
       <c r="G59" s="27" t="n"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3503,15 +3505,13 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F60" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G60" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G60" s="27" t="n"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>app</t>
@@ -3521,7 +3521,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3536,16 +3536,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F61" s="27" t="n"/>
-      <c r="G61" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G61" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3560,7 +3574,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F62" s="27" t="n"/>
@@ -3569,103 +3583,91 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F63" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="n"/>
       <c r="G63" s="27" t="n"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F64" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G64" s="27" t="n"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="n"/>
       <c r="G65" s="27" t="n"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3680,31 +3682,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F66" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G66" s="27" t="n"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F67" s="27" t="n"/>
@@ -3713,7 +3727,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3728,28 +3742,16 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F68" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F68" s="27" t="n"/>
       <c r="G68" s="27" t="n"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3764,52 +3766,52 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G69" s="27" t="n"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n"/>
       <c r="G70" s="27" t="n"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3824,16 +3826,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F71" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F71" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G71" s="27" t="n"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3848,7 +3862,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F72" s="27" t="n"/>
@@ -3857,69 +3871,69 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G73" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="n"/>
+      <c r="G73" s="27" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="n"/>
-      <c r="G74" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G74" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3934,7 +3948,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F75" s="27" t="n"/>
@@ -3943,43 +3957,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F76" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="n"/>
       <c r="G76" s="27" t="n"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3994,16 +3996,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F77" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F77" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G77" s="27" t="n"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4018,7 +4032,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F78" s="27" t="n"/>
@@ -4027,43 +4041,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F79" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F79" s="27" t="n"/>
       <c r="G79" s="27" t="n"/>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4083,11 +4085,11 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F80" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G80" s="27" t="n"/>
       <c r="H80" t="inlineStr">
@@ -4099,31 +4101,43 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F81" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F81" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G81" s="27" t="n"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4138,7 +4152,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F82" s="27" t="n"/>
@@ -4147,7 +4161,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4162,7 +4176,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F83" s="27" t="n"/>
@@ -4171,43 +4185,31 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F84" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F84" s="27" t="n"/>
       <c r="G84" s="27" t="n"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4222,26 +4224,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F85" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F85" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G85" s="27" t="n"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4255,7 +4269,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4270,7 +4284,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F87" s="27" t="n"/>
@@ -4279,7 +4293,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4294,7 +4308,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F88" s="27" t="n"/>
@@ -4303,7 +4317,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4318,7 +4332,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F89" s="27" t="n"/>
@@ -4327,7 +4341,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4342,7 +4356,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F90" s="27" t="n"/>
@@ -4351,7 +4365,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4366,7 +4380,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F91" s="27" t="n"/>
@@ -4375,22 +4389,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F92" s="27" t="n"/>
@@ -4399,7 +4413,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4423,7 +4437,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4438,7 +4452,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F94" s="27" t="n"/>
@@ -4447,7 +4461,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4462,7 +4476,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F95" s="27" t="n"/>
@@ -4471,7 +4485,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4486,7 +4500,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F96" s="27" t="n"/>
@@ -4495,7 +4509,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4510,7 +4524,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F97" s="27" t="n"/>
@@ -4519,7 +4533,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4543,7 +4557,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4558,7 +4572,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F99" s="27" t="n"/>
@@ -4567,7 +4581,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4582,11 +4596,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F100" s="27" t="n"/>
       <c r="G100" s="27" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F101" s="27" t="n"/>
+      <c r="G101" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-29 02:40 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-29 06:33 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1015,7 +1015,9 @@
       <c r="M6" s="23" t="n">
         <v>21456</v>
       </c>
-      <c r="N6" s="23" t="n"/>
+      <c r="N6" s="23" t="n">
+        <v>266</v>
+      </c>
       <c r="O6" s="23" t="n"/>
       <c r="P6" s="23" t="n"/>
       <c r="Q6" s="23" t="n"/>
@@ -1441,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1499,7 +1501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29 02:35:57</t>
+          <t>2026-10-29 06:32:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1519,15 +1521,13 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>21456</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>2371</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>app</t>
@@ -1537,17 +1537,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:12</t>
+          <t>2026-10-29 02:35:57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1561,29 +1561,31 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>4018</v>
-      </c>
-      <c r="G3" s="27" t="n"/>
+        <v>21456</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>2371</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28 23:47:44</t>
+          <t>2026-10-29 00:00:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1597,21 +1599,19 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>2371</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>371</v>
-      </c>
+        <v>4018</v>
+      </c>
+      <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28 23:46:44</t>
+          <t>2026-10-28 23:47:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1626,16 +1626,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>2371</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:32</t>
+          <t>2026-10-28 23:46:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1650,7 +1664,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F6" s="27" t="n"/>
@@ -1659,7 +1673,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28 17:45:48</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1674,30 +1688,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>271</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28 10:22:51</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1712,16 +1712,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>271</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1736,28 +1750,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>271</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n"/>
       <c r="G9" s="27" t="n"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1777,15 +1779,13 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>1401</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G10" s="27" t="n"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>app</t>
@@ -1795,17 +1795,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1815,13 +1815,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>10320</v>
-      </c>
-      <c r="G11" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>app</t>
@@ -1831,7 +1833,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1851,11 +1853,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>12221</v>
+        <v>10320</v>
       </c>
       <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
@@ -1867,7 +1869,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1887,11 +1889,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>10300</v>
+        <v>12221</v>
       </c>
       <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
@@ -1903,7 +1905,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1923,11 +1925,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>10595</v>
+        <v>10300</v>
       </c>
       <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
@@ -1939,7 +1941,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1959,11 +1961,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>11109</v>
+        <v>10595</v>
       </c>
       <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
@@ -1975,7 +1977,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1995,11 +1997,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>13681</v>
+        <v>11109</v>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
@@ -2011,17 +2013,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2031,15 +2033,13 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>13681</v>
+      </c>
+      <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>app</t>
@@ -2049,17 +2049,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2069,13 +2069,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G18" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>app</t>
@@ -2085,7 +2087,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2105,11 +2107,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>307</v>
+        <v>4640</v>
       </c>
       <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
@@ -2121,7 +2123,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2141,11 +2143,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>3787</v>
+        <v>307</v>
       </c>
       <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
@@ -2157,7 +2159,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2177,11 +2179,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>4947</v>
+        <v>3787</v>
       </c>
       <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
@@ -2193,17 +2195,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2213,11 +2215,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>311</v>
+        <v>4947</v>
       </c>
       <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
@@ -2229,7 +2231,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2249,15 +2251,13 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G23" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G23" s="27" t="n"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>app</t>
@@ -2267,7 +2267,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2282,16 +2282,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2306,40 +2320,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G25" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="27" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2353,29 +2353,31 @@
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>8300</v>
-      </c>
-      <c r="G26" s="27" t="n"/>
+        <v>1157</v>
+      </c>
+      <c r="G26" s="27" t="n">
+        <v>911</v>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2389,21 +2391,19 @@
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G27" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>8300</v>
+      </c>
+      <c r="G27" s="27" t="n"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2427,9 +2427,11 @@
         </is>
       </c>
       <c r="F28" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="G28" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G28" s="27" t="n"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>app</t>
@@ -2439,7 +2441,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2459,15 +2461,13 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F29" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G29" s="27" t="n"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>app</t>
@@ -2477,7 +2477,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="F30" s="27" t="n">
+        <v>20274</v>
+      </c>
+      <c r="G30" s="27" t="n">
         <v>3510</v>
-      </c>
-      <c r="G30" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2515,17 +2515,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2539,29 +2539,31 @@
         </is>
       </c>
       <c r="F31" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G31" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2575,19 +2577,19 @@
         </is>
       </c>
       <c r="F32" s="27" t="n">
-        <v>351</v>
+        <v>13001</v>
       </c>
       <c r="G32" s="27" t="n"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2602,16 +2604,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G33" s="27" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2626,40 +2640,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G34" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="27" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2673,29 +2673,31 @@
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G35" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2709,21 +2711,19 @@
         </is>
       </c>
       <c r="F36" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G36" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G36" s="27" t="n"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G37" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2785,9 +2785,11 @@
         </is>
       </c>
       <c r="F38" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G38" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G38" s="27" t="n"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>app</t>
@@ -2797,7 +2799,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2817,15 +2819,13 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F39" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G39" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G39" s="27" t="n"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>app</t>
@@ -2835,7 +2835,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2850,16 +2850,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G40" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2874,40 +2888,26 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G41" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="27" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2917,13 +2917,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F42" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G42" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G42" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>app</t>
@@ -2933,7 +2935,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2953,15 +2955,13 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F43" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G43" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G43" s="27" t="n"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>app</t>
@@ -2971,7 +2971,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2991,11 +2991,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F44" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3029,35 +3029,35 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F45" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G45" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3071,31 +3071,31 @@
         </is>
       </c>
       <c r="F46" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G46" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3109,29 +3109,31 @@
         </is>
       </c>
       <c r="F47" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G47" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3145,21 +3147,19 @@
         </is>
       </c>
       <c r="F48" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G48" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G48" s="27" t="n"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3174,16 +3174,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G49" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3198,28 +3212,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F50" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="n"/>
       <c r="G50" s="27" t="n"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3239,15 +3241,13 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F51" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G51" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G51" s="27" t="n"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>app</t>
@@ -3257,17 +3257,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3281,9 +3281,11 @@
         </is>
       </c>
       <c r="F52" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G52" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G52" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>app</t>
@@ -3293,31 +3295,43 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F53" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G53" s="27" t="n"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3332,7 +3346,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F54" s="27" t="n"/>
@@ -3341,53 +3355,41 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n"/>
       <c r="G55" s="27" t="n"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3397,47 +3399,59 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F56" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G56" s="27" t="n"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G57" s="27" t="n"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3452,7 +3466,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3461,22 +3475,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F59" s="27" t="n"/>
@@ -3485,7 +3499,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3500,28 +3514,16 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n"/>
       <c r="G60" s="27" t="n"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3541,15 +3543,13 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F61" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G61" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G61" s="27" t="n"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>app</t>
@@ -3559,7 +3559,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3574,16 +3574,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F62" s="27" t="n"/>
-      <c r="G62" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G62" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3598,7 +3612,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3607,103 +3621,91 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F64" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="n"/>
       <c r="G64" s="27" t="n"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G65" s="27" t="n"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F66" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="n"/>
       <c r="G66" s="27" t="n"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3718,31 +3720,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G67" s="27" t="n"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F68" s="27" t="n"/>
@@ -3751,7 +3765,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3766,28 +3780,16 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n"/>
       <c r="G69" s="27" t="n"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3802,52 +3804,52 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G70" s="27" t="n"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F71" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F71" s="27" t="n"/>
       <c r="G71" s="27" t="n"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3862,16 +3864,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F72" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G72" s="27" t="n"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3886,7 +3900,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F73" s="27" t="n"/>
@@ -3895,69 +3909,69 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G74" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="n"/>
+      <c r="G74" s="27" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="n"/>
-      <c r="G75" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G75" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3972,7 +3986,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F76" s="27" t="n"/>
@@ -3981,43 +3995,31 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F77" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F77" s="27" t="n"/>
       <c r="G77" s="27" t="n"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4032,16 +4034,28 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F78" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G78" s="27" t="n"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4056,7 +4070,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F79" s="27" t="n"/>
@@ -4065,43 +4079,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F80" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F80" s="27" t="n"/>
       <c r="G80" s="27" t="n"/>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4121,11 +4123,11 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F81" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G81" s="27" t="n"/>
       <c r="H81" t="inlineStr">
@@ -4137,31 +4139,43 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F82" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F82" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G82" s="27" t="n"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4176,7 +4190,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F83" s="27" t="n"/>
@@ -4185,7 +4199,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4200,7 +4214,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F84" s="27" t="n"/>
@@ -4209,43 +4223,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F85" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F85" s="27" t="n"/>
       <c r="G85" s="27" t="n"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4260,26 +4262,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F86" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F86" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G86" s="27" t="n"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4293,7 +4307,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4308,7 +4322,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F88" s="27" t="n"/>
@@ -4317,7 +4331,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4332,7 +4346,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F89" s="27" t="n"/>
@@ -4341,7 +4355,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4356,7 +4370,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F90" s="27" t="n"/>
@@ -4365,7 +4379,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4380,7 +4394,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F91" s="27" t="n"/>
@@ -4389,7 +4403,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4404,7 +4418,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F92" s="27" t="n"/>
@@ -4413,22 +4427,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F93" s="27" t="n"/>
@@ -4437,7 +4451,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4461,7 +4475,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4476,7 +4490,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F95" s="27" t="n"/>
@@ -4485,7 +4499,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4500,7 +4514,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F96" s="27" t="n"/>
@@ -4509,7 +4523,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4524,7 +4538,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F97" s="27" t="n"/>
@@ -4533,7 +4547,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4548,7 +4562,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F98" s="27" t="n"/>
@@ -4557,7 +4571,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4581,7 +4595,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4596,7 +4610,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F100" s="27" t="n"/>
@@ -4605,7 +4619,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4620,11 +4634,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F101" s="27" t="n"/>
       <c r="G101" s="27" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F102" s="27" t="n"/>
+      <c r="G102" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-29 06:33 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-29 09:16 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1121,7 +1121,9 @@
       <c r="M8" s="23" t="n">
         <v>4018</v>
       </c>
-      <c r="N8" s="23" t="n"/>
+      <c r="N8" s="23" t="n">
+        <v>30</v>
+      </c>
       <c r="O8" s="23" t="n"/>
       <c r="P8" s="23" t="n"/>
       <c r="Q8" s="23" t="n"/>
@@ -1443,7 +1445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1501,17 +1503,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29 06:32:56</t>
+          <t>2026-10-29 09:14:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1525,19 +1527,19 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>266</v>
+        <v>30</v>
       </c>
       <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29 02:35:57</t>
+          <t>2026-10-29 06:32:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1557,15 +1559,13 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>21456</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>2371</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="G3" s="27" t="n"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>app</t>
@@ -1575,17 +1575,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:12</t>
+          <t>2026-10-29 02:35:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1599,29 +1599,31 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>4018</v>
-      </c>
-      <c r="G4" s="27" t="n"/>
+        <v>21456</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>2371</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28 23:47:44</t>
+          <t>2026-10-29 00:00:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1635,21 +1637,19 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>2371</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>371</v>
-      </c>
+        <v>4018</v>
+      </c>
+      <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28 23:46:44</t>
+          <t>2026-10-28 23:47:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1664,16 +1664,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>2371</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:32</t>
+          <t>2026-10-28 23:46:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1688,7 +1702,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F7" s="27" t="n"/>
@@ -1697,7 +1711,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28 17:45:48</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1712,30 +1726,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>271</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="27" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28 10:22:51</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1750,16 +1750,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>271</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1774,28 +1788,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>271</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n"/>
       <c r="G10" s="27" t="n"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1815,15 +1817,13 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>1401</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G11" s="27" t="n"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>app</t>
@@ -1833,17 +1833,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1853,13 +1853,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>10320</v>
-      </c>
-      <c r="G12" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1869,7 +1871,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1889,11 +1891,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>12221</v>
+        <v>10320</v>
       </c>
       <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
@@ -1905,7 +1907,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1925,11 +1927,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>10300</v>
+        <v>12221</v>
       </c>
       <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
@@ -1941,7 +1943,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1961,11 +1963,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>10595</v>
+        <v>10300</v>
       </c>
       <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
@@ -1977,7 +1979,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1997,11 +1999,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>11109</v>
+        <v>10595</v>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
@@ -2013,7 +2015,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2033,11 +2035,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>13681</v>
+        <v>11109</v>
       </c>
       <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
@@ -2049,17 +2051,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2069,15 +2071,13 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>13681</v>
+      </c>
+      <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>app</t>
@@ -2087,17 +2087,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2107,13 +2107,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G19" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>app</t>
@@ -2123,7 +2125,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,11 +2145,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>307</v>
+        <v>4640</v>
       </c>
       <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
@@ -2159,7 +2161,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2179,11 +2181,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>3787</v>
+        <v>307</v>
       </c>
       <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
@@ -2195,7 +2197,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,11 +2217,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>4947</v>
+        <v>3787</v>
       </c>
       <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
@@ -2231,17 +2233,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2251,11 +2253,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>311</v>
+        <v>4947</v>
       </c>
       <c r="G23" s="27" t="n"/>
       <c r="H23" t="inlineStr">
@@ -2267,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2287,15 +2289,13 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G24" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>app</t>
@@ -2305,7 +2305,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2320,16 +2320,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2344,40 +2358,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G26" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="27" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2391,29 +2391,31 @@
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>8300</v>
-      </c>
-      <c r="G27" s="27" t="n"/>
+        <v>1157</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>911</v>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2427,21 +2429,19 @@
         </is>
       </c>
       <c r="F28" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>8300</v>
+      </c>
+      <c r="G28" s="27" t="n"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2465,9 +2465,11 @@
         </is>
       </c>
       <c r="F29" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="G29" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G29" s="27" t="n"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>app</t>
@@ -2477,7 +2479,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2497,15 +2499,13 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G30" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>app</t>
@@ -2515,7 +2515,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="F31" s="27" t="n">
+        <v>20274</v>
+      </c>
+      <c r="G31" s="27" t="n">
         <v>3510</v>
-      </c>
-      <c r="G31" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2553,17 +2553,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2577,29 +2577,31 @@
         </is>
       </c>
       <c r="F32" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G32" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2613,19 +2615,19 @@
         </is>
       </c>
       <c r="F33" s="27" t="n">
-        <v>351</v>
+        <v>13001</v>
       </c>
       <c r="G33" s="27" t="n"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2640,16 +2642,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G34" s="27" t="n"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2664,40 +2678,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G35" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n"/>
+      <c r="G35" s="27" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2711,29 +2711,31 @@
         </is>
       </c>
       <c r="F36" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G36" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2747,21 +2749,19 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G37" s="27" t="n"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="F38" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G38" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G38" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2823,9 +2823,11 @@
         </is>
       </c>
       <c r="F39" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G39" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G39" s="27" t="n"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>app</t>
@@ -2835,7 +2837,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2855,15 +2857,13 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F40" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G40" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G40" s="27" t="n"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>app</t>
@@ -2873,7 +2873,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2888,16 +2888,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2912,40 +2926,26 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G42" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n"/>
+      <c r="G42" s="27" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2955,13 +2955,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F43" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G43" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G43" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>app</t>
@@ -2971,7 +2973,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2991,15 +2993,13 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F44" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G44" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G44" s="27" t="n"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>app</t>
@@ -3009,7 +3009,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3029,11 +3029,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F45" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G45" s="27" t="n">
         <v>0</v>
@@ -3047,7 +3047,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3067,35 +3067,35 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F46" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3109,31 +3109,31 @@
         </is>
       </c>
       <c r="F47" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3147,29 +3147,31 @@
         </is>
       </c>
       <c r="F48" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G48" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3183,21 +3185,19 @@
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G49" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G49" s="27" t="n"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3212,16 +3212,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F50" s="27" t="n"/>
-      <c r="G50" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G50" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3236,28 +3250,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3277,15 +3279,13 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F52" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G52" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G52" s="27" t="n"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>app</t>
@@ -3295,17 +3295,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3319,9 +3319,11 @@
         </is>
       </c>
       <c r="F53" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G53" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G53" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>app</t>
@@ -3331,31 +3333,43 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G54" s="27" t="n"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3370,7 +3384,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F55" s="27" t="n"/>
@@ -3379,53 +3393,41 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n"/>
       <c r="G56" s="27" t="n"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3435,47 +3437,59 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F57" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G57" s="27" t="n"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F58" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G58" s="27" t="n"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3490,7 +3504,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F59" s="27" t="n"/>
@@ -3499,22 +3513,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F60" s="27" t="n"/>
@@ -3523,7 +3537,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3538,28 +3552,16 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F61" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="n"/>
       <c r="G61" s="27" t="n"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3579,15 +3581,13 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F62" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G62" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G62" s="27" t="n"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>app</t>
@@ -3597,7 +3597,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3612,16 +3612,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F63" s="27" t="n"/>
-      <c r="G63" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G63" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3636,7 +3650,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F64" s="27" t="n"/>
@@ -3645,103 +3659,91 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="n"/>
       <c r="G65" s="27" t="n"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F66" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G66" s="27" t="n"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="n"/>
       <c r="G67" s="27" t="n"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3756,31 +3758,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F68" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F68" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G68" s="27" t="n"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F69" s="27" t="n"/>
@@ -3789,7 +3803,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3804,28 +3818,16 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n"/>
       <c r="G70" s="27" t="n"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3840,52 +3842,52 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F71" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F71" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G71" s="27" t="n"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F72" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="n"/>
       <c r="G72" s="27" t="n"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3900,16 +3902,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G73" s="27" t="n"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3924,7 +3938,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F74" s="27" t="n"/>
@@ -3933,69 +3947,69 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G75" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="n"/>
+      <c r="G75" s="27" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F76" s="27" t="n"/>
-      <c r="G76" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G76" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4010,7 +4024,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F77" s="27" t="n"/>
@@ -4019,43 +4033,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F78" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="n"/>
       <c r="G78" s="27" t="n"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4070,16 +4072,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F79" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F79" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G79" s="27" t="n"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4094,7 +4108,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F80" s="27" t="n"/>
@@ -4103,43 +4117,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F81" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F81" s="27" t="n"/>
       <c r="G81" s="27" t="n"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4159,11 +4161,11 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F82" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G82" s="27" t="n"/>
       <c r="H82" t="inlineStr">
@@ -4175,31 +4177,43 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F83" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F83" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G83" s="27" t="n"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4214,7 +4228,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F84" s="27" t="n"/>
@@ -4223,7 +4237,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4238,7 +4252,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F85" s="27" t="n"/>
@@ -4247,43 +4261,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F86" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F86" s="27" t="n"/>
       <c r="G86" s="27" t="n"/>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4298,26 +4300,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F87" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F87" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G87" s="27" t="n"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4331,7 +4345,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4346,7 +4360,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F89" s="27" t="n"/>
@@ -4355,7 +4369,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4370,7 +4384,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F90" s="27" t="n"/>
@@ -4379,7 +4393,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4394,7 +4408,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F91" s="27" t="n"/>
@@ -4403,7 +4417,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4418,7 +4432,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F92" s="27" t="n"/>
@@ -4427,7 +4441,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4442,7 +4456,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F93" s="27" t="n"/>
@@ -4451,22 +4465,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F94" s="27" t="n"/>
@@ -4475,7 +4489,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4499,7 +4513,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4514,7 +4528,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F96" s="27" t="n"/>
@@ -4523,7 +4537,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4538,7 +4552,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F97" s="27" t="n"/>
@@ -4547,7 +4561,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4562,7 +4576,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F98" s="27" t="n"/>
@@ -4571,7 +4585,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4586,7 +4600,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F99" s="27" t="n"/>
@@ -4595,7 +4609,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4619,7 +4633,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4634,7 +4648,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F101" s="27" t="n"/>
@@ -4643,7 +4657,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4658,11 +4672,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F102" s="27" t="n"/>
       <c r="G102" s="27" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F103" s="27" t="n"/>
+      <c r="G103" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-29 09:16 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-29 14:45 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1016,7 +1016,7 @@
         <v>21456</v>
       </c>
       <c r="N6" s="23" t="n">
-        <v>266</v>
+        <v>1011</v>
       </c>
       <c r="O6" s="23" t="n"/>
       <c r="P6" s="23" t="n"/>
@@ -1445,7 +1445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1503,17 +1503,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29 09:14:12</t>
+          <t>2026-10-29 14:44:19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1527,29 +1527,31 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="G2" s="27" t="n"/>
+        <v>1011</v>
+      </c>
+      <c r="G2" s="27" t="n">
+        <v>266</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29 06:32:56</t>
+          <t>2026-10-29 09:14:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1563,19 +1565,19 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>266</v>
+        <v>30</v>
       </c>
       <c r="G3" s="27" t="n"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29 02:35:57</t>
+          <t>2026-10-29 06:32:56</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1595,15 +1597,13 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>21456</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>2371</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>app</t>
@@ -1613,17 +1613,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:12</t>
+          <t>2026-10-29 02:35:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1637,29 +1637,31 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>4018</v>
-      </c>
-      <c r="G5" s="27" t="n"/>
+        <v>21456</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>2371</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28 23:47:44</t>
+          <t>2026-10-29 00:00:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1673,21 +1675,19 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>2371</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>371</v>
-      </c>
+        <v>4018</v>
+      </c>
+      <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28 23:46:44</t>
+          <t>2026-10-28 23:47:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1702,16 +1702,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>2371</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:32</t>
+          <t>2026-10-28 23:46:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1726,7 +1740,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F8" s="27" t="n"/>
@@ -1735,7 +1749,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28 17:45:48</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1750,30 +1764,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>271</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="27" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28 10:22:51</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1788,16 +1788,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>271</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1812,28 +1826,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>271</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n"/>
       <c r="G11" s="27" t="n"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1853,15 +1855,13 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>1401</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G12" s="27" t="n"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>app</t>
@@ -1871,17 +1871,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1891,13 +1891,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>10320</v>
-      </c>
-      <c r="G13" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>app</t>
@@ -1907,7 +1909,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1927,11 +1929,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>12221</v>
+        <v>10320</v>
       </c>
       <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
@@ -1943,7 +1945,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1963,11 +1965,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>10300</v>
+        <v>12221</v>
       </c>
       <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
@@ -1979,7 +1981,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1999,11 +2001,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>10595</v>
+        <v>10300</v>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
@@ -2015,7 +2017,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2035,11 +2037,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>11109</v>
+        <v>10595</v>
       </c>
       <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
@@ -2051,7 +2053,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2071,11 +2073,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>13681</v>
+        <v>11109</v>
       </c>
       <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
@@ -2087,17 +2089,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2107,15 +2109,13 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>13681</v>
+      </c>
+      <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>app</t>
@@ -2125,17 +2125,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2145,13 +2145,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G20" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>app</t>
@@ -2161,7 +2163,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2181,11 +2183,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>307</v>
+        <v>4640</v>
       </c>
       <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
@@ -2197,7 +2199,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2217,11 +2219,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>3787</v>
+        <v>307</v>
       </c>
       <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
@@ -2233,7 +2235,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2253,11 +2255,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>4947</v>
+        <v>3787</v>
       </c>
       <c r="G23" s="27" t="n"/>
       <c r="H23" t="inlineStr">
@@ -2269,17 +2271,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2289,11 +2291,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>311</v>
+        <v>4947</v>
       </c>
       <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
@@ -2305,7 +2307,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2325,15 +2327,13 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G25" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G25" s="27" t="n"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>app</t>
@@ -2343,7 +2343,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2358,16 +2358,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G26" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2382,40 +2396,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G27" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n"/>
+      <c r="G27" s="27" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2429,29 +2429,31 @@
         </is>
       </c>
       <c r="F28" s="27" t="n">
-        <v>8300</v>
-      </c>
-      <c r="G28" s="27" t="n"/>
+        <v>1157</v>
+      </c>
+      <c r="G28" s="27" t="n">
+        <v>911</v>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2465,21 +2467,19 @@
         </is>
       </c>
       <c r="F29" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>8300</v>
+      </c>
+      <c r="G29" s="27" t="n"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2503,9 +2503,11 @@
         </is>
       </c>
       <c r="F30" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="G30" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>app</t>
@@ -2515,7 +2517,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2535,15 +2537,13 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F31" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G31" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G31" s="27" t="n"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>app</t>
@@ -2553,7 +2553,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F32" s="27" t="n">
+        <v>20274</v>
+      </c>
+      <c r="G32" s="27" t="n">
         <v>3510</v>
-      </c>
-      <c r="G32" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2591,17 +2591,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2615,29 +2615,31 @@
         </is>
       </c>
       <c r="F33" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G33" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2651,19 +2653,19 @@
         </is>
       </c>
       <c r="F34" s="27" t="n">
-        <v>351</v>
+        <v>13001</v>
       </c>
       <c r="G34" s="27" t="n"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2678,16 +2680,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G35" s="27" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2702,40 +2716,26 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G36" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2749,29 +2749,31 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G37" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2785,21 +2787,19 @@
         </is>
       </c>
       <c r="F38" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G38" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G38" s="27" t="n"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="F39" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G39" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G39" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2861,9 +2861,11 @@
         </is>
       </c>
       <c r="F40" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G40" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G40" s="27" t="n"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>app</t>
@@ -2873,7 +2875,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2893,15 +2895,13 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F41" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G41" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G41" s="27" t="n"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>app</t>
@@ -2911,7 +2911,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2926,16 +2926,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="n"/>
-      <c r="G42" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G42" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2950,40 +2964,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G43" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="27" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2993,13 +2993,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F44" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G44" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G44" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>app</t>
@@ -3009,7 +3011,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3029,15 +3031,13 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F45" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G45" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G45" s="27" t="n"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>app</t>
@@ -3047,7 +3047,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3067,11 +3067,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F46" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0</v>
@@ -3085,7 +3085,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3105,35 +3105,35 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F47" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G47" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3147,31 +3147,31 @@
         </is>
       </c>
       <c r="F48" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3185,29 +3185,31 @@
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G49" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3221,21 +3223,19 @@
         </is>
       </c>
       <c r="F50" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G50" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G50" s="27" t="n"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3250,16 +3250,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="n"/>
-      <c r="G51" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G51" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3274,28 +3288,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n"/>
       <c r="G52" s="27" t="n"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3315,15 +3317,13 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F53" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G53" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G53" s="27" t="n"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>app</t>
@@ -3333,17 +3333,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3357,9 +3357,11 @@
         </is>
       </c>
       <c r="F54" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G54" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G54" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>app</t>
@@ -3369,31 +3371,43 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G55" s="27" t="n"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3408,7 +3422,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F56" s="27" t="n"/>
@@ -3417,53 +3431,41 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="n"/>
       <c r="G57" s="27" t="n"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3473,47 +3475,59 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F58" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G58" s="27" t="n"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G59" s="27" t="n"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3528,7 +3542,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F60" s="27" t="n"/>
@@ -3537,22 +3551,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3561,7 +3575,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3576,28 +3590,16 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F62" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="n"/>
       <c r="G62" s="27" t="n"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3617,15 +3619,13 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F63" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G63" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G63" s="27" t="n"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>app</t>
@@ -3635,7 +3635,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3650,16 +3650,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F64" s="27" t="n"/>
-      <c r="G64" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G64" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3674,7 +3688,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F65" s="27" t="n"/>
@@ -3683,103 +3697,91 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F66" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="n"/>
       <c r="G66" s="27" t="n"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G67" s="27" t="n"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F68" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F68" s="27" t="n"/>
       <c r="G68" s="27" t="n"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3794,31 +3796,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G69" s="27" t="n"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F70" s="27" t="n"/>
@@ -3827,7 +3841,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3842,28 +3856,16 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F71" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F71" s="27" t="n"/>
       <c r="G71" s="27" t="n"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3878,52 +3880,52 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F72" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G72" s="27" t="n"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="n"/>
       <c r="G73" s="27" t="n"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3938,16 +3940,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G74" s="27" t="n"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3962,7 +3976,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F75" s="27" t="n"/>
@@ -3971,69 +3985,69 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F76" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G76" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="n"/>
+      <c r="G76" s="27" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F77" s="27" t="n"/>
-      <c r="G77" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F77" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G77" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4048,7 +4062,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F78" s="27" t="n"/>
@@ -4057,43 +4071,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F79" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F79" s="27" t="n"/>
       <c r="G79" s="27" t="n"/>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4108,16 +4110,28 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F80" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F80" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G80" s="27" t="n"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4132,7 +4146,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F81" s="27" t="n"/>
@@ -4141,43 +4155,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F82" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F82" s="27" t="n"/>
       <c r="G82" s="27" t="n"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4197,11 +4199,11 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F83" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G83" s="27" t="n"/>
       <c r="H83" t="inlineStr">
@@ -4213,31 +4215,43 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F84" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F84" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G84" s="27" t="n"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4252,7 +4266,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F85" s="27" t="n"/>
@@ -4261,7 +4275,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4276,7 +4290,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F86" s="27" t="n"/>
@@ -4285,43 +4299,31 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F87" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F87" s="27" t="n"/>
       <c r="G87" s="27" t="n"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4336,26 +4338,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F88" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F88" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G88" s="27" t="n"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4369,7 +4383,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4384,7 +4398,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F90" s="27" t="n"/>
@@ -4393,7 +4407,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4408,7 +4422,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F91" s="27" t="n"/>
@@ -4417,7 +4431,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4432,7 +4446,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F92" s="27" t="n"/>
@@ -4441,7 +4455,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4456,7 +4470,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F93" s="27" t="n"/>
@@ -4465,7 +4479,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4480,7 +4494,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F94" s="27" t="n"/>
@@ -4489,22 +4503,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F95" s="27" t="n"/>
@@ -4513,7 +4527,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4537,7 +4551,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4552,7 +4566,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F97" s="27" t="n"/>
@@ -4561,7 +4575,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4576,7 +4590,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F98" s="27" t="n"/>
@@ -4585,7 +4599,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4600,7 +4614,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F99" s="27" t="n"/>
@@ -4609,7 +4623,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4624,7 +4638,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F100" s="27" t="n"/>
@@ -4633,7 +4647,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4657,7 +4671,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4672,7 +4686,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F102" s="27" t="n"/>
@@ -4681,7 +4695,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4696,11 +4710,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F103" s="27" t="n"/>
       <c r="G103" s="27" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F104" s="27" t="n"/>
+      <c r="G104" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-29 14:45 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-29 14:51 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1284,7 +1284,9 @@
       <c r="L11" s="23" t="n">
         <v>12221</v>
       </c>
-      <c r="M11" s="23" t="n"/>
+      <c r="M11" s="23" t="n">
+        <v>10100</v>
+      </c>
       <c r="N11" s="23" t="n"/>
       <c r="O11" s="23" t="n"/>
       <c r="P11" s="23" t="n"/>
@@ -1445,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1503,17 +1505,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29 14:44:19</t>
+          <t>2026-10-29 14:50:59</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1523,15 +1525,13 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>1011</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>266</v>
-      </c>
+        <v>10100</v>
+      </c>
+      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>app</t>
@@ -1541,17 +1541,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29 09:14:12</t>
+          <t>2026-10-29 14:44:19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1565,29 +1565,31 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="G3" s="27" t="n"/>
+        <v>1011</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>266</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29 06:32:56</t>
+          <t>2026-10-29 09:14:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1601,19 +1603,19 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>266</v>
+        <v>30</v>
       </c>
       <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29 02:35:57</t>
+          <t>2026-10-29 06:32:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1633,15 +1635,13 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>21456</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>2371</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>app</t>
@@ -1651,17 +1651,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:12</t>
+          <t>2026-10-29 02:35:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1675,29 +1675,31 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>4018</v>
-      </c>
-      <c r="G6" s="27" t="n"/>
+        <v>21456</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>2371</v>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28 23:47:44</t>
+          <t>2026-10-29 00:00:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1711,21 +1713,19 @@
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>2371</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>371</v>
-      </c>
+        <v>4018</v>
+      </c>
+      <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28 23:46:44</t>
+          <t>2026-10-28 23:47:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1740,16 +1740,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>2371</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:32</t>
+          <t>2026-10-28 23:46:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1764,7 +1778,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F9" s="27" t="n"/>
@@ -1773,7 +1787,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28 17:45:48</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1788,30 +1802,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>271</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28 10:22:51</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1826,16 +1826,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>271</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1850,28 +1864,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n">
-        <v>271</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n"/>
       <c r="G12" s="27" t="n"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1891,15 +1893,13 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>1401</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G13" s="27" t="n"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>app</t>
@@ -1909,17 +1909,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1929,13 +1929,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>10320</v>
-      </c>
-      <c r="G14" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>app</t>
@@ -1945,7 +1947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1965,11 +1967,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>12221</v>
+        <v>10320</v>
       </c>
       <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
@@ -1981,7 +1983,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2001,11 +2003,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>10300</v>
+        <v>12221</v>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
@@ -2017,7 +2019,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2037,11 +2039,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>10595</v>
+        <v>10300</v>
       </c>
       <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
@@ -2053,7 +2055,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2073,11 +2075,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>11109</v>
+        <v>10595</v>
       </c>
       <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
@@ -2089,7 +2091,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2109,11 +2111,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>13681</v>
+        <v>11109</v>
       </c>
       <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
@@ -2125,17 +2127,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2145,15 +2147,13 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>13681</v>
+      </c>
+      <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>app</t>
@@ -2163,17 +2163,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2183,13 +2183,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G21" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>app</t>
@@ -2199,7 +2201,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2219,11 +2221,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>307</v>
+        <v>4640</v>
       </c>
       <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
@@ -2235,7 +2237,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2255,11 +2257,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>3787</v>
+        <v>307</v>
       </c>
       <c r="G23" s="27" t="n"/>
       <c r="H23" t="inlineStr">
@@ -2271,7 +2273,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2291,11 +2293,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>4947</v>
+        <v>3787</v>
       </c>
       <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
@@ -2307,17 +2309,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2327,11 +2329,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>311</v>
+        <v>4947</v>
       </c>
       <c r="G25" s="27" t="n"/>
       <c r="H25" t="inlineStr">
@@ -2343,7 +2345,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2363,15 +2365,13 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G26" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G26" s="27" t="n"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>app</t>
@@ -2381,7 +2381,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2396,16 +2396,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2420,40 +2434,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="27" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2467,29 +2467,31 @@
         </is>
       </c>
       <c r="F29" s="27" t="n">
-        <v>8300</v>
-      </c>
-      <c r="G29" s="27" t="n"/>
+        <v>1157</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>911</v>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2503,21 +2505,19 @@
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G30" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>8300</v>
+      </c>
+      <c r="G30" s="27" t="n"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2541,9 +2541,11 @@
         </is>
       </c>
       <c r="F31" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="G31" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G31" s="27" t="n"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>app</t>
@@ -2553,7 +2555,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2573,15 +2575,13 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F32" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G32" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G32" s="27" t="n"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>app</t>
@@ -2591,7 +2591,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="F33" s="27" t="n">
+        <v>20274</v>
+      </c>
+      <c r="G33" s="27" t="n">
         <v>3510</v>
-      </c>
-      <c r="G33" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2629,17 +2629,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2653,29 +2653,31 @@
         </is>
       </c>
       <c r="F34" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G34" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2689,19 +2691,19 @@
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>351</v>
+        <v>13001</v>
       </c>
       <c r="G35" s="27" t="n"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2716,16 +2718,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G36" s="27" t="n"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2740,40 +2754,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2787,29 +2787,31 @@
         </is>
       </c>
       <c r="F38" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G38" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G38" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2823,21 +2825,19 @@
         </is>
       </c>
       <c r="F39" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G39" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G39" s="27" t="n"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="F40" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G40" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G40" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2899,9 +2899,11 @@
         </is>
       </c>
       <c r="F41" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G41" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G41" s="27" t="n"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>app</t>
@@ -2911,7 +2913,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2931,15 +2933,13 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F42" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G42" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G42" s="27" t="n"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>app</t>
@@ -2949,7 +2949,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2964,16 +2964,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G43" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2988,40 +3002,26 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G44" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="27" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3031,13 +3031,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F45" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G45" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G45" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>app</t>
@@ -3047,7 +3049,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3067,15 +3069,13 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F46" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G46" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G46" s="27" t="n"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>app</t>
@@ -3085,7 +3085,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3105,11 +3105,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F47" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G47" s="27" t="n">
         <v>0</v>
@@ -3123,7 +3123,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3143,35 +3143,35 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F48" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3185,31 +3185,31 @@
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3223,29 +3223,31 @@
         </is>
       </c>
       <c r="F50" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G50" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3259,21 +3261,19 @@
         </is>
       </c>
       <c r="F51" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G51" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G51" s="27" t="n"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3288,16 +3288,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="n"/>
-      <c r="G52" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G52" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3312,28 +3326,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F53" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="n"/>
       <c r="G53" s="27" t="n"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3353,15 +3355,13 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F54" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G54" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G54" s="27" t="n"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>app</t>
@@ -3371,17 +3371,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3395,9 +3395,11 @@
         </is>
       </c>
       <c r="F55" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G55" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G55" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>app</t>
@@ -3407,31 +3409,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G56" s="27" t="n"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3446,7 +3460,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F57" s="27" t="n"/>
@@ -3455,53 +3469,41 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F58" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="n"/>
       <c r="G58" s="27" t="n"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3511,47 +3513,59 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F59" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G59" s="27" t="n"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G60" s="27" t="n"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3566,7 +3580,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F61" s="27" t="n"/>
@@ -3575,22 +3589,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F62" s="27" t="n"/>
@@ -3599,7 +3613,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3614,28 +3628,16 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F63" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="n"/>
       <c r="G63" s="27" t="n"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3655,15 +3657,13 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F64" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G64" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G64" s="27" t="n"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>app</t>
@@ -3673,7 +3673,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3688,16 +3688,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="n"/>
-      <c r="G65" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G65" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3712,7 +3726,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F66" s="27" t="n"/>
@@ -3721,103 +3735,91 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="n"/>
       <c r="G67" s="27" t="n"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F68" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F68" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G68" s="27" t="n"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n"/>
       <c r="G69" s="27" t="n"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3832,31 +3834,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G70" s="27" t="n"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
@@ -3865,7 +3879,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3880,28 +3894,16 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F72" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="n"/>
       <c r="G72" s="27" t="n"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3916,52 +3918,52 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G73" s="27" t="n"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="n"/>
       <c r="G74" s="27" t="n"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3976,16 +3978,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G75" s="27" t="n"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4000,7 +4014,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F76" s="27" t="n"/>
@@ -4009,69 +4023,69 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F77" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G77" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F77" s="27" t="n"/>
+      <c r="G77" s="27" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F78" s="27" t="n"/>
-      <c r="G78" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G78" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4086,7 +4100,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F79" s="27" t="n"/>
@@ -4095,43 +4109,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F80" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F80" s="27" t="n"/>
       <c r="G80" s="27" t="n"/>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4146,16 +4148,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F81" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F81" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G81" s="27" t="n"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4170,7 +4184,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F82" s="27" t="n"/>
@@ -4179,43 +4193,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F83" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F83" s="27" t="n"/>
       <c r="G83" s="27" t="n"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4235,11 +4237,11 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F84" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G84" s="27" t="n"/>
       <c r="H84" t="inlineStr">
@@ -4251,31 +4253,43 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F85" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F85" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G85" s="27" t="n"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4290,7 +4304,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F86" s="27" t="n"/>
@@ -4299,7 +4313,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4314,7 +4328,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F87" s="27" t="n"/>
@@ -4323,43 +4337,31 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F88" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F88" s="27" t="n"/>
       <c r="G88" s="27" t="n"/>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4374,26 +4376,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F89" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F89" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G89" s="27" t="n"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4407,7 +4421,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4422,7 +4436,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F91" s="27" t="n"/>
@@ -4431,7 +4445,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4446,7 +4460,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F92" s="27" t="n"/>
@@ -4455,7 +4469,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4470,7 +4484,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F93" s="27" t="n"/>
@@ -4479,7 +4493,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4494,7 +4508,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F94" s="27" t="n"/>
@@ -4503,7 +4517,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4518,7 +4532,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F95" s="27" t="n"/>
@@ -4527,22 +4541,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F96" s="27" t="n"/>
@@ -4551,7 +4565,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4575,7 +4589,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4590,7 +4604,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F98" s="27" t="n"/>
@@ -4599,7 +4613,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4614,7 +4628,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F99" s="27" t="n"/>
@@ -4623,7 +4637,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4638,7 +4652,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F100" s="27" t="n"/>
@@ -4647,7 +4661,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4662,7 +4676,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F101" s="27" t="n"/>
@@ -4671,7 +4685,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4695,7 +4709,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4710,7 +4724,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F103" s="27" t="n"/>
@@ -4719,7 +4733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4734,11 +4748,35 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F104" s="27" t="n"/>
       <c r="G104" s="27" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F105" s="27" t="n"/>
+      <c r="G105" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-29 14:51 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-29 16:30 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1016,7 +1016,7 @@
         <v>21456</v>
       </c>
       <c r="N6" s="23" t="n">
-        <v>1011</v>
+        <v>2210</v>
       </c>
       <c r="O6" s="23" t="n"/>
       <c r="P6" s="23" t="n"/>
@@ -1447,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1505,17 +1505,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29 14:50:59</t>
+          <t>2026-10-29 16:26:29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1525,13 +1525,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>10100</v>
-      </c>
-      <c r="G2" s="27" t="n"/>
+        <v>2210</v>
+      </c>
+      <c r="G2" s="27" t="n">
+        <v>1011</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>app</t>
@@ -1541,17 +1543,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29 14:44:19</t>
+          <t>2026-10-29 14:50:59</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1561,15 +1563,13 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>1011</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>266</v>
-      </c>
+        <v>10100</v>
+      </c>
+      <c r="G3" s="27" t="n"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>app</t>
@@ -1579,17 +1579,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29 09:14:12</t>
+          <t>2026-10-29 14:44:19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1603,29 +1603,31 @@
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="G4" s="27" t="n"/>
+        <v>1011</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>266</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29 06:32:56</t>
+          <t>2026-10-29 09:14:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1639,19 +1641,19 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>266</v>
+        <v>30</v>
       </c>
       <c r="G5" s="27" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29 02:35:57</t>
+          <t>2026-10-29 06:32:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1671,15 +1673,13 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>21456</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>2371</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>app</t>
@@ -1689,17 +1689,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:12</t>
+          <t>2026-10-29 02:35:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1713,29 +1713,31 @@
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>4018</v>
-      </c>
-      <c r="G7" s="27" t="n"/>
+        <v>21456</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>2371</v>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28 23:47:44</t>
+          <t>2026-10-29 00:00:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1749,21 +1751,19 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>2371</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>371</v>
-      </c>
+        <v>4018</v>
+      </c>
+      <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28 23:46:44</t>
+          <t>2026-10-28 23:47:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1778,16 +1778,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>2371</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:32</t>
+          <t>2026-10-28 23:46:44</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1802,7 +1816,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F10" s="27" t="n"/>
@@ -1811,7 +1825,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28 17:45:48</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1826,30 +1840,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>271</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28 10:22:51</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1864,16 +1864,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>271</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1888,28 +1902,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>271</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n"/>
       <c r="G13" s="27" t="n"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1929,15 +1931,13 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>1401</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G14" s="27" t="n"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>app</t>
@@ -1947,17 +1947,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1967,13 +1967,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>10320</v>
-      </c>
-      <c r="G15" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>app</t>
@@ -1983,7 +1985,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2003,11 +2005,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>12221</v>
+        <v>10320</v>
       </c>
       <c r="G16" s="27" t="n"/>
       <c r="H16" t="inlineStr">
@@ -2019,7 +2021,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2039,11 +2041,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>10300</v>
+        <v>12221</v>
       </c>
       <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
@@ -2055,7 +2057,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2075,11 +2077,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>10595</v>
+        <v>10300</v>
       </c>
       <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
@@ -2091,7 +2093,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2111,11 +2113,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>11109</v>
+        <v>10595</v>
       </c>
       <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
@@ -2127,7 +2129,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2147,11 +2149,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>13681</v>
+        <v>11109</v>
       </c>
       <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
@@ -2163,17 +2165,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2183,15 +2185,13 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G21" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>13681</v>
+      </c>
+      <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>app</t>
@@ -2201,17 +2201,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2221,13 +2221,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G22" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>app</t>
@@ -2237,7 +2239,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2257,11 +2259,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>307</v>
+        <v>4640</v>
       </c>
       <c r="G23" s="27" t="n"/>
       <c r="H23" t="inlineStr">
@@ -2273,7 +2275,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2293,11 +2295,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>3787</v>
+        <v>307</v>
       </c>
       <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
@@ -2309,7 +2311,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2329,11 +2331,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>4947</v>
+        <v>3787</v>
       </c>
       <c r="G25" s="27" t="n"/>
       <c r="H25" t="inlineStr">
@@ -2345,17 +2347,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2365,11 +2367,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>311</v>
+        <v>4947</v>
       </c>
       <c r="G26" s="27" t="n"/>
       <c r="H26" t="inlineStr">
@@ -2381,7 +2383,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2401,15 +2403,13 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G27" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G27" s="27" t="n"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>app</t>
@@ -2419,7 +2419,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2434,16 +2434,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G28" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2458,40 +2472,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="27" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2505,29 +2505,31 @@
         </is>
       </c>
       <c r="F30" s="27" t="n">
-        <v>8300</v>
-      </c>
-      <c r="G30" s="27" t="n"/>
+        <v>1157</v>
+      </c>
+      <c r="G30" s="27" t="n">
+        <v>911</v>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2541,21 +2543,19 @@
         </is>
       </c>
       <c r="F31" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G31" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>8300</v>
+      </c>
+      <c r="G31" s="27" t="n"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2579,9 +2579,11 @@
         </is>
       </c>
       <c r="F32" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="G32" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G32" s="27" t="n"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>app</t>
@@ -2591,7 +2593,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2611,15 +2613,13 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F33" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G33" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G33" s="27" t="n"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>app</t>
@@ -2629,7 +2629,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="F34" s="27" t="n">
+        <v>20274</v>
+      </c>
+      <c r="G34" s="27" t="n">
         <v>3510</v>
-      </c>
-      <c r="G34" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2667,17 +2667,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2691,29 +2691,31 @@
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G35" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2727,19 +2729,19 @@
         </is>
       </c>
       <c r="F36" s="27" t="n">
-        <v>351</v>
+        <v>13001</v>
       </c>
       <c r="G36" s="27" t="n"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2754,16 +2756,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G37" s="27" t="n"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2778,40 +2792,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G38" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
+      <c r="G38" s="27" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2825,29 +2825,31 @@
         </is>
       </c>
       <c r="F39" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G39" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G39" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2861,21 +2863,19 @@
         </is>
       </c>
       <c r="F40" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G40" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G40" s="27" t="n"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F41" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G41" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G41" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2937,9 +2937,11 @@
         </is>
       </c>
       <c r="F42" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G42" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G42" s="27" t="n"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>app</t>
@@ -2949,7 +2951,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2969,15 +2971,13 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F43" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G43" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G43" s="27" t="n"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>app</t>
@@ -2987,7 +2987,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3002,16 +3002,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G44" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3026,40 +3040,26 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G45" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n"/>
+      <c r="G45" s="27" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3069,13 +3069,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F46" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G46" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>app</t>
@@ -3085,7 +3087,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3105,15 +3107,13 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F47" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G47" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G47" s="27" t="n"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>app</t>
@@ -3123,7 +3123,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3143,11 +3143,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F48" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>0</v>
@@ -3161,7 +3161,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3181,35 +3181,35 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G49" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3223,31 +3223,31 @@
         </is>
       </c>
       <c r="F50" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G50" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3261,29 +3261,31 @@
         </is>
       </c>
       <c r="F51" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G51" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3297,21 +3299,19 @@
         </is>
       </c>
       <c r="F52" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G52" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G52" s="27" t="n"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3326,16 +3326,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F53" s="27" t="n"/>
-      <c r="G53" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G53" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3350,28 +3364,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n"/>
       <c r="G54" s="27" t="n"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3391,15 +3393,13 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F55" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G55" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G55" s="27" t="n"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>app</t>
@@ -3409,17 +3409,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3433,9 +3433,11 @@
         </is>
       </c>
       <c r="F56" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G56" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G56" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>app</t>
@@ -3445,31 +3447,43 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G57" s="27" t="n"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3484,7 +3498,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F58" s="27" t="n"/>
@@ -3493,53 +3507,41 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n"/>
       <c r="G59" s="27" t="n"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3549,47 +3551,59 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F60" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G60" s="27" t="n"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F61" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G61" s="27" t="n"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3604,7 +3618,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F62" s="27" t="n"/>
@@ -3613,22 +3627,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3637,7 +3651,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3652,28 +3666,16 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F64" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="n"/>
       <c r="G64" s="27" t="n"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3693,15 +3695,13 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F65" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G65" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G65" s="27" t="n"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>app</t>
@@ -3711,7 +3711,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3726,16 +3726,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F66" s="27" t="n"/>
-      <c r="G66" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G66" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3750,7 +3764,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F67" s="27" t="n"/>
@@ -3759,103 +3773,91 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F68" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F68" s="27" t="n"/>
       <c r="G68" s="27" t="n"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G69" s="27" t="n"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n"/>
       <c r="G70" s="27" t="n"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3870,31 +3872,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F71" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F71" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G71" s="27" t="n"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F72" s="27" t="n"/>
@@ -3903,7 +3917,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3918,28 +3932,16 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="n"/>
       <c r="G73" s="27" t="n"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3954,52 +3956,52 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G74" s="27" t="n"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="n"/>
       <c r="G75" s="27" t="n"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4014,16 +4016,28 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F76" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G76" s="27" t="n"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4038,7 +4052,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F77" s="27" t="n"/>
@@ -4047,69 +4061,69 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F78" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G78" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="n"/>
+      <c r="G78" s="27" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F79" s="27" t="n"/>
-      <c r="G79" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F79" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G79" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4124,7 +4138,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F80" s="27" t="n"/>
@@ -4133,43 +4147,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F81" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F81" s="27" t="n"/>
       <c r="G81" s="27" t="n"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4184,16 +4186,28 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F82" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F82" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G82" s="27" t="n"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4208,7 +4222,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F83" s="27" t="n"/>
@@ -4217,43 +4231,31 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F84" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F84" s="27" t="n"/>
       <c r="G84" s="27" t="n"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4273,11 +4275,11 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F85" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G85" s="27" t="n"/>
       <c r="H85" t="inlineStr">
@@ -4289,31 +4291,43 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F86" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F86" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G86" s="27" t="n"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4328,7 +4342,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F87" s="27" t="n"/>
@@ -4337,7 +4351,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4352,7 +4366,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F88" s="27" t="n"/>
@@ -4361,43 +4375,31 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F89" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F89" s="27" t="n"/>
       <c r="G89" s="27" t="n"/>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4412,26 +4414,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F90" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F90" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G90" s="27" t="n"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4445,7 +4459,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4460,7 +4474,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F92" s="27" t="n"/>
@@ -4469,7 +4483,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4484,7 +4498,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F93" s="27" t="n"/>
@@ -4493,7 +4507,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4508,7 +4522,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F94" s="27" t="n"/>
@@ -4517,7 +4531,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4532,7 +4546,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F95" s="27" t="n"/>
@@ -4541,7 +4555,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4556,7 +4570,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F96" s="27" t="n"/>
@@ -4565,22 +4579,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F97" s="27" t="n"/>
@@ -4589,7 +4603,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4613,7 +4627,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4628,7 +4642,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F99" s="27" t="n"/>
@@ -4637,7 +4651,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4652,7 +4666,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F100" s="27" t="n"/>
@@ -4661,7 +4675,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4676,7 +4690,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F101" s="27" t="n"/>
@@ -4685,7 +4699,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4700,7 +4714,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F102" s="27" t="n"/>
@@ -4709,7 +4723,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4733,7 +4747,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4748,7 +4762,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F104" s="27" t="n"/>
@@ -4757,7 +4771,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4772,11 +4786,35 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F105" s="27" t="n"/>
       <c r="G105" s="27" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F106" s="27" t="n"/>
+      <c r="G106" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-29 16:30 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-30 00:39 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>4018</v>
       </c>
       <c r="N8" s="23" t="n">
-        <v>30</v>
+        <v>6655</v>
       </c>
       <c r="O8" s="23" t="n"/>
       <c r="P8" s="23" t="n"/>
@@ -1447,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1505,17 +1505,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:26:29</t>
+          <t>2026-10-30 00:00:15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1529,31 +1529,31 @@
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>2210</v>
+        <v>6655</v>
       </c>
       <c r="G2" s="27" t="n">
-        <v>1011</v>
+        <v>30</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29 14:50:59</t>
+          <t>2026-10-29 16:26:29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1563,13 +1563,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>10100</v>
-      </c>
-      <c r="G3" s="27" t="n"/>
+        <v>2210</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>1011</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>app</t>
@@ -1579,17 +1581,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29 14:44:19</t>
+          <t>2026-10-29 14:50:59</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1599,15 +1601,13 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>1011</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>266</v>
-      </c>
+        <v>10100</v>
+      </c>
+      <c r="G4" s="27" t="n"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>app</t>
@@ -1617,17 +1617,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29 09:14:12</t>
+          <t>2026-10-29 14:44:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1641,29 +1641,31 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="G5" s="27" t="n"/>
+        <v>1011</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>266</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29 06:32:56</t>
+          <t>2026-10-29 09:14:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1677,19 +1679,19 @@
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>266</v>
+        <v>30</v>
       </c>
       <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29 02:35:57</t>
+          <t>2026-10-29 06:32:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1709,15 +1711,13 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>21456</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>2371</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>app</t>
@@ -1727,17 +1727,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:12</t>
+          <t>2026-10-29 02:35:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1751,29 +1751,31 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>4018</v>
-      </c>
-      <c r="G8" s="27" t="n"/>
+        <v>21456</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>2371</v>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28 23:47:44</t>
+          <t>2026-10-29 00:00:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1787,21 +1789,19 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>2371</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>371</v>
-      </c>
+        <v>4018</v>
+      </c>
+      <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28 23:46:44</t>
+          <t>2026-10-28 23:47:44</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1816,16 +1816,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>2371</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:32</t>
+          <t>2026-10-28 23:46:44</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1840,7 +1854,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F11" s="27" t="n"/>
@@ -1849,7 +1863,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28 17:45:48</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1864,30 +1878,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>271</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28 10:22:51</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1902,16 +1902,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>271</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1926,28 +1940,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="n">
-        <v>271</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n"/>
       <c r="G14" s="27" t="n"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1967,15 +1969,13 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>1401</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>app</t>
@@ -1985,17 +1985,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2005,13 +2005,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>10320</v>
-      </c>
-      <c r="G16" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>app</t>
@@ -2021,7 +2023,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2041,11 +2043,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>12221</v>
+        <v>10320</v>
       </c>
       <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
@@ -2057,7 +2059,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2077,11 +2079,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>10300</v>
+        <v>12221</v>
       </c>
       <c r="G18" s="27" t="n"/>
       <c r="H18" t="inlineStr">
@@ -2093,7 +2095,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2113,11 +2115,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>10595</v>
+        <v>10300</v>
       </c>
       <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
@@ -2129,7 +2131,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2149,11 +2151,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>11109</v>
+        <v>10595</v>
       </c>
       <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
@@ -2165,7 +2167,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2185,11 +2187,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>13681</v>
+        <v>11109</v>
       </c>
       <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
@@ -2201,17 +2203,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2221,15 +2223,13 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G22" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>13681</v>
+      </c>
+      <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>app</t>
@@ -2239,17 +2239,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2259,13 +2259,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G23" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G23" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>app</t>
@@ -2275,7 +2277,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2295,11 +2297,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>307</v>
+        <v>4640</v>
       </c>
       <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
@@ -2311,7 +2313,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2331,11 +2333,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>3787</v>
+        <v>307</v>
       </c>
       <c r="G25" s="27" t="n"/>
       <c r="H25" t="inlineStr">
@@ -2347,7 +2349,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2367,11 +2369,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>4947</v>
+        <v>3787</v>
       </c>
       <c r="G26" s="27" t="n"/>
       <c r="H26" t="inlineStr">
@@ -2383,17 +2385,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2403,11 +2405,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>311</v>
+        <v>4947</v>
       </c>
       <c r="G27" s="27" t="n"/>
       <c r="H27" t="inlineStr">
@@ -2419,7 +2421,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2439,15 +2441,13 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F28" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G28" s="27" t="n"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>app</t>
@@ -2457,7 +2457,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2472,16 +2472,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2496,40 +2510,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G30" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="27" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2543,29 +2543,31 @@
         </is>
       </c>
       <c r="F31" s="27" t="n">
-        <v>8300</v>
-      </c>
-      <c r="G31" s="27" t="n"/>
+        <v>1157</v>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>911</v>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2579,21 +2581,19 @@
         </is>
       </c>
       <c r="F32" s="27" t="n">
-        <v>911</v>
-      </c>
-      <c r="G32" s="27" t="n">
-        <v>351</v>
-      </c>
+        <v>8300</v>
+      </c>
+      <c r="G32" s="27" t="n"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2617,9 +2617,11 @@
         </is>
       </c>
       <c r="F33" s="27" t="n">
+        <v>911</v>
+      </c>
+      <c r="G33" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G33" s="27" t="n"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>app</t>
@@ -2629,7 +2631,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2649,15 +2651,13 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F34" s="27" t="n">
-        <v>20274</v>
-      </c>
-      <c r="G34" s="27" t="n">
-        <v>3510</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G34" s="27" t="n"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>app</t>
@@ -2667,7 +2667,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="F35" s="27" t="n">
+        <v>20274</v>
+      </c>
+      <c r="G35" s="27" t="n">
         <v>3510</v>
-      </c>
-      <c r="G35" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2705,17 +2705,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2729,29 +2729,31 @@
         </is>
       </c>
       <c r="F36" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G36" s="27" t="n"/>
+        <v>3510</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2765,19 +2767,19 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>351</v>
+        <v>13001</v>
       </c>
       <c r="G37" s="27" t="n"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2792,16 +2794,28 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>351</v>
+      </c>
       <c r="G38" s="27" t="n"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2816,40 +2830,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G39" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2863,29 +2863,31 @@
         </is>
       </c>
       <c r="F40" s="27" t="n">
-        <v>7493</v>
-      </c>
-      <c r="G40" s="27" t="n"/>
+        <v>8060</v>
+      </c>
+      <c r="G40" s="27" t="n">
+        <v>122</v>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2899,21 +2901,19 @@
         </is>
       </c>
       <c r="F41" s="27" t="n">
-        <v>122</v>
-      </c>
-      <c r="G41" s="27" t="n">
-        <v>121</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G41" s="27" t="n"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="F42" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="G42" s="27" t="n">
         <v>121</v>
-      </c>
-      <c r="G42" s="27" t="n">
-        <v>120</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2975,9 +2975,11 @@
         </is>
       </c>
       <c r="F43" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G43" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="G43" s="27" t="n"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>app</t>
@@ -2987,7 +2989,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3007,15 +3009,13 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F44" s="27" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G44" s="27" t="n">
-        <v>2680</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G44" s="27" t="n"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>app</t>
@@ -3025,7 +3025,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3040,16 +3040,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G45" s="27" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3064,40 +3078,26 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n">
-        <v>2680</v>
-      </c>
-      <c r="G46" s="27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n"/>
+      <c r="G46" s="27" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3107,13 +3107,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F47" s="27" t="n">
-        <v>4933</v>
-      </c>
-      <c r="G47" s="27" t="n"/>
+        <v>2680</v>
+      </c>
+      <c r="G47" s="27" t="n">
+        <v>2650</v>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>app</t>
@@ -3123,7 +3125,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3143,15 +3145,13 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F48" s="27" t="n">
-        <v>7567</v>
-      </c>
-      <c r="G48" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G48" s="27" t="n"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>app</t>
@@ -3161,7 +3161,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3181,11 +3181,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>4189</v>
+        <v>7567</v>
       </c>
       <c r="G49" s="27" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3219,35 +3219,35 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F50" s="27" t="n">
-        <v>3685</v>
+        <v>4189</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3261,31 +3261,31 @@
         </is>
       </c>
       <c r="F51" s="27" t="n">
-        <v>2650</v>
+        <v>3685</v>
       </c>
       <c r="G51" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3299,29 +3299,31 @@
         </is>
       </c>
       <c r="F52" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="27" t="n"/>
+        <v>2650</v>
+      </c>
+      <c r="G52" s="27" t="n">
+        <v>831</v>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3335,21 +3337,19 @@
         </is>
       </c>
       <c r="F53" s="27" t="n">
-        <v>831</v>
-      </c>
-      <c r="G53" s="27" t="n">
-        <v>387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G53" s="27" t="n"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3364,16 +3364,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="n"/>
-      <c r="G54" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G54" s="27" t="n">
+        <v>387</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3388,28 +3402,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="n">
-        <v>387</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n"/>
       <c r="G55" s="27" t="n"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3429,15 +3431,13 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F56" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G56" s="27" t="n">
-        <v>1100</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G56" s="27" t="n"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>app</t>
@@ -3447,17 +3447,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3471,9 +3471,11 @@
         </is>
       </c>
       <c r="F57" s="27" t="n">
-        <v>9097</v>
-      </c>
-      <c r="G57" s="27" t="n"/>
+        <v>9720</v>
+      </c>
+      <c r="G57" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>app</t>
@@ -3483,31 +3485,43 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F58" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G58" s="27" t="n"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3522,7 +3536,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F59" s="27" t="n"/>
@@ -3531,53 +3545,41 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n"/>
       <c r="G60" s="27" t="n"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3587,47 +3589,59 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F61" s="27" t="n">
-        <v>0</v>
+        <v>10808</v>
       </c>
       <c r="G61" s="27" t="n"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F62" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G62" s="27" t="n"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3642,7 +3656,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F63" s="27" t="n"/>
@@ -3651,22 +3665,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F64" s="27" t="n"/>
@@ -3675,7 +3689,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3690,28 +3704,16 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="n"/>
       <c r="G65" s="27" t="n"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3731,15 +3733,13 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F66" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G66" s="27" t="n">
-        <v>1985</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="G66" s="27" t="n"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>app</t>
@@ -3749,7 +3749,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3764,16 +3764,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="n"/>
-      <c r="G67" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G67" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3788,7 +3802,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>unstory</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F68" s="27" t="n"/>
@@ -3797,103 +3811,91 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>unstory</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n"/>
       <c r="G69" s="27" t="n"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n">
+        <v>4842</v>
+      </c>
       <c r="G70" s="27" t="n"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F71" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F71" s="27" t="n"/>
       <c r="G71" s="27" t="n"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3908,31 +3910,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F72" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G72" s="27" t="n"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F73" s="27" t="n"/>
@@ -3941,7 +3955,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3956,28 +3970,16 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="n"/>
       <c r="G74" s="27" t="n"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3992,52 +3994,52 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="n">
+        <v>12641</v>
+      </c>
       <c r="G75" s="27" t="n"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F76" s="27" t="n">
-        <v>5345</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="n"/>
       <c r="G76" s="27" t="n"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4052,16 +4054,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F77" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F77" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G77" s="27" t="n"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4076,7 +4090,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F78" s="27" t="n"/>
@@ -4085,69 +4099,69 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F79" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G79" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F79" s="27" t="n"/>
+      <c r="G79" s="27" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F80" s="27" t="n"/>
-      <c r="G80" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F80" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G80" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4162,7 +4176,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F81" s="27" t="n"/>
@@ -4171,43 +4185,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F82" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F82" s="27" t="n"/>
       <c r="G82" s="27" t="n"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4222,16 +4224,28 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F83" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F83" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G83" s="27" t="n"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4246,7 +4260,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F84" s="27" t="n"/>
@@ -4255,43 +4269,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F85" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F85" s="27" t="n"/>
       <c r="G85" s="27" t="n"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4311,11 +4313,11 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F86" s="27" t="n">
-        <v>9060</v>
+        <v>100</v>
       </c>
       <c r="G86" s="27" t="n"/>
       <c r="H86" t="inlineStr">
@@ -4327,31 +4329,43 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F87" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F87" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G87" s="27" t="n"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4366,7 +4380,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F88" s="27" t="n"/>
@@ -4375,7 +4389,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4390,7 +4404,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F89" s="27" t="n"/>
@@ -4399,43 +4413,31 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:42:39</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F90" s="27" t="n">
-        <v>6310</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F90" s="27" t="n"/>
       <c r="G90" s="27" t="n"/>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-21 03:05:30</t>
+          <t>2026-10-21 04:34:33</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4450,26 +4452,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F91" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F91" s="27" t="n">
+        <v>6310</v>
+      </c>
       <c r="G91" s="27" t="n"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-20 21:27:27</t>
+          <t>2026-10-21 03:05:30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>helbert</t>
+          <t>rogelio</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Helbert Contreras</t>
+          <t>Rogelio Garcia</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4483,7 +4497,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:09</t>
+          <t>2026-10-20 21:27:27</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4498,7 +4512,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F93" s="27" t="n"/>
@@ -4507,7 +4521,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-20 21:24:07</t>
+          <t>2026-10-20 21:24:09</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4522,7 +4536,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F94" s="27" t="n"/>
@@ -4531,7 +4545,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:48</t>
+          <t>2026-10-20 21:24:07</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4546,7 +4560,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F95" s="27" t="n"/>
@@ -4555,7 +4569,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-20 21:23:44</t>
+          <t>2026-10-20 21:23:48</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4570,7 +4584,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F96" s="27" t="n"/>
@@ -4579,7 +4593,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-20 21:20:08</t>
+          <t>2026-10-20 21:23:44</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4594,7 +4608,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F97" s="27" t="n"/>
@@ -4603,22 +4617,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-20 20:48:02</t>
+          <t>2026-10-20 21:20:08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>helbert</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Helbert Contreras</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F98" s="27" t="n"/>
@@ -4627,7 +4641,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:34</t>
+          <t>2026-10-20 20:48:02</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4651,7 +4665,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-20 20:41:28</t>
+          <t>2026-10-20 20:41:34</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4666,7 +4680,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F100" s="27" t="n"/>
@@ -4675,7 +4689,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-20 20:27:02</t>
+          <t>2026-10-20 20:41:28</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4690,7 +4704,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F101" s="27" t="n"/>
@@ -4699,7 +4713,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-20 20:22:11</t>
+          <t>2026-10-20 20:27:02</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4714,7 +4728,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F102" s="27" t="n"/>
@@ -4723,7 +4737,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-20 20:20:27</t>
+          <t>2026-10-20 20:22:11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4738,7 +4752,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>requested</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="F103" s="27" t="n"/>
@@ -4747,7 +4761,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-10-20 19:58:34</t>
+          <t>2026-10-20 20:20:27</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4771,7 +4785,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:19</t>
+          <t>2026-10-20 19:58:34</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4786,7 +4800,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>requested</t>
         </is>
       </c>
       <c r="F105" s="27" t="n"/>
@@ -4795,7 +4809,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-10-20 19:11:09</t>
+          <t>2026-10-20 19:11:19</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4810,11 +4824,35 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F106" s="27" t="n"/>
       <c r="G106" s="27" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:11:09</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>eron</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Eron Netto</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F107" s="27" t="n"/>
+      <c r="G107" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/step-tracking_Team8.xlsx
+++ b/step-tracking_Team8.xlsx
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>Updated 2026-10-30 00:39 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
+          <t>Updated 2026-10-30 03:28 UTC by the Nokia - Step Challenge 2026 - Team 8 app</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1016,9 +1016,11 @@
         <v>21456</v>
       </c>
       <c r="N6" s="23" t="n">
-        <v>2210</v>
-      </c>
-      <c r="O6" s="23" t="n"/>
+        <v>10401</v>
+      </c>
+      <c r="O6" s="23" t="n">
+        <v>251</v>
+      </c>
       <c r="P6" s="23" t="n"/>
       <c r="Q6" s="23" t="n"/>
       <c r="R6" s="24" t="n"/>
@@ -1447,7 +1449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1505,17 +1507,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-30 00:00:15</t>
+          <t>2026-10-30 03:19:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1525,25 +1527,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F2" s="27" t="n">
-        <v>6655</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>30</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="G2" s="27" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29 16:26:29</t>
+          <t>2026-10-30 03:18:50</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
+        <v>10401</v>
+      </c>
+      <c r="G3" s="27" t="n">
         <v>2210</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>1011</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1581,17 +1581,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29 14:50:59</t>
+          <t>2026-10-30 00:00:15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1601,23 +1601,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>10100</v>
-      </c>
-      <c r="G4" s="27" t="n"/>
+        <v>6655</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>30</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29 14:44:19</t>
+          <t>2026-10-29 16:26:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1641,10 +1643,10 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
+        <v>2210</v>
+      </c>
+      <c r="G5" s="27" t="n">
         <v>1011</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>266</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1655,17 +1657,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29 09:14:12</t>
+          <t>2026-10-29 14:50:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1675,23 +1677,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>30</v>
+        <v>10100</v>
       </c>
       <c r="G6" s="27" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29 06:32:56</t>
+          <t>2026-10-29 14:44:19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1715,9 +1717,11 @@
         </is>
       </c>
       <c r="F7" s="27" t="n">
+        <v>1011</v>
+      </c>
+      <c r="G7" s="27" t="n">
         <v>266</v>
       </c>
-      <c r="G7" s="27" t="n"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>app</t>
@@ -1727,17 +1731,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29 02:35:57</t>
+          <t>2026-10-29 09:14:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1747,35 +1751,33 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>21456</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>2371</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G8" s="27" t="n"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:12</t>
+          <t>2026-10-29 06:32:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1785,23 +1787,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>4018</v>
+        <v>266</v>
       </c>
       <c r="G9" s="27" t="n"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28 23:47:44</t>
+          <t>2026-10-29 02:35:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1825,10 +1827,10 @@
         </is>
       </c>
       <c r="F10" s="27" t="n">
+        <v>21456</v>
+      </c>
+      <c r="G10" s="27" t="n">
         <v>2371</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>371</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1839,31 +1841,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28 23:46:44</t>
+          <t>2026-10-29 00:00:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>4018</v>
+      </c>
       <c r="G11" s="27" t="n"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28 21:24:32</t>
+          <t>2026-10-28 23:47:44</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1878,16 +1892,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>2371</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28 17:45:48</t>
+          <t>2026-10-28 23:46:44</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1902,30 +1930,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>371</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>271</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="27" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28 10:22:51</t>
+          <t>2026-10-28 21:24:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1940,7 +1954,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F14" s="27" t="n"/>
@@ -1949,7 +1963,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-28 06:27:01</t>
+          <t>2026-10-28 17:45:48</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1973,9 +1987,11 @@
         </is>
       </c>
       <c r="F15" s="27" t="n">
+        <v>371</v>
+      </c>
+      <c r="G15" s="27" t="n">
         <v>271</v>
       </c>
-      <c r="G15" s="27" t="n"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>app</t>
@@ -1985,7 +2001,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-28 06:26:50</t>
+          <t>2026-10-28 10:22:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2000,40 +2016,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-28 05:23:00</t>
+          <t>2026-10-28 06:27:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2043,11 +2045,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>10320</v>
+        <v>271</v>
       </c>
       <c r="G17" s="27" t="n"/>
       <c r="H17" t="inlineStr">
@@ -2059,17 +2061,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-28 05:21:45</t>
+          <t>2026-10-28 06:26:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2083,9 +2085,11 @@
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>12221</v>
-      </c>
-      <c r="G18" s="27" t="n"/>
+        <v>9670</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>1401</v>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>app</t>
@@ -2095,7 +2099,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-28 05:20:41</t>
+          <t>2026-10-28 05:23:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2115,11 +2119,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>10300</v>
+        <v>10320</v>
       </c>
       <c r="G19" s="27" t="n"/>
       <c r="H19" t="inlineStr">
@@ -2131,7 +2135,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-28 05:15:21</t>
+          <t>2026-10-28 05:21:45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2151,11 +2155,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>10595</v>
+        <v>12221</v>
       </c>
       <c r="G20" s="27" t="n"/>
       <c r="H20" t="inlineStr">
@@ -2167,7 +2171,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-28 05:13:25</t>
+          <t>2026-10-28 05:20:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2187,11 +2191,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>11109</v>
+        <v>10300</v>
       </c>
       <c r="G21" s="27" t="n"/>
       <c r="H21" t="inlineStr">
@@ -2203,7 +2207,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-28 05:12:16</t>
+          <t>2026-10-28 05:15:21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2223,11 +2227,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>13681</v>
+        <v>10595</v>
       </c>
       <c r="G22" s="27" t="n"/>
       <c r="H22" t="inlineStr">
@@ -2239,17 +2243,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 15:27:47</t>
+          <t>2026-10-28 05:13:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2259,15 +2263,13 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G23" s="27" t="n">
-        <v>311</v>
-      </c>
+        <v>11109</v>
+      </c>
+      <c r="G23" s="27" t="n"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>app</t>
@@ -2277,17 +2279,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45:13</t>
+          <t>2026-10-28 05:12:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2297,11 +2299,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>4640</v>
+        <v>13681</v>
       </c>
       <c r="G24" s="27" t="n"/>
       <c r="H24" t="inlineStr">
@@ -2313,17 +2315,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:39</t>
+          <t>2026-10-27 15:27:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2333,13 +2335,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>307</v>
-      </c>
-      <c r="G25" s="27" t="n"/>
+        <v>1401</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>app</t>
@@ -2349,7 +2353,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-27 14:44:05</t>
+          <t>2026-10-27 14:45:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2369,11 +2373,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>3787</v>
+        <v>4640</v>
       </c>
       <c r="G26" s="27" t="n"/>
       <c r="H26" t="inlineStr">
@@ -2385,7 +2389,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27 14:41:31</t>
+          <t>2026-10-27 14:44:39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2405,11 +2409,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>4947</v>
+        <v>307</v>
       </c>
       <c r="G27" s="27" t="n"/>
       <c r="H27" t="inlineStr">
@@ -2421,17 +2425,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:15</t>
+          <t>2026-10-27 14:44:05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2441,11 +2445,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F28" s="27" t="n">
-        <v>311</v>
+        <v>3787</v>
       </c>
       <c r="G28" s="27" t="n"/>
       <c r="H28" t="inlineStr">
@@ -2457,17 +2461,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-27 10:23:08</t>
+          <t>2026-10-27 14:41:31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2477,15 +2481,13 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F29" s="27" t="n">
-        <v>15809</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>1157</v>
-      </c>
+        <v>4947</v>
+      </c>
+      <c r="G29" s="27" t="n"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>app</t>
@@ -2495,7 +2497,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-27 00:10:08</t>
+          <t>2026-10-27 10:23:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2510,16 +2512,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>311</v>
+      </c>
       <c r="G30" s="27" t="n"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:51</t>
+          <t>2026-10-27 10:23:08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2543,10 +2557,10 @@
         </is>
       </c>
       <c r="F31" s="27" t="n">
+        <v>15809</v>
+      </c>
+      <c r="G31" s="27" t="n">
         <v>1157</v>
-      </c>
-      <c r="G31" s="27" t="n">
-        <v>911</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2557,43 +2571,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02:49</t>
+          <t>2026-10-27 00:10:08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n">
-        <v>8300</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n"/>
       <c r="G32" s="27" t="n"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42:55</t>
+          <t>2026-10-27 00:07:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2617,10 +2619,10 @@
         </is>
       </c>
       <c r="F33" s="27" t="n">
+        <v>1157</v>
+      </c>
+      <c r="G33" s="27" t="n">
         <v>911</v>
-      </c>
-      <c r="G33" s="27" t="n">
-        <v>351</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2631,17 +2633,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:47</t>
+          <t>2026-10-27 00:02:49</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2655,19 +2657,19 @@
         </is>
       </c>
       <c r="F34" s="27" t="n">
-        <v>351</v>
+        <v>8300</v>
       </c>
       <c r="G34" s="27" t="n"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-26 03:51:39</t>
+          <t>2026-10-26 14:42:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2687,14 +2689,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>20274</v>
+        <v>911</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>3510</v>
+        <v>351</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2705,7 +2707,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-26 01:16:52</t>
+          <t>2026-10-26 03:51:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2725,15 +2727,13 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F36" s="27" t="n">
-        <v>3510</v>
-      </c>
-      <c r="G36" s="27" t="n">
         <v>351</v>
       </c>
+      <c r="G36" s="27" t="n"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>app</t>
@@ -2743,17 +2743,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-26 00:07:57</t>
+          <t>2026-10-26 03:51:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2767,19 +2767,21 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>13001</v>
-      </c>
-      <c r="G37" s="27" t="n"/>
+        <v>20274</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <v>3510</v>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-25 16:12:55</t>
+          <t>2026-10-26 01:16:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2803,9 +2805,11 @@
         </is>
       </c>
       <c r="F38" s="27" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G38" s="27" t="n">
         <v>351</v>
       </c>
-      <c r="G38" s="27" t="n"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>app</t>
@@ -2815,31 +2819,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:56</t>
+          <t>2026-10-26 00:07:57</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>13001</v>
+      </c>
       <c r="G39" s="27" t="n"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-25 02:00:55</t>
+          <t>2026-10-25 16:12:55</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2859,15 +2875,13 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F40" s="27" t="n">
-        <v>8060</v>
-      </c>
-      <c r="G40" s="27" t="n">
-        <v>122</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G40" s="27" t="n"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>app</t>
@@ -2877,43 +2891,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-25 00:11:33</t>
+          <t>2026-10-25 12:15:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="n">
-        <v>7493</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="n"/>
       <c r="G41" s="27" t="n"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:21</t>
+          <t>2026-10-25 02:00:55</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2937,10 +2939,10 @@
         </is>
       </c>
       <c r="F42" s="27" t="n">
+        <v>8060</v>
+      </c>
+      <c r="G42" s="27" t="n">
         <v>122</v>
-      </c>
-      <c r="G42" s="27" t="n">
-        <v>121</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2951,17 +2953,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-24 16:46:10</t>
+          <t>2026-10-25 00:11:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2975,21 +2977,19 @@
         </is>
       </c>
       <c r="F43" s="27" t="n">
-        <v>121</v>
-      </c>
-      <c r="G43" s="27" t="n">
-        <v>120</v>
-      </c>
+        <v>7493</v>
+      </c>
+      <c r="G43" s="27" t="n"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>shortcut</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-24 08:35:48</t>
+          <t>2026-10-24 16:46:21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3013,9 +3013,11 @@
         </is>
       </c>
       <c r="F44" s="27" t="n">
-        <v>120</v>
-      </c>
-      <c r="G44" s="27" t="n"/>
+        <v>122</v>
+      </c>
+      <c r="G44" s="27" t="n">
+        <v>121</v>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>app</t>
@@ -3025,7 +3027,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-24 02:51:37</t>
+          <t>2026-10-24 16:46:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3045,14 +3047,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F45" s="27" t="n">
-        <v>8981</v>
+        <v>121</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>2680</v>
+        <v>120</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3063,7 +3065,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-24 01:14:58</t>
+          <t>2026-10-24 08:35:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3078,16 +3080,28 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>120</v>
+      </c>
       <c r="G46" s="27" t="n"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 20:18:43</t>
+          <t>2026-10-24 02:51:37</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3111,10 +3125,10 @@
         </is>
       </c>
       <c r="F47" s="27" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G47" s="27" t="n">
         <v>2680</v>
-      </c>
-      <c r="G47" s="27" t="n">
-        <v>2650</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3125,53 +3139,41 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:58</t>
+          <t>2026-10-24 01:14:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="n">
-        <v>4933</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="n"/>
       <c r="G48" s="27" t="n"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:45</t>
+          <t>2026-10-23 20:18:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3181,14 +3183,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F49" s="27" t="n">
-        <v>7567</v>
+        <v>2680</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>0</v>
+        <v>2650</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3199,7 +3201,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:27</t>
+          <t>2026-10-23 19:50:58</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3219,15 +3221,13 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F50" s="27" t="n">
-        <v>4189</v>
-      </c>
-      <c r="G50" s="27" t="n">
-        <v>0</v>
-      </c>
+        <v>4933</v>
+      </c>
+      <c r="G50" s="27" t="n"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>app</t>
@@ -3237,7 +3237,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23 19:49:41</t>
+          <t>2026-10-23 19:50:45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F51" s="27" t="n">
-        <v>3685</v>
+        <v>7567</v>
       </c>
       <c r="G51" s="27" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-23 18:21:22</t>
+          <t>2026-10-23 19:50:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3295,14 +3295,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F52" s="27" t="n">
-        <v>2650</v>
+        <v>4189</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-23 15:07:26</t>
+          <t>2026-10-23 19:49:41</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3337,9 +3337,11 @@
         </is>
       </c>
       <c r="F53" s="27" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G53" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="27" t="n"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>shortcut</t>
@@ -3349,7 +3351,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-23 13:29:42</t>
+          <t>2026-10-23 18:21:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3373,10 +3375,10 @@
         </is>
       </c>
       <c r="F54" s="27" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G54" s="27" t="n">
         <v>831</v>
-      </c>
-      <c r="G54" s="27" t="n">
-        <v>387</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3387,31 +3389,43 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-23 09:09:43</t>
+          <t>2026-10-23 15:07:26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G55" s="27" t="n"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:26</t>
+          <t>2026-10-23 13:29:42</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3435,9 +3449,11 @@
         </is>
       </c>
       <c r="F56" s="27" t="n">
+        <v>831</v>
+      </c>
+      <c r="G56" s="27" t="n">
         <v>387</v>
       </c>
-      <c r="G56" s="27" t="n"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>app</t>
@@ -3447,7 +3463,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-23 08:06:10</t>
+          <t>2026-10-23 09:09:43</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3462,40 +3478,26 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="n">
-        <v>9720</v>
-      </c>
-      <c r="G57" s="27" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="27" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-23 01:18:21</t>
+          <t>2026-10-23 08:06:26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3505,11 +3507,11 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F58" s="27" t="n">
-        <v>9097</v>
+        <v>387</v>
       </c>
       <c r="G58" s="27" t="n"/>
       <c r="H58" t="inlineStr">
@@ -3521,190 +3523,216 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22 17:45:58</t>
+          <t>2026-10-23 08:06:10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>9720</v>
+      </c>
+      <c r="G59" s="27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37:14</t>
+          <t>2026-10-23 01:18:21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>9097</v>
+      </c>
       <c r="G60" s="27" t="n"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22 15:53:11</t>
+          <t>2026-10-22 17:45:58</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F61" s="27" t="n">
-        <v>10808</v>
-      </c>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="n"/>
       <c r="G61" s="27" t="n"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-22 15:25:40</t>
+          <t>2026-10-22 17:37:14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F62" s="27" t="n">
-        <v>0</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="n"/>
       <c r="G62" s="27" t="n"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>shortcut</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 15:53:11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F63" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="n">
+        <v>10808</v>
+      </c>
       <c r="G63" s="27" t="n"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-22 11:21:02</t>
+          <t>2026-10-22 15:25:40</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>requested</t>
-        </is>
-      </c>
-      <c r="F64" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G64" s="27" t="n"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-22 11:06:21</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="F65" s="27" t="n"/>
@@ -3713,43 +3741,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:33</t>
+          <t>2026-10-22 11:21:02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="F66" s="27" t="n">
-        <v>1100</v>
-      </c>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="n"/>
       <c r="G66" s="27" t="n"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-22 10:31:24</t>
+          <t>2026-10-22 11:06:21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3764,30 +3780,16 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="n">
-        <v>18461</v>
-      </c>
-      <c r="G67" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="n"/>
+      <c r="G67" s="27" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:56</t>
+          <t>2026-10-22 10:31:33</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3802,16 +3804,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="F68" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F68" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="G68" s="27" t="n"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-22 10:21:15</t>
+          <t>2026-10-22 10:31:24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3826,52 +3840,54 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>unstory</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n"/>
-      <c r="G69" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="n">
+        <v>18461</v>
+      </c>
+      <c r="G69" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-22 04:46:10</t>
+          <t>2026-10-22 10:21:56</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="n">
-        <v>4842</v>
-      </c>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="n"/>
       <c r="G70" s="27" t="n"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-22 03:50:41</t>
+          <t>2026-10-22 10:21:15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3886,7 +3902,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>unstory</t>
         </is>
       </c>
       <c r="F71" s="27" t="n"/>
@@ -3895,17 +3911,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21 23:51:07</t>
+          <t>2026-10-22 04:46:10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3919,34 +3935,34 @@
         </is>
       </c>
       <c r="F72" s="27" t="n">
-        <v>0</v>
+        <v>4842</v>
       </c>
       <c r="G72" s="27" t="n"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>shortcut</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21 23:49:15</t>
+          <t>2026-10-22 03:50:41</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>story</t>
         </is>
       </c>
       <c r="F73" s="27" t="n"/>
@@ -3955,67 +3971,67 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21 23:14:41</t>
+          <t>2026-10-21 23:51:07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="G74" s="27" t="n"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21 23:13:32</t>
+          <t>2026-10-21 23:49:15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>minerva</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minerva Perez</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="n">
-        <v>12641</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="n"/>
       <c r="G75" s="27" t="n"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21 23:11:16</t>
+          <t>2026-10-21 23:14:41</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4030,7 +4046,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>avatar</t>
         </is>
       </c>
       <c r="F76" s="27" t="n"/>
@@ -4039,17 +4055,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21 23:05:30</t>
+          <t>2026-10-21 23:13:32</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4063,7 +4079,7 @@
         </is>
       </c>
       <c r="F77" s="27" t="n">
-        <v>5345</v>
+        <v>12641</v>
       </c>
       <c r="G77" s="27" t="n"/>
       <c r="H77" t="inlineStr">
@@ -4075,22 +4091,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:30</t>
+          <t>2026-10-21 23:11:16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>armando</t>
+          <t>minerva</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Armando Alarcon</t>
+          <t>Minerva Perez</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F78" s="27" t="n"/>
@@ -4099,7 +4115,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-21 23:04:04</t>
+          <t>2026-10-21 23:05:30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4114,69 +4130,67 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F79" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F79" s="27" t="n">
+        <v>5345</v>
+      </c>
       <c r="G79" s="27" t="n"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:34</t>
+          <t>2026-10-21 23:04:30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F80" s="27" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G80" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F80" s="27" t="n"/>
+      <c r="G80" s="27" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-21 13:12:27</t>
+          <t>2026-10-21 23:04:04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>armando</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Armando Alarcon</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>avatar</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F81" s="27" t="n"/>
@@ -4185,82 +4199,84 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:56</t>
+          <t>2026-10-21 13:42:34</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>danielle</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Danielle Surini</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F82" s="27" t="n"/>
-      <c r="G82" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F82" s="27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G82" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-21 12:36:32</t>
+          <t>2026-10-21 13:12:27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F83" s="27" t="n">
-        <v>10383</v>
-      </c>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="F83" s="27" t="n"/>
       <c r="G83" s="27" t="n"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-21 12:28:14</t>
+          <t>2026-10-21 13:11:56</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>gonza</t>
+          <t>danielle</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gonza Souza</t>
+          <t>Danielle Surini</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>synckey</t>
+          <t>joined</t>
         </is>
       </c>
       <c r="F84" s="27" t="n"/>
@@ -4269,7 +4285,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-21 12:25:53</t>
+          <t>2026-10-21 12:36:32</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4284,136 +4300,148 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>joined</t>
-        </is>
-      </c>
-      <c r="F85" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F85" s="27" t="n">
+        <v>10383</v>
+      </c>
       <c r="G85" s="27" t="n"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-21 11:03:58</t>
+          <t>2026-10-21 12:28:14</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F86" s="27" t="n">
-        <v>100</v>
-      </c>
+          <t>synckey</t>
+        </is>
+      </c>
+      <c r="F86" s="27" t="n"/>
       <c r="G86" s="27" t="n"/>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-21 11:01:42</t>
+          <t>2026-10-21 12:25:53</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>eron</t>
+          <t>gonza</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Eron Netto</t>
+          <t>Gonza Souza</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>steps</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="F87" s="27" t="n">
-        <v>9060</v>
-      </c>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="F87" s="27" t="n"/>
       <c r="G87" s="27" t="n"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-21 10:44:13</t>
+          <t>2026-10-21 11:03:58</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>synckey</t>
-        </is>
-      </c>
-      <c r="F88" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F88" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="G88" s="27" t="n"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-21 10:43:02</t>
+          <t>2026-10-21 11:01:42</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>luis</t>
+          <t>eron</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Luís Rodney</t>
+          <t>Eron Netto</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>avatar</t>
-        </is>
-      </c>
-      <c r="F89" s="27" t="n"/>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F89" s="27" t="n">
+        <v>9060</v>
+      </c>
       <c r="G89" s="27" t="n"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-21 10:42:39</t>
+          <t>2026-10-21 10:44:13</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4428,7 +4456,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>joined</t>
+          <t>synckey</t>
         </is>
       </c>
       <c r="F90" s="27" t="n"/>
@@ -4437,53 +4465,41 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-21 04:34:33</t>
+          <t>2026-10-21 10:43:02</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>rogelio</t>
+          <t>luis</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Rogelio Garcia</t>
+          <t>Luís Rodney</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>